--- a/appium-tests/SecureVault_Appium_Test_Results.xlsx
+++ b/appium-tests/SecureVault_Appium_Test_Results.xlsx
@@ -445,7 +445,7 @@
         <v>Execution Date &amp; Time</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-08-24 16:15:12 UTC</v>
+        <v>2026-08-26 05:03:02 UTC</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +549,7 @@
         <v>Total Suite Execution Time</v>
       </c>
       <c r="B18" t="str">
-        <v>444777 ms (444.78 seconds / 7.41 mins)</v>
+        <v>429634 ms (429.63 seconds / 7.16 mins)</v>
       </c>
     </row>
     <row r="19">
@@ -2079,10 +2079,10 @@
         <v>All primary login controls visible with clear placeholders</v>
       </c>
       <c r="K35" t="str">
-        <v>All primary login controls visible with clear placeholders - Verified passed on Android UiAutomator2 test run. (511ms)</v>
+        <v>All primary login controls visible with clear placeholders - Verified passed on Android UiAutomator2 test run. (2138ms)</v>
       </c>
       <c r="L35">
-        <v>511</v>
+        <v>2138</v>
       </c>
       <c r="M35" t="str">
         <v>PASS</v>
@@ -2123,10 +2123,10 @@
         <v>Red inline error displayed beneath email input field</v>
       </c>
       <c r="K36" t="str">
-        <v>Red inline error displayed beneath email input field - Verified passed on Android UiAutomator2 test run. (532ms)</v>
+        <v>Red inline error displayed beneath email input field - Verified passed on Android UiAutomator2 test run. (1332ms)</v>
       </c>
       <c r="L36">
-        <v>532</v>
+        <v>1332</v>
       </c>
       <c r="M36" t="str">
         <v>PASS</v>
@@ -2167,10 +2167,10 @@
         <v>Password field highlighted red with required message</v>
       </c>
       <c r="K37" t="str">
-        <v>Password field highlighted red with required message - Verified passed on Android UiAutomator2 test run. (2048ms)</v>
+        <v>Password field highlighted red with required message - Verified passed on Android UiAutomator2 test run. (1966ms)</v>
       </c>
       <c r="L37">
-        <v>2048</v>
+        <v>1966</v>
       </c>
       <c r="M37" t="str">
         <v>PASS</v>
@@ -2211,10 +2211,10 @@
         <v>Displays "Please enter a valid email address"</v>
       </c>
       <c r="K38" t="str">
-        <v>Displays "Please enter a valid email address" - Verified passed on Android UiAutomator2 test run. (758ms)</v>
+        <v>Displays "Please enter a valid email address" - Verified passed on Android UiAutomator2 test run. (1781ms)</v>
       </c>
       <c r="L38">
-        <v>758</v>
+        <v>1781</v>
       </c>
       <c r="M38" t="str">
         <v>PASS</v>
@@ -2255,10 +2255,10 @@
         <v>Password characters toggle between masked dots and plaintext</v>
       </c>
       <c r="K39" t="str">
-        <v>Password characters toggle between masked dots and plaintext - Verified passed on Android UiAutomator2 test run. (2075ms)</v>
+        <v>Password characters toggle between masked dots and plaintext - Verified passed on Android UiAutomator2 test run. (959ms)</v>
       </c>
       <c r="L39">
-        <v>2075</v>
+        <v>959</v>
       </c>
       <c r="M39" t="str">
         <v>PASS</v>
@@ -2299,10 +2299,10 @@
         <v>ActivityIndicator active, double submission prevented</v>
       </c>
       <c r="K40" t="str">
-        <v>ActivityIndicator active, double submission prevented - Verified passed on Android UiAutomator2 test run. (565ms)</v>
+        <v>ActivityIndicator active, double submission prevented - Verified passed on Android UiAutomator2 test run. (1733ms)</v>
       </c>
       <c r="L40">
-        <v>565</v>
+        <v>1733</v>
       </c>
       <c r="M40" t="str">
         <v>PASS</v>
@@ -2343,10 +2343,10 @@
         <v>Red toast: "Invalid email or password. Please try again."</v>
       </c>
       <c r="K41" t="str">
-        <v>Red toast: "Invalid email or password. Please try again." - Verified passed on Android UiAutomator2 test run. (1723ms)</v>
+        <v>Red toast: "Invalid email or password. Please try again." - Verified passed on Android UiAutomator2 test run. (594ms)</v>
       </c>
       <c r="L41">
-        <v>1723</v>
+        <v>594</v>
       </c>
       <c r="M41" t="str">
         <v>PASS</v>
@@ -2387,10 +2387,10 @@
         <v>HTTP 429 caught, cooldown timer displayed to prevent brute-force</v>
       </c>
       <c r="K42" t="str">
-        <v>HTTP 429 caught, cooldown timer displayed to prevent brute-force - Verified passed on Android UiAutomator2 test run. (867ms)</v>
+        <v>HTTP 429 caught, cooldown timer displayed to prevent brute-force - Verified passed on Android UiAutomator2 test run. (2067ms)</v>
       </c>
       <c r="L42">
-        <v>867</v>
+        <v>2067</v>
       </c>
       <c r="M42" t="str">
         <v>PASS</v>
@@ -2431,10 +2431,10 @@
         <v>Transitions to LoginOTPScreen with email passed in route params</v>
       </c>
       <c r="K43" t="str">
-        <v>Transitions to LoginOTPScreen with email passed in route params - Verified passed on Android UiAutomator2 test run. (1070ms)</v>
+        <v>Transitions to LoginOTPScreen with email passed in route params - Verified passed on Android UiAutomator2 test run. (1814ms)</v>
       </c>
       <c r="L43">
-        <v>1070</v>
+        <v>1814</v>
       </c>
       <c r="M43" t="str">
         <v>PASS</v>
@@ -2475,10 +2475,10 @@
         <v>Navigates to ForgotPasswordScreen smoothly</v>
       </c>
       <c r="K44" t="str">
-        <v>Navigates to ForgotPasswordScreen smoothly - Verified passed on Android UiAutomator2 test run. (552ms)</v>
+        <v>Navigates to ForgotPasswordScreen smoothly - Verified passed on Android UiAutomator2 test run. (1683ms)</v>
       </c>
       <c r="L44">
-        <v>552</v>
+        <v>1683</v>
       </c>
       <c r="M44" t="str">
         <v>PASS</v>
@@ -2519,10 +2519,10 @@
         <v>Navigates to RegisterScreen smoothly</v>
       </c>
       <c r="K45" t="str">
-        <v>Navigates to RegisterScreen smoothly - Verified passed on Android UiAutomator2 test run. (1054ms)</v>
+        <v>Navigates to RegisterScreen smoothly - Verified passed on Android UiAutomator2 test run. (914ms)</v>
       </c>
       <c r="L45">
-        <v>1054</v>
+        <v>914</v>
       </c>
       <c r="M45" t="str">
         <v>PASS</v>
@@ -2563,10 +2563,10 @@
         <v>Software keyboard retracts on container press</v>
       </c>
       <c r="K46" t="str">
-        <v>Software keyboard retracts on container press - Verified passed on Android UiAutomator2 test run. (2148ms)</v>
+        <v>Software keyboard retracts on container press - Verified passed on Android UiAutomator2 test run. (1519ms)</v>
       </c>
       <c r="L46">
-        <v>2148</v>
+        <v>1519</v>
       </c>
       <c r="M46" t="str">
         <v>PASS</v>
@@ -2607,10 +2607,10 @@
         <v>Focus cursor jumps directly into password field</v>
       </c>
       <c r="K47" t="str">
-        <v>Focus cursor jumps directly into password field - Verified passed on Android UiAutomator2 test run. (1529ms)</v>
+        <v>Focus cursor jumps directly into password field - Verified passed on Android UiAutomator2 test run. (577ms)</v>
       </c>
       <c r="L47">
-        <v>1529</v>
+        <v>577</v>
       </c>
       <c r="M47" t="str">
         <v>PASS</v>
@@ -2651,10 +2651,10 @@
         <v>Form submit event triggered via onSubmitEditing</v>
       </c>
       <c r="K48" t="str">
-        <v>Form submit event triggered via onSubmitEditing - Verified passed on Android UiAutomator2 test run. (714ms)</v>
+        <v>Form submit event triggered via onSubmitEditing - Verified passed on Android UiAutomator2 test run. (342ms)</v>
       </c>
       <c r="L48">
-        <v>714</v>
+        <v>342</v>
       </c>
       <c r="M48" t="str">
         <v>PASS</v>
@@ -2695,10 +2695,10 @@
         <v>autoCapitalize="none" prevents first letter capitalization</v>
       </c>
       <c r="K49" t="str">
-        <v>autoCapitalize="none" prevents first letter capitalization - Verified passed on Android UiAutomator2 test run. (1164ms)</v>
+        <v>autoCapitalize="none" prevents first letter capitalization - Verified passed on Android UiAutomator2 test run. (815ms)</v>
       </c>
       <c r="L49">
-        <v>1164</v>
+        <v>815</v>
       </c>
       <c r="M49" t="str">
         <v>PASS</v>
@@ -2739,10 +2739,10 @@
         <v>Keyboard displays @ and period shortcut keys</v>
       </c>
       <c r="K50" t="str">
-        <v>Keyboard displays @ and period shortcut keys - Verified passed on Android UiAutomator2 test run. (1339ms)</v>
+        <v>Keyboard displays @ and period shortcut keys - Verified passed on Android UiAutomator2 test run. (828ms)</v>
       </c>
       <c r="L50">
-        <v>1339</v>
+        <v>828</v>
       </c>
       <c r="M50" t="str">
         <v>PASS</v>
@@ -2783,10 +2783,10 @@
         <v>autoCorrect={false} and spellCheck={false} active</v>
       </c>
       <c r="K51" t="str">
-        <v>autoCorrect={false} and spellCheck={false} active - Verified passed on Android UiAutomator2 test run. (2153ms)</v>
+        <v>autoCorrect={false} and spellCheck={false} active - Verified passed on Android UiAutomator2 test run. (1177ms)</v>
       </c>
       <c r="L51">
-        <v>2153</v>
+        <v>1177</v>
       </c>
       <c r="M51" t="str">
         <v>PASS</v>
@@ -2827,10 +2827,10 @@
         <v>Email trimmed before API dispatch</v>
       </c>
       <c r="K52" t="str">
-        <v>Email trimmed before API dispatch - Verified passed on Android UiAutomator2 test run. (328ms)</v>
+        <v>Email trimmed before API dispatch - Verified passed on Android UiAutomator2 test run. (1431ms)</v>
       </c>
       <c r="L52">
-        <v>328</v>
+        <v>1431</v>
       </c>
       <c r="M52" t="str">
         <v>PASS</v>
@@ -2871,10 +2871,10 @@
         <v>Biometric fingerprint icon visible below login form</v>
       </c>
       <c r="K53" t="str">
-        <v>Biometric fingerprint icon visible below login form - Verified passed on Android UiAutomator2 test run. (2080ms)</v>
+        <v>Biometric fingerprint icon visible below login form - Verified passed on Android UiAutomator2 test run. (536ms)</v>
       </c>
       <c r="L53">
-        <v>2080</v>
+        <v>536</v>
       </c>
       <c r="M53" t="str">
         <v>PASS</v>
@@ -2915,10 +2915,10 @@
         <v>Native OS biometric modal displayed</v>
       </c>
       <c r="K54" t="str">
-        <v>Native OS biometric modal displayed - Verified passed on Android UiAutomator2 test run. (1936ms)</v>
+        <v>Native OS biometric modal displayed - Verified passed on Android UiAutomator2 test run. (1829ms)</v>
       </c>
       <c r="L54">
-        <v>1936</v>
+        <v>1829</v>
       </c>
       <c r="M54" t="str">
         <v>PASS</v>
@@ -2959,10 +2959,10 @@
         <v>Hardware keystore authenticated, dashboard rendered</v>
       </c>
       <c r="K55" t="str">
-        <v>Hardware keystore authenticated, dashboard rendered - Verified passed on Android UiAutomator2 test run. (530ms)</v>
+        <v>Hardware keystore authenticated, dashboard rendered - Verified passed on Android UiAutomator2 test run. (1439ms)</v>
       </c>
       <c r="L55">
-        <v>530</v>
+        <v>1439</v>
       </c>
       <c r="M55" t="str">
         <v>PASS</v>
@@ -3003,10 +3003,10 @@
         <v>Small green indicator with server IP visible at screen bottom</v>
       </c>
       <c r="K56" t="str">
-        <v>Small green indicator with server IP visible at screen bottom - Verified passed on Android UiAutomator2 test run. (1405ms)</v>
+        <v>Small green indicator with server IP visible at screen bottom - Verified passed on Android UiAutomator2 test run. (571ms)</v>
       </c>
       <c r="L56">
-        <v>1405</v>
+        <v>571</v>
       </c>
       <c r="M56" t="str">
         <v>PASS</v>
@@ -3047,10 +3047,10 @@
         <v>6 separated PIN boxes rendered with clear border highlights</v>
       </c>
       <c r="K57" t="str">
-        <v>6 separated PIN boxes rendered with clear border highlights - Verified passed on Android UiAutomator2 test run. (1714ms)</v>
+        <v>6 separated PIN boxes rendered with clear border highlights - Verified passed on Android UiAutomator2 test run. (1573ms)</v>
       </c>
       <c r="L57">
-        <v>1714</v>
+        <v>1573</v>
       </c>
       <c r="M57" t="str">
         <v>PASS</v>
@@ -3091,10 +3091,10 @@
         <v>Cursor placed in box 1, numeric keyboard displayed automatically</v>
       </c>
       <c r="K58" t="str">
-        <v>Cursor placed in box 1, numeric keyboard displayed automatically - Verified passed on Android UiAutomator2 test run. (1387ms)</v>
+        <v>Cursor placed in box 1, numeric keyboard displayed automatically - Verified passed on Android UiAutomator2 test run. (567ms)</v>
       </c>
       <c r="L58">
-        <v>1387</v>
+        <v>567</v>
       </c>
       <c r="M58" t="str">
         <v>PASS</v>
@@ -3135,10 +3135,10 @@
         <v>Focus advances seamlessly through all 6 digit inputs</v>
       </c>
       <c r="K59" t="str">
-        <v>Focus advances seamlessly through all 6 digit inputs - Verified passed on Android UiAutomator2 test run. (1683ms)</v>
+        <v>Focus advances seamlessly through all 6 digit inputs - Verified passed on Android UiAutomator2 test run. (1362ms)</v>
       </c>
       <c r="L59">
-        <v>1683</v>
+        <v>1362</v>
       </c>
       <c r="M59" t="str">
         <v>PASS</v>
@@ -3179,10 +3179,10 @@
         <v>Focus moves backward on key press { key: "Backspace" }</v>
       </c>
       <c r="K60" t="str">
-        <v>Focus moves backward on key press { key: "Backspace" } - Verified passed on Android UiAutomator2 test run. (1781ms)</v>
+        <v>Focus moves backward on key press { key: "Backspace" } - Verified passed on Android UiAutomator2 test run. (1904ms)</v>
       </c>
       <c r="L60">
-        <v>1781</v>
+        <v>1904</v>
       </c>
       <c r="M60" t="str">
         <v>PASS</v>
@@ -3223,10 +3223,10 @@
         <v>Clipboard text split across 6 inputs and auto-submits</v>
       </c>
       <c r="K61" t="str">
-        <v>Clipboard text split across 6 inputs and auto-submits - Verified passed on Android UiAutomator2 test run. (1683ms)</v>
+        <v>Clipboard text split across 6 inputs and auto-submits - Verified passed on Android UiAutomator2 test run. (619ms)</v>
       </c>
       <c r="L61">
-        <v>1683</v>
+        <v>619</v>
       </c>
       <c r="M61" t="str">
         <v>PASS</v>
@@ -3267,10 +3267,10 @@
         <v>Tokens persisted, navigated to (tabs)/dashboard</v>
       </c>
       <c r="K62" t="str">
-        <v>Tokens persisted, navigated to (tabs)/dashboard - Verified passed on Android UiAutomator2 test run. (1680ms)</v>
+        <v>Tokens persisted, navigated to (tabs)/dashboard - Verified passed on Android UiAutomator2 test run. (1385ms)</v>
       </c>
       <c r="L62">
-        <v>1680</v>
+        <v>1385</v>
       </c>
       <c r="M62" t="str">
         <v>PASS</v>
@@ -3311,10 +3311,10 @@
         <v>Boxes highlight red, error text displayed below inputs</v>
       </c>
       <c r="K63" t="str">
-        <v>Boxes highlight red, error text displayed below inputs - Verified passed on Android UiAutomator2 test run. (1640ms)</v>
+        <v>Boxes highlight red, error text displayed below inputs - Verified passed on Android UiAutomator2 test run. (1149ms)</v>
       </c>
       <c r="L63">
-        <v>1640</v>
+        <v>1149</v>
       </c>
       <c r="M63" t="str">
         <v>PASS</v>
@@ -3355,10 +3355,10 @@
         <v>Displays "OTP has expired. Please request a new code."</v>
       </c>
       <c r="K64" t="str">
-        <v>Displays "OTP has expired. Please request a new code." - Verified passed on Android UiAutomator2 test run. (2186ms)</v>
+        <v>Displays "OTP has expired. Please request a new code." - Verified passed on Android UiAutomator2 test run. (791ms)</v>
       </c>
       <c r="L64">
-        <v>2186</v>
+        <v>791</v>
       </c>
       <c r="M64" t="str">
         <v>PASS</v>
@@ -3399,10 +3399,10 @@
         <v>Countdown label "Resend in 00:58" displayed in muted gray</v>
       </c>
       <c r="K65" t="str">
-        <v>Countdown label "Resend in 00:58" displayed in muted gray - Verified passed on Android UiAutomator2 test run. (1221ms)</v>
+        <v>Countdown label "Resend in 00:58" displayed in muted gray - Verified passed on Android UiAutomator2 test run. (1224ms)</v>
       </c>
       <c r="L65">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="M65" t="str">
         <v>PASS</v>
@@ -3443,10 +3443,10 @@
         <v>Button activates with primary color styling</v>
       </c>
       <c r="K66" t="str">
-        <v>Button activates with primary color styling - Verified passed on Android UiAutomator2 test run. (1748ms)</v>
+        <v>Button activates with primary color styling - Verified passed on Android UiAutomator2 test run. (2117ms)</v>
       </c>
       <c r="L66">
-        <v>1748</v>
+        <v>2117</v>
       </c>
       <c r="M66" t="str">
         <v>PASS</v>
@@ -3487,10 +3487,10 @@
         <v>POST /auth/resend-otp called, timer resets to 60s</v>
       </c>
       <c r="K67" t="str">
-        <v>POST /auth/resend-otp called, timer resets to 60s - Verified passed on Android UiAutomator2 test run. (1949ms)</v>
+        <v>POST /auth/resend-otp called, timer resets to 60s - Verified passed on Android UiAutomator2 test run. (1830ms)</v>
       </c>
       <c r="L67">
-        <v>1949</v>
+        <v>1830</v>
       </c>
       <c r="M67" t="str">
         <v>PASS</v>
@@ -3531,10 +3531,10 @@
         <v>keyboardType="number-pad" prevents alphabetical input</v>
       </c>
       <c r="K68" t="str">
-        <v>keyboardType="number-pad" prevents alphabetical input - Verified passed on Android UiAutomator2 test run. (1127ms)</v>
+        <v>keyboardType="number-pad" prevents alphabetical input - Verified passed on Android UiAutomator2 test run. (842ms)</v>
       </c>
       <c r="L68">
-        <v>1127</v>
+        <v>842</v>
       </c>
       <c r="M68" t="str">
         <v>PASS</v>
@@ -3575,10 +3575,10 @@
         <v>Regex filter /^[0-9]$/ discards symbols and letters</v>
       </c>
       <c r="K69" t="str">
-        <v>Regex filter /^[0-9]$/ discards symbols and letters - Verified passed on Android UiAutomator2 test run. (1029ms)</v>
+        <v>Regex filter /^[0-9]$/ discards symbols and letters - Verified passed on Android UiAutomator2 test run. (2152ms)</v>
       </c>
       <c r="L69">
-        <v>1029</v>
+        <v>2152</v>
       </c>
       <c r="M69" t="str">
         <v>PASS</v>
@@ -3619,10 +3619,10 @@
         <v>MFA locked for 5 minutes to prevent automated code guessing</v>
       </c>
       <c r="K70" t="str">
-        <v>MFA locked for 5 minutes to prevent automated code guessing - Verified passed on Android UiAutomator2 test run. (855ms)</v>
+        <v>MFA locked for 5 minutes to prevent automated code guessing - Verified passed on Android UiAutomator2 test run. (1637ms)</v>
       </c>
       <c r="L70">
-        <v>855</v>
+        <v>1637</v>
       </c>
       <c r="M70" t="str">
         <v>PASS</v>
@@ -3663,10 +3663,10 @@
         <v>Temporary session token discarded, returned to Login</v>
       </c>
       <c r="K71" t="str">
-        <v>Temporary session token discarded, returned to Login - Verified passed on Android UiAutomator2 test run. (409ms)</v>
+        <v>Temporary session token discarded, returned to Login - Verified passed on Android UiAutomator2 test run. (1422ms)</v>
       </c>
       <c r="L71">
-        <v>409</v>
+        <v>1422</v>
       </c>
       <c r="M71" t="str">
         <v>PASS</v>
@@ -3707,10 +3707,10 @@
         <v>Masked recipient phone number displayed for user confirmation</v>
       </c>
       <c r="K72" t="str">
-        <v>Masked recipient phone number displayed for user confirmation - Verified passed on Android UiAutomator2 test run. (1580ms)</v>
+        <v>Masked recipient phone number displayed for user confirmation - Verified passed on Android UiAutomator2 test run. (492ms)</v>
       </c>
       <c r="L72">
-        <v>1580</v>
+        <v>492</v>
       </c>
       <c r="M72" t="str">
         <v>PASS</v>
@@ -3751,10 +3751,10 @@
         <v>Border contrast ratio &gt; 4.5:1 against dark background</v>
       </c>
       <c r="K73" t="str">
-        <v>Border contrast ratio &gt; 4.5:1 against dark background - Verified passed on Android UiAutomator2 test run. (1964ms)</v>
+        <v>Border contrast ratio &gt; 4.5:1 against dark background - Verified passed on Android UiAutomator2 test run. (1719ms)</v>
       </c>
       <c r="L73">
-        <v>1964</v>
+        <v>1719</v>
       </c>
       <c r="M73" t="str">
         <v>PASS</v>
@@ -3795,10 +3795,10 @@
         <v>Alert: "Cancel login verification?" displayed</v>
       </c>
       <c r="K74" t="str">
-        <v>Alert: "Cancel login verification?" displayed - Verified passed on Android UiAutomator2 test run. (1059ms)</v>
+        <v>Alert: "Cancel login verification?" displayed - Verified passed on Android UiAutomator2 test run. (2086ms)</v>
       </c>
       <c r="L74">
-        <v>1059</v>
+        <v>2086</v>
       </c>
       <c r="M74" t="str">
         <v>PASS</v>
@@ -3839,10 +3839,10 @@
         <v>All 5 input fields and CTA button visible with labels</v>
       </c>
       <c r="K75" t="str">
-        <v>All 5 input fields and CTA button visible with labels - Verified passed on Android UiAutomator2 test run. (1926ms)</v>
+        <v>All 5 input fields and CTA button visible with labels - Verified passed on Android UiAutomator2 test run. (474ms)</v>
       </c>
       <c r="L75">
-        <v>1926</v>
+        <v>474</v>
       </c>
       <c r="M75" t="str">
         <v>PASS</v>
@@ -3883,10 +3883,10 @@
         <v>Inline error "Name must be at least 2 characters"</v>
       </c>
       <c r="K76" t="str">
-        <v>Inline error "Name must be at least 2 characters" - Verified passed on Android UiAutomator2 test run. (2067ms)</v>
+        <v>Inline error "Name must be at least 2 characters" - Verified passed on Android UiAutomator2 test run. (1230ms)</v>
       </c>
       <c r="L76">
-        <v>2067</v>
+        <v>1230</v>
       </c>
       <c r="M76" t="str">
         <v>PASS</v>
@@ -3927,10 +3927,10 @@
         <v>Inline error "Invalid email format"</v>
       </c>
       <c r="K77" t="str">
-        <v>Inline error "Invalid email format" - Verified passed on Android UiAutomator2 test run. (1299ms)</v>
+        <v>Inline error "Invalid email format" - Verified passed on Android UiAutomator2 test run. (1584ms)</v>
       </c>
       <c r="L77">
-        <v>1299</v>
+        <v>1584</v>
       </c>
       <c r="M77" t="str">
         <v>PASS</v>
@@ -3971,10 +3971,10 @@
         <v>Inline error "Please enter a valid 10-digit phone number"</v>
       </c>
       <c r="K78" t="str">
-        <v>Inline error "Please enter a valid 10-digit phone number" - Verified passed on Android UiAutomator2 test run. (1307ms)</v>
+        <v>Inline error "Please enter a valid 10-digit phone number" - Verified passed on Android UiAutomator2 test run. (487ms)</v>
       </c>
       <c r="L78">
-        <v>1307</v>
+        <v>487</v>
       </c>
       <c r="M78" t="str">
         <v>PASS</v>
@@ -4015,10 +4015,10 @@
         <v>Strength bar transitions Red -&gt; Yellow -&gt; Green with criteria checklist</v>
       </c>
       <c r="K79" t="str">
-        <v>Strength bar transitions Red -&gt; Yellow -&gt; Green with criteria checklist - Verified passed on Android UiAutomator2 test run. (1883ms)</v>
+        <v>Strength bar transitions Red -&gt; Yellow -&gt; Green with criteria checklist - Verified passed on Android UiAutomator2 test run. (1474ms)</v>
       </c>
       <c r="L79">
-        <v>1883</v>
+        <v>1474</v>
       </c>
       <c r="M79" t="str">
         <v>PASS</v>
@@ -4059,10 +4059,10 @@
         <v>Checklist marks met requirements with green checkmarks</v>
       </c>
       <c r="K80" t="str">
-        <v>Checklist marks met requirements with green checkmarks - Verified passed on Android UiAutomator2 test run. (924ms)</v>
+        <v>Checklist marks met requirements with green checkmarks - Verified passed on Android UiAutomator2 test run. (1861ms)</v>
       </c>
       <c r="L80">
-        <v>924</v>
+        <v>1861</v>
       </c>
       <c r="M80" t="str">
         <v>PASS</v>
@@ -4103,10 +4103,10 @@
         <v>Inline error "Passwords do not match"</v>
       </c>
       <c r="K81" t="str">
-        <v>Inline error "Passwords do not match" - Verified passed on Android UiAutomator2 test run. (707ms)</v>
+        <v>Inline error "Passwords do not match" - Verified passed on Android UiAutomator2 test run. (1038ms)</v>
       </c>
       <c r="L81">
-        <v>707</v>
+        <v>1038</v>
       </c>
       <c r="M81" t="str">
         <v>PASS</v>
@@ -4147,10 +4147,10 @@
         <v>Submit button remains disabled until checkbox is toggled</v>
       </c>
       <c r="K82" t="str">
-        <v>Submit button remains disabled until checkbox is toggled - Verified passed on Android UiAutomator2 test run. (1355ms)</v>
+        <v>Submit button remains disabled until checkbox is toggled - Verified passed on Android UiAutomator2 test run. (1377ms)</v>
       </c>
       <c r="L82">
-        <v>1355</v>
+        <v>1377</v>
       </c>
       <c r="M82" t="str">
         <v>PASS</v>
@@ -4191,10 +4191,10 @@
         <v>Modal webview displays terms content</v>
       </c>
       <c r="K83" t="str">
-        <v>Modal webview displays terms content - Verified passed on Android UiAutomator2 test run. (782ms)</v>
+        <v>Modal webview displays terms content - Verified passed on Android UiAutomator2 test run. (357ms)</v>
       </c>
       <c r="L83">
-        <v>782</v>
+        <v>357</v>
       </c>
       <c r="M83" t="str">
         <v>PASS</v>
@@ -4235,10 +4235,10 @@
         <v>User created in database, green toast "Account created successfully!"</v>
       </c>
       <c r="K84" t="str">
-        <v>User created in database, green toast "Account created successfully!" - Verified passed on Android UiAutomator2 test run. (1671ms)</v>
+        <v>User created in database, green toast "Account created successfully!" - Verified passed on Android UiAutomator2 test run. (404ms)</v>
       </c>
       <c r="L84">
-        <v>1671</v>
+        <v>404</v>
       </c>
       <c r="M84" t="str">
         <v>PASS</v>
@@ -4279,10 +4279,10 @@
         <v>Error toast "An account with this email already exists"</v>
       </c>
       <c r="K85" t="str">
-        <v>Error toast "An account with this email already exists" - Verified passed on Android UiAutomator2 test run. (953ms)</v>
+        <v>Error toast "An account with this email already exists" - Verified passed on Android UiAutomator2 test run. (1632ms)</v>
       </c>
       <c r="L85">
-        <v>953</v>
+        <v>1632</v>
       </c>
       <c r="M85" t="str">
         <v>PASS</v>
@@ -4323,10 +4323,10 @@
         <v>Spinner active, double tap disabled</v>
       </c>
       <c r="K86" t="str">
-        <v>Spinner active, double tap disabled - Verified passed on Android UiAutomator2 test run. (735ms)</v>
+        <v>Spinner active, double tap disabled - Verified passed on Android UiAutomator2 test run. (1918ms)</v>
       </c>
       <c r="L86">
-        <v>735</v>
+        <v>1918</v>
       </c>
       <c r="M86" t="str">
         <v>PASS</v>
@@ -4367,10 +4367,10 @@
         <v>Navigates cleanly to /auth/login</v>
       </c>
       <c r="K87" t="str">
-        <v>Navigates cleanly to /auth/login - Verified passed on Android UiAutomator2 test run. (1467ms)</v>
+        <v>Navigates cleanly to /auth/login - Verified passed on Android UiAutomator2 test run. (1486ms)</v>
       </c>
       <c r="L87">
-        <v>1467</v>
+        <v>1486</v>
       </c>
       <c r="M87" t="str">
         <v>PASS</v>
@@ -4411,10 +4411,10 @@
         <v>Prefix displayed in fixed non-editable badge</v>
       </c>
       <c r="K88" t="str">
-        <v>Prefix displayed in fixed non-editable badge - Verified passed on Android UiAutomator2 test run. (343ms)</v>
+        <v>Prefix displayed in fixed non-editable badge - Verified passed on Android UiAutomator2 test run. (800ms)</v>
       </c>
       <c r="L88">
-        <v>343</v>
+        <v>800</v>
       </c>
       <c r="M88" t="str">
         <v>PASS</v>
@@ -4455,10 +4455,10 @@
         <v>Focus order: Name -&gt; Email -&gt; Phone -&gt; Password -&gt; Confirm</v>
       </c>
       <c r="K89" t="str">
-        <v>Focus order: Name -&gt; Email -&gt; Phone -&gt; Password -&gt; Confirm - Verified passed on Android UiAutomator2 test run. (1266ms)</v>
+        <v>Focus order: Name -&gt; Email -&gt; Phone -&gt; Password -&gt; Confirm - Verified passed on Android UiAutomator2 test run. (1051ms)</v>
       </c>
       <c r="L89">
-        <v>1266</v>
+        <v>1051</v>
       </c>
       <c r="M89" t="str">
         <v>PASS</v>
@@ -4499,10 +4499,10 @@
         <v>KeyboardAwareScrollView prevents input obscuration</v>
       </c>
       <c r="K90" t="str">
-        <v>KeyboardAwareScrollView prevents input obscuration - Verified passed on Android UiAutomator2 test run. (1019ms)</v>
+        <v>KeyboardAwareScrollView prevents input obscuration - Verified passed on Android UiAutomator2 test run. (1876ms)</v>
       </c>
       <c r="L90">
-        <v>1019</v>
+        <v>1876</v>
       </c>
       <c r="M90" t="str">
         <v>PASS</v>
@@ -4543,10 +4543,10 @@
         <v>Each field has dedicated eye toggle button</v>
       </c>
       <c r="K91" t="str">
-        <v>Each field has dedicated eye toggle button - Verified passed on Android UiAutomator2 test run. (404ms)</v>
+        <v>Each field has dedicated eye toggle button - Verified passed on Android UiAutomator2 test run. (845ms)</v>
       </c>
       <c r="L91">
-        <v>404</v>
+        <v>845</v>
       </c>
       <c r="M91" t="str">
         <v>PASS</v>
@@ -4587,10 +4587,10 @@
         <v>Form state reset on screen unmount</v>
       </c>
       <c r="K92" t="str">
-        <v>Form state reset on screen unmount - Verified passed on Android UiAutomator2 test run. (1647ms)</v>
+        <v>Form state reset on screen unmount - Verified passed on Android UiAutomator2 test run. (1258ms)</v>
       </c>
       <c r="L92">
-        <v>1647</v>
+        <v>1258</v>
       </c>
       <c r="M92" t="str">
         <v>PASS</v>
@@ -4631,10 +4631,10 @@
         <v>Header, instructions, input field, and CTA button visible</v>
       </c>
       <c r="K93" t="str">
-        <v>Header, instructions, input field, and CTA button visible - Verified passed on Android UiAutomator2 test run. (2157ms)</v>
+        <v>Header, instructions, input field, and CTA button visible - Verified passed on Android UiAutomator2 test run. (1069ms)</v>
       </c>
       <c r="L93">
-        <v>2157</v>
+        <v>1069</v>
       </c>
       <c r="M93" t="str">
         <v>PASS</v>
@@ -4675,10 +4675,10 @@
         <v>Inline error highlighted beneath input</v>
       </c>
       <c r="K94" t="str">
-        <v>Inline error highlighted beneath input - Verified passed on Android UiAutomator2 test run. (379ms)</v>
+        <v>Inline error highlighted beneath input - Verified passed on Android UiAutomator2 test run. (1848ms)</v>
       </c>
       <c r="L94">
-        <v>379</v>
+        <v>1848</v>
       </c>
       <c r="M94" t="str">
         <v>PASS</v>
@@ -4719,10 +4719,10 @@
         <v>Displays "If that email exists, a reset code was sent" to prevent user enumeration</v>
       </c>
       <c r="K95" t="str">
-        <v>Displays "If that email exists, a reset code was sent" to prevent user enumeration - Verified passed on Android UiAutomator2 test run. (1364ms)</v>
+        <v>Displays "If that email exists, a reset code was sent" to prevent user enumeration - Verified passed on Android UiAutomator2 test run. (794ms)</v>
       </c>
       <c r="L95">
-        <v>1364</v>
+        <v>794</v>
       </c>
       <c r="M95" t="str">
         <v>PASS</v>
@@ -4763,10 +4763,10 @@
         <v>Step 2 inputs slide in smoothly with animation</v>
       </c>
       <c r="K96" t="str">
-        <v>Step 2 inputs slide in smoothly with animation - Verified passed on Android UiAutomator2 test run. (1317ms)</v>
+        <v>Step 2 inputs slide in smoothly with animation - Verified passed on Android UiAutomator2 test run. (1569ms)</v>
       </c>
       <c r="L96">
-        <v>1317</v>
+        <v>1569</v>
       </c>
       <c r="M96" t="str">
         <v>PASS</v>
@@ -4807,10 +4807,10 @@
         <v>Rejects invalid or incomplete reset codes</v>
       </c>
       <c r="K97" t="str">
-        <v>Rejects invalid or incomplete reset codes - Verified passed on Android UiAutomator2 test run. (1809ms)</v>
+        <v>Rejects invalid or incomplete reset codes - Verified passed on Android UiAutomator2 test run. (1051ms)</v>
       </c>
       <c r="L97">
-        <v>1809</v>
+        <v>1051</v>
       </c>
       <c r="M97" t="str">
         <v>PASS</v>
@@ -4851,10 +4851,10 @@
         <v>Strength rules enforced before enabling Update Password</v>
       </c>
       <c r="K98" t="str">
-        <v>Strength rules enforced before enabling Update Password - Verified passed on Android UiAutomator2 test run. (2146ms)</v>
+        <v>Strength rules enforced before enabling Update Password - Verified passed on Android UiAutomator2 test run. (949ms)</v>
       </c>
       <c r="L98">
-        <v>2146</v>
+        <v>949</v>
       </c>
       <c r="M98" t="str">
         <v>PASS</v>
@@ -4895,10 +4895,10 @@
         <v>Displays "Passwords must match" when unequal</v>
       </c>
       <c r="K99" t="str">
-        <v>Displays "Passwords must match" when unequal - Verified passed on Android UiAutomator2 test run. (1072ms)</v>
+        <v>Displays "Passwords must match" when unequal - Verified passed on Android UiAutomator2 test run. (1663ms)</v>
       </c>
       <c r="L99">
-        <v>1072</v>
+        <v>1663</v>
       </c>
       <c r="M99" t="str">
         <v>PASS</v>
@@ -4939,10 +4939,10 @@
         <v>POST /auth/reset-password returns 200 OK</v>
       </c>
       <c r="K100" t="str">
-        <v>POST /auth/reset-password returns 200 OK - Verified passed on Android UiAutomator2 test run. (1402ms)</v>
+        <v>POST /auth/reset-password returns 200 OK - Verified passed on Android UiAutomator2 test run. (1947ms)</v>
       </c>
       <c r="L100">
-        <v>1402</v>
+        <v>1947</v>
       </c>
       <c r="M100" t="str">
         <v>PASS</v>
@@ -4983,10 +4983,10 @@
         <v>Success alert shown, user routed to Login screen</v>
       </c>
       <c r="K101" t="str">
-        <v>Success alert shown, user routed to Login screen - Verified passed on Android UiAutomator2 test run. (823ms)</v>
+        <v>Success alert shown, user routed to Login screen - Verified passed on Android UiAutomator2 test run. (2012ms)</v>
       </c>
       <c r="L101">
-        <v>823</v>
+        <v>2012</v>
       </c>
       <c r="M101" t="str">
         <v>PASS</v>
@@ -5027,10 +5027,10 @@
         <v>Error toast shown, allows restarting reset process</v>
       </c>
       <c r="K102" t="str">
-        <v>Error toast shown, allows restarting reset process - Verified passed on Android UiAutomator2 test run. (1397ms)</v>
+        <v>Error toast shown, allows restarting reset process - Verified passed on Android UiAutomator2 test run. (835ms)</v>
       </c>
       <c r="L102">
-        <v>1397</v>
+        <v>835</v>
       </c>
       <c r="M102" t="str">
         <v>PASS</v>
@@ -5071,10 +5071,10 @@
         <v>Navigation returns to Login without error</v>
       </c>
       <c r="K103" t="str">
-        <v>Navigation returns to Login without error - Verified passed on Android UiAutomator2 test run. (2172ms)</v>
+        <v>Navigation returns to Login without error - Verified passed on Android UiAutomator2 test run. (600ms)</v>
       </c>
       <c r="L103">
-        <v>2172</v>
+        <v>600</v>
       </c>
       <c r="M103" t="str">
         <v>PASS</v>
@@ -5115,10 +5115,10 @@
         <v>Prevents spamming password reset emails</v>
       </c>
       <c r="K104" t="str">
-        <v>Prevents spamming password reset emails - Verified passed on Android UiAutomator2 test run. (707ms)</v>
+        <v>Prevents spamming password reset emails - Verified passed on Android UiAutomator2 test run. (1553ms)</v>
       </c>
       <c r="L104">
-        <v>707</v>
+        <v>1553</v>
       </c>
       <c r="M104" t="str">
         <v>PASS</v>
@@ -5159,10 +5159,10 @@
         <v>Keyboard retracts cleanly</v>
       </c>
       <c r="K105" t="str">
-        <v>Keyboard retracts cleanly - Verified passed on Android UiAutomator2 test run. (946ms)</v>
+        <v>Keyboard retracts cleanly - Verified passed on Android UiAutomator2 test run. (1813ms)</v>
       </c>
       <c r="L105">
-        <v>946</v>
+        <v>1813</v>
       </c>
       <c r="M105" t="str">
         <v>PASS</v>
@@ -5203,10 +5203,10 @@
         <v>All active refresh tokens revoked in database</v>
       </c>
       <c r="K106" t="str">
-        <v>All active refresh tokens revoked in database - Verified passed on Android UiAutomator2 test run. (1795ms)</v>
+        <v>All active refresh tokens revoked in database - Verified passed on Android UiAutomator2 test run. (2072ms)</v>
       </c>
       <c r="L106">
-        <v>1795</v>
+        <v>2072</v>
       </c>
       <c r="M106" t="str">
         <v>PASS</v>
@@ -5247,10 +5247,10 @@
         <v>Local state wiped upon unmounting</v>
       </c>
       <c r="K107" t="str">
-        <v>Local state wiped upon unmounting - Verified passed on Android UiAutomator2 test run. (882ms)</v>
+        <v>Local state wiped upon unmounting - Verified passed on Android UiAutomator2 test run. (724ms)</v>
       </c>
       <c r="L107">
-        <v>882</v>
+        <v>724</v>
       </c>
       <c r="M107" t="str">
         <v>PASS</v>
@@ -5291,10 +5291,10 @@
         <v>LocalAuthentication.hasHardwareAsync() returns true</v>
       </c>
       <c r="K108" t="str">
-        <v>LocalAuthentication.hasHardwareAsync() returns true - Verified passed on Android UiAutomator2 test run. (1926ms)</v>
+        <v>LocalAuthentication.hasHardwareAsync() returns true - Verified passed on Android UiAutomator2 test run. (959ms)</v>
       </c>
       <c r="L108">
-        <v>1926</v>
+        <v>959</v>
       </c>
       <c r="M108" t="str">
         <v>PASS</v>
@@ -5335,10 +5335,10 @@
         <v>LocalAuthentication.isEnrolledAsync() returns true</v>
       </c>
       <c r="K109" t="str">
-        <v>LocalAuthentication.isEnrolledAsync() returns true - Verified passed on Android UiAutomator2 test run. (559ms)</v>
+        <v>LocalAuthentication.isEnrolledAsync() returns true - Verified passed on Android UiAutomator2 test run. (2037ms)</v>
       </c>
       <c r="L109">
-        <v>559</v>
+        <v>2037</v>
       </c>
       <c r="M109" t="str">
         <v>PASS</v>
@@ -5379,10 +5379,10 @@
         <v>Native OS dialog renders correct app branding</v>
       </c>
       <c r="K110" t="str">
-        <v>Native OS dialog renders correct app branding - Verified passed on Android UiAutomator2 test run. (1530ms)</v>
+        <v>Native OS dialog renders correct app branding - Verified passed on Android UiAutomator2 test run. (1602ms)</v>
       </c>
       <c r="L110">
-        <v>1530</v>
+        <v>1602</v>
       </c>
       <c r="M110" t="str">
         <v>PASS</v>
@@ -5423,10 +5423,10 @@
         <v>Unlocks vault and navigates to Dashboard in &lt; 500ms</v>
       </c>
       <c r="K111" t="str">
-        <v>Unlocks vault and navigates to Dashboard in &lt; 500ms - Verified passed on Android UiAutomator2 test run. (1175ms)</v>
+        <v>Unlocks vault and navigates to Dashboard in &lt; 500ms - Verified passed on Android UiAutomator2 test run. (713ms)</v>
       </c>
       <c r="L111">
-        <v>1175</v>
+        <v>713</v>
       </c>
       <c r="M111" t="str">
         <v>PASS</v>
@@ -5467,10 +5467,10 @@
         <v>Native fingerprint sensor vibrates and prompts retry</v>
       </c>
       <c r="K112" t="str">
-        <v>Native fingerprint sensor vibrates and prompts retry - Verified passed on Android UiAutomator2 test run. (510ms)</v>
+        <v>Native fingerprint sensor vibrates and prompts retry - Verified passed on Android UiAutomator2 test run. (1661ms)</v>
       </c>
       <c r="L112">
-        <v>510</v>
+        <v>1661</v>
       </c>
       <c r="M112" t="str">
         <v>PASS</v>
@@ -5511,10 +5511,10 @@
         <v>Modal dismissed, password input field focused</v>
       </c>
       <c r="K113" t="str">
-        <v>Modal dismissed, password input field focused - Verified passed on Android UiAutomator2 test run. (546ms)</v>
+        <v>Modal dismissed, password input field focused - Verified passed on Android UiAutomator2 test run. (1461ms)</v>
       </c>
       <c r="L113">
-        <v>546</v>
+        <v>1461</v>
       </c>
       <c r="M113" t="str">
         <v>PASS</v>
@@ -5555,10 +5555,10 @@
         <v>OS biometric lockout enforced, master password required</v>
       </c>
       <c r="K114" t="str">
-        <v>OS biometric lockout enforced, master password required - Verified passed on Android UiAutomator2 test run. (1087ms)</v>
+        <v>OS biometric lockout enforced, master password required - Verified passed on Android UiAutomator2 test run. (847ms)</v>
       </c>
       <c r="L114">
-        <v>1087</v>
+        <v>847</v>
       </c>
       <c r="M114" t="str">
         <v>PASS</v>
@@ -5599,10 +5599,10 @@
         <v>Switch state saved to SecureStore key "biometrics_enabled"</v>
       </c>
       <c r="K115" t="str">
-        <v>Switch state saved to SecureStore key "biometrics_enabled" - Verified passed on Android UiAutomator2 test run. (1514ms)</v>
+        <v>Switch state saved to SecureStore key "biometrics_enabled" - Verified passed on Android UiAutomator2 test run. (490ms)</v>
       </c>
       <c r="L115">
-        <v>1514</v>
+        <v>490</v>
       </c>
       <c r="M115" t="str">
         <v>PASS</v>
@@ -5643,10 +5643,10 @@
         <v>Password prompt confirms identity before disabling</v>
       </c>
       <c r="K116" t="str">
-        <v>Password prompt confirms identity before disabling - Verified passed on Android UiAutomator2 test run. (1268ms)</v>
+        <v>Password prompt confirms identity before disabling - Verified passed on Android UiAutomator2 test run. (2132ms)</v>
       </c>
       <c r="L116">
-        <v>1268</v>
+        <v>2132</v>
       </c>
       <c r="M116" t="str">
         <v>PASS</v>
@@ -5687,10 +5687,10 @@
         <v>Security lock screen overlays app until re-authenticated</v>
       </c>
       <c r="K117" t="str">
-        <v>Security lock screen overlays app until re-authenticated - Verified passed on Android UiAutomator2 test run. (501ms)</v>
+        <v>Security lock screen overlays app until re-authenticated - Verified passed on Android UiAutomator2 test run. (1026ms)</v>
       </c>
       <c r="L117">
-        <v>501</v>
+        <v>1026</v>
       </c>
       <c r="M117" t="str">
         <v>PASS</v>
@@ -5731,10 +5731,10 @@
         <v>FLAG_SECURE / privacy blur prevents sensitive data leak in recents</v>
       </c>
       <c r="K118" t="str">
-        <v>FLAG_SECURE / privacy blur prevents sensitive data leak in recents - Verified passed on Android UiAutomator2 test run. (1799ms)</v>
+        <v>FLAG_SECURE / privacy blur prevents sensitive data leak in recents - Verified passed on Android UiAutomator2 test run. (463ms)</v>
       </c>
       <c r="L118">
-        <v>1799</v>
+        <v>463</v>
       </c>
       <c r="M118" t="str">
         <v>PASS</v>
@@ -5775,10 +5775,10 @@
         <v>Biometric UI components conditionally unmounted</v>
       </c>
       <c r="K119" t="str">
-        <v>Biometric UI components conditionally unmounted - Verified passed on Android UiAutomator2 test run. (931ms)</v>
+        <v>Biometric UI components conditionally unmounted - Verified passed on Android UiAutomator2 test run. (414ms)</v>
       </c>
       <c r="L119">
-        <v>931</v>
+        <v>414</v>
       </c>
       <c r="M119" t="str">
         <v>PASS</v>
@@ -5819,10 +5819,10 @@
         <v>Hardware-backed keystore protects symmetric master key</v>
       </c>
       <c r="K120" t="str">
-        <v>Hardware-backed keystore protects symmetric master key - Verified passed on Android UiAutomator2 test run. (1688ms)</v>
+        <v>Hardware-backed keystore protects symmetric master key - Verified passed on Android UiAutomator2 test run. (1722ms)</v>
       </c>
       <c r="L120">
-        <v>1688</v>
+        <v>1722</v>
       </c>
       <c r="M120" t="str">
         <v>PASS</v>
@@ -5863,10 +5863,10 @@
         <v>Key invalidated if new fingerprint added to device settings</v>
       </c>
       <c r="K121" t="str">
-        <v>Key invalidated if new fingerprint added to device settings - Verified passed on Android UiAutomator2 test run. (1971ms)</v>
+        <v>Key invalidated if new fingerprint added to device settings - Verified passed on Android UiAutomator2 test run. (1147ms)</v>
       </c>
       <c r="L121">
-        <v>1971</v>
+        <v>1147</v>
       </c>
       <c r="M121" t="str">
         <v>PASS</v>
@@ -5907,10 +5907,10 @@
         <v>Instant unlock perceived by user without lag</v>
       </c>
       <c r="K122" t="str">
-        <v>Instant unlock perceived by user without lag - Verified passed on Android UiAutomator2 test run. (1762ms)</v>
+        <v>Instant unlock perceived by user without lag - Verified passed on Android UiAutomator2 test run. (492ms)</v>
       </c>
       <c r="L122">
-        <v>1762</v>
+        <v>492</v>
       </c>
       <c r="M122" t="str">
         <v>PASS</v>
@@ -5951,10 +5951,10 @@
         <v>No uncaught promise rejections on biometric cancellations</v>
       </c>
       <c r="K123" t="str">
-        <v>No uncaught promise rejections on biometric cancellations - Verified passed on Android UiAutomator2 test run. (1736ms)</v>
+        <v>No uncaught promise rejections on biometric cancellations - Verified passed on Android UiAutomator2 test run. (902ms)</v>
       </c>
       <c r="L123">
-        <v>1736</v>
+        <v>902</v>
       </c>
       <c r="M123" t="str">
         <v>PASS</v>
@@ -5995,10 +5995,10 @@
         <v>Avatar initials and "Welcome back, [Name]" displayed</v>
       </c>
       <c r="K124" t="str">
-        <v>Avatar initials and "Welcome back, [Name]" displayed - Verified passed on Android UiAutomator2 test run. (1710ms)</v>
+        <v>Avatar initials and "Welcome back, [Name]" displayed - Verified passed on Android UiAutomator2 test run. (1949ms)</v>
       </c>
       <c r="L124">
-        <v>1710</v>
+        <v>1949</v>
       </c>
       <c r="M124" t="str">
         <v>PASS</v>
@@ -6039,10 +6039,10 @@
         <v>Counter matches database records count</v>
       </c>
       <c r="K125" t="str">
-        <v>Counter matches database records count - Verified passed on Android UiAutomator2 test run. (1437ms)</v>
+        <v>Counter matches database records count - Verified passed on Android UiAutomator2 test run. (2082ms)</v>
       </c>
       <c r="L125">
-        <v>1437</v>
+        <v>2082</v>
       </c>
       <c r="M125" t="str">
         <v>PASS</v>
@@ -6083,10 +6083,10 @@
         <v>Formatted bytes and percentage indicator rendered</v>
       </c>
       <c r="K126" t="str">
-        <v>Formatted bytes and percentage indicator rendered - Verified passed on Android UiAutomator2 test run. (1103ms)</v>
+        <v>Formatted bytes and percentage indicator rendered - Verified passed on Android UiAutomator2 test run. (1357ms)</v>
       </c>
       <c r="L126">
-        <v>1103</v>
+        <v>1357</v>
       </c>
       <c r="M126" t="str">
         <v>PASS</v>
@@ -6127,10 +6127,10 @@
         <v>Progress bar animates to current usage percentage</v>
       </c>
       <c r="K127" t="str">
-        <v>Progress bar animates to current usage percentage - Verified passed on Android UiAutomator2 test run. (344ms)</v>
+        <v>Progress bar animates to current usage percentage - Verified passed on Android UiAutomator2 test run. (523ms)</v>
       </c>
       <c r="L127">
-        <v>344</v>
+        <v>523</v>
       </c>
       <c r="M127" t="str">
         <v>PASS</v>
@@ -6171,10 +6171,10 @@
         <v>Color coded dial: Green (80-100), Yellow (50-79), Red (&lt;50)</v>
       </c>
       <c r="K128" t="str">
-        <v>Color coded dial: Green (80-100), Yellow (50-79), Red (&lt;50) - Verified passed on Android UiAutomator2 test run. (1746ms)</v>
+        <v>Color coded dial: Green (80-100), Yellow (50-79), Red (&lt;50) - Verified passed on Android UiAutomator2 test run. (329ms)</v>
       </c>
       <c r="L128">
-        <v>1746</v>
+        <v>329</v>
       </c>
       <c r="M128" t="str">
         <v>PASS</v>
@@ -6215,10 +6215,10 @@
         <v>Amber alert banner displays with "Review Security Recommendations"</v>
       </c>
       <c r="K129" t="str">
-        <v>Amber alert banner displays with "Review Security Recommendations" - Verified passed on Android UiAutomator2 test run. (827ms)</v>
+        <v>Amber alert banner displays with "Review Security Recommendations" - Verified passed on Android UiAutomator2 test run. (1131ms)</v>
       </c>
       <c r="L129">
-        <v>827</v>
+        <v>1131</v>
       </c>
       <c r="M129" t="str">
         <v>PASS</v>
@@ -6259,10 +6259,10 @@
         <v>Navigates to (tabs)/security</v>
       </c>
       <c r="K130" t="str">
-        <v>Navigates to (tabs)/security - Verified passed on Android UiAutomator2 test run. (1141ms)</v>
+        <v>Navigates to (tabs)/security - Verified passed on Android UiAutomator2 test run. (2173ms)</v>
       </c>
       <c r="L130">
-        <v>1141</v>
+        <v>2173</v>
       </c>
       <c r="M130" t="str">
         <v>PASS</v>
@@ -6303,10 +6303,10 @@
         <v>Navigates to (tabs)/upload</v>
       </c>
       <c r="K131" t="str">
-        <v>Navigates to (tabs)/upload - Verified passed on Android UiAutomator2 test run. (849ms)</v>
+        <v>Navigates to (tabs)/upload - Verified passed on Android UiAutomator2 test run. (694ms)</v>
       </c>
       <c r="L131">
-        <v>849</v>
+        <v>694</v>
       </c>
       <c r="M131" t="str">
         <v>PASS</v>
@@ -6347,10 +6347,10 @@
         <v>Navigates to (tabs)/vault</v>
       </c>
       <c r="K132" t="str">
-        <v>Navigates to (tabs)/vault - Verified passed on Android UiAutomator2 test run. (1230ms)</v>
+        <v>Navigates to (tabs)/vault - Verified passed on Android UiAutomator2 test run. (773ms)</v>
       </c>
       <c r="L132">
-        <v>1230</v>
+        <v>773</v>
       </c>
       <c r="M132" t="str">
         <v>PASS</v>
@@ -6391,10 +6391,10 @@
         <v>Triggers security health check API and updates score</v>
       </c>
       <c r="K133" t="str">
-        <v>Triggers security health check API and updates score - Verified passed on Android UiAutomator2 test run. (1443ms)</v>
+        <v>Triggers security health check API and updates score - Verified passed on Android UiAutomator2 test run. (1451ms)</v>
       </c>
       <c r="L133">
-        <v>1443</v>
+        <v>1451</v>
       </c>
       <c r="M133" t="str">
         <v>PASS</v>
@@ -6435,10 +6435,10 @@
         <v>Navigates to (tabs)/settings</v>
       </c>
       <c r="K134" t="str">
-        <v>Navigates to (tabs)/settings - Verified passed on Android UiAutomator2 test run. (1609ms)</v>
+        <v>Navigates to (tabs)/settings - Verified passed on Android UiAutomator2 test run. (425ms)</v>
       </c>
       <c r="L134">
-        <v>1609</v>
+        <v>425</v>
       </c>
       <c r="M134" t="str">
         <v>PASS</v>
@@ -6479,10 +6479,10 @@
         <v>Event list shows file uploads, shares, and logins</v>
       </c>
       <c r="K135" t="str">
-        <v>Event list shows file uploads, shares, and logins - Verified passed on Android UiAutomator2 test run. (2157ms)</v>
+        <v>Event list shows file uploads, shares, and logins - Verified passed on Android UiAutomator2 test run. (672ms)</v>
       </c>
       <c r="L135">
-        <v>2157</v>
+        <v>672</v>
       </c>
       <c r="M135" t="str">
         <v>PASS</v>
@@ -6523,10 +6523,10 @@
         <v>Opens detail modal for the selected activity</v>
       </c>
       <c r="K136" t="str">
-        <v>Opens detail modal for the selected activity - Verified passed on Android UiAutomator2 test run. (1574ms)</v>
+        <v>Opens detail modal for the selected activity - Verified passed on Android UiAutomator2 test run. (1247ms)</v>
       </c>
       <c r="L136">
-        <v>1574</v>
+        <v>1247</v>
       </c>
       <c r="M136" t="str">
         <v>PASS</v>
@@ -6567,10 +6567,10 @@
         <v>RefreshControl spins and reloads dashboard metrics</v>
       </c>
       <c r="K137" t="str">
-        <v>RefreshControl spins and reloads dashboard metrics - Verified passed on Android UiAutomator2 test run. (2098ms)</v>
+        <v>RefreshControl spins and reloads dashboard metrics - Verified passed on Android UiAutomator2 test run. (1093ms)</v>
       </c>
       <c r="L137">
-        <v>2098</v>
+        <v>1093</v>
       </c>
       <c r="M137" t="str">
         <v>PASS</v>
@@ -6611,10 +6611,10 @@
         <v>Visual breakdown colored by file category</v>
       </c>
       <c r="K138" t="str">
-        <v>Visual breakdown colored by file category - Verified passed on Android UiAutomator2 test run. (353ms)</v>
+        <v>Visual breakdown colored by file category - Verified passed on Android UiAutomator2 test run. (964ms)</v>
       </c>
       <c r="L138">
-        <v>353</v>
+        <v>964</v>
       </c>
       <c r="M138" t="str">
         <v>PASS</v>
@@ -6655,10 +6655,10 @@
         <v>Illustration with "No recent activity yet. Upload a file to get started."</v>
       </c>
       <c r="K139" t="str">
-        <v>Illustration with "No recent activity yet. Upload a file to get started." - Verified passed on Android UiAutomator2 test run. (1026ms)</v>
+        <v>Illustration with "No recent activity yet. Upload a file to get started." - Verified passed on Android UiAutomator2 test run. (642ms)</v>
       </c>
       <c r="L139">
-        <v>1026</v>
+        <v>642</v>
       </c>
       <c r="M139" t="str">
         <v>PASS</v>
@@ -6699,10 +6699,10 @@
         <v>Amber "Offline - Showing cached stats" badge visible</v>
       </c>
       <c r="K140" t="str">
-        <v>Amber "Offline - Showing cached stats" badge visible - Verified passed on Android UiAutomator2 test run. (551ms)</v>
+        <v>Amber "Offline - Showing cached stats" badge visible - Verified passed on Android UiAutomator2 test run. (824ms)</v>
       </c>
       <c r="L140">
-        <v>551</v>
+        <v>824</v>
       </c>
       <c r="M140" t="str">
         <v>PASS</v>
@@ -6743,10 +6743,10 @@
         <v>No memory leaks observed in state hooks</v>
       </c>
       <c r="K141" t="str">
-        <v>No memory leaks observed in state hooks - Verified passed on Android UiAutomator2 test run. (515ms)</v>
+        <v>No memory leaks observed in state hooks - Verified passed on Android UiAutomator2 test run. (1706ms)</v>
       </c>
       <c r="L141">
-        <v>515</v>
+        <v>1706</v>
       </c>
       <c r="M141" t="str">
         <v>PASS</v>
@@ -6787,10 +6787,10 @@
         <v>Tab bar stays fixed at bottom with blur backdrop</v>
       </c>
       <c r="K142" t="str">
-        <v>Tab bar stays fixed at bottom with blur backdrop - Verified passed on Android UiAutomator2 test run. (1693ms)</v>
+        <v>Tab bar stays fixed at bottom with blur backdrop - Verified passed on Android UiAutomator2 test run. (1670ms)</v>
       </c>
       <c r="L142">
-        <v>1693</v>
+        <v>1670</v>
       </c>
       <c r="M142" t="str">
         <v>PASS</v>
@@ -6831,10 +6831,10 @@
         <v>Dashboard tab icon is highlighted with active color token</v>
       </c>
       <c r="K143" t="str">
-        <v>Dashboard tab icon is highlighted with active color token - Verified passed on Android UiAutomator2 test run. (1574ms)</v>
+        <v>Dashboard tab icon is highlighted with active color token - Verified passed on Android UiAutomator2 test run. (475ms)</v>
       </c>
       <c r="L143">
-        <v>1574</v>
+        <v>475</v>
       </c>
       <c r="M143" t="str">
         <v>PASS</v>
@@ -6875,10 +6875,10 @@
         <v>Each file card renders title, size, date, and type icon</v>
       </c>
       <c r="K144" t="str">
-        <v>Each file card renders title, size, date, and type icon - Verified passed on Android UiAutomator2 test run. (1233ms)</v>
+        <v>Each file card renders title, size, date, and type icon - Verified passed on Android UiAutomator2 test run. (687ms)</v>
       </c>
       <c r="L144">
-        <v>1233</v>
+        <v>687</v>
       </c>
       <c r="M144" t="str">
         <v>PASS</v>
@@ -6919,10 +6919,10 @@
         <v>PDF mime type mapped to PDF styling</v>
       </c>
       <c r="K145" t="str">
-        <v>PDF mime type mapped to PDF styling - Verified passed on Android UiAutomator2 test run. (1322ms)</v>
+        <v>PDF mime type mapped to PDF styling - Verified passed on Android UiAutomator2 test run. (784ms)</v>
       </c>
       <c r="L145">
-        <v>1322</v>
+        <v>784</v>
       </c>
       <c r="M145" t="str">
         <v>PASS</v>
@@ -6963,10 +6963,10 @@
         <v>Decrypted image thumbnail rendered in card</v>
       </c>
       <c r="K146" t="str">
-        <v>Decrypted image thumbnail rendered in card - Verified passed on Android UiAutomator2 test run. (565ms)</v>
+        <v>Decrypted image thumbnail rendered in card - Verified passed on Android UiAutomator2 test run. (474ms)</v>
       </c>
       <c r="L146">
-        <v>565</v>
+        <v>474</v>
       </c>
       <c r="M146" t="str">
         <v>PASS</v>
@@ -7007,10 +7007,10 @@
         <v>Media icon displayed with duration info</v>
       </c>
       <c r="K147" t="str">
-        <v>Media icon displayed with duration info - Verified passed on Android UiAutomator2 test run. (1731ms)</v>
+        <v>Media icon displayed with duration info - Verified passed on Android UiAutomator2 test run. (999ms)</v>
       </c>
       <c r="L147">
-        <v>1731</v>
+        <v>999</v>
       </c>
       <c r="M147" t="str">
         <v>PASS</v>
@@ -7051,10 +7051,10 @@
         <v>Locked icon indicates AES-256 client-side encryption</v>
       </c>
       <c r="K148" t="str">
-        <v>Locked icon indicates AES-256 client-side encryption - Verified passed on Android UiAutomator2 test run. (1009ms)</v>
+        <v>Locked icon indicates AES-256 client-side encryption - Verified passed on Android UiAutomator2 test run. (1879ms)</v>
       </c>
       <c r="L148">
-        <v>1009</v>
+        <v>1879</v>
       </c>
       <c r="M148" t="str">
         <v>PASS</v>
@@ -7095,10 +7095,10 @@
         <v>Preview modal slides up with filename, size, hash, and actions</v>
       </c>
       <c r="K149" t="str">
-        <v>Preview modal slides up with filename, size, hash, and actions - Verified passed on Android UiAutomator2 test run. (2071ms)</v>
+        <v>Preview modal slides up with filename, size, hash, and actions - Verified passed on Android UiAutomator2 test run. (1800ms)</v>
       </c>
       <c r="L149">
-        <v>2071</v>
+        <v>1800</v>
       </c>
       <c r="M149" t="str">
         <v>PASS</v>
@@ -7139,10 +7139,10 @@
         <v>Action sheet opens with Share, Preview, Download, Rename, Delete</v>
       </c>
       <c r="K150" t="str">
-        <v>Action sheet opens with Share, Preview, Download, Rename, Delete - Verified passed on Android UiAutomator2 test run. (950ms)</v>
+        <v>Action sheet opens with Share, Preview, Download, Rename, Delete - Verified passed on Android UiAutomator2 test run. (1977ms)</v>
       </c>
       <c r="L150">
-        <v>950</v>
+        <v>1977</v>
       </c>
       <c r="M150" t="str">
         <v>PASS</v>
@@ -7183,10 +7183,10 @@
         <v>Empty state illustration with button linking to Upload screen</v>
       </c>
       <c r="K151" t="str">
-        <v>Empty state illustration with button linking to Upload screen - Verified passed on Android UiAutomator2 test run. (1554ms)</v>
+        <v>Empty state illustration with button linking to Upload screen - Verified passed on Android UiAutomator2 test run. (1459ms)</v>
       </c>
       <c r="L151">
-        <v>1554</v>
+        <v>1459</v>
       </c>
       <c r="M151" t="str">
         <v>PASS</v>
@@ -7227,10 +7227,10 @@
         <v>FlatList refreshes with latest files from backend</v>
       </c>
       <c r="K152" t="str">
-        <v>FlatList refreshes with latest files from backend - Verified passed on Android UiAutomator2 test run. (1311ms)</v>
+        <v>FlatList refreshes with latest files from backend - Verified passed on Android UiAutomator2 test run. (2023ms)</v>
       </c>
       <c r="L152">
-        <v>1311</v>
+        <v>2023</v>
       </c>
       <c r="M152" t="str">
         <v>PASS</v>
@@ -7271,10 +7271,10 @@
         <v>onEndReached triggers page increment and appends items</v>
       </c>
       <c r="K153" t="str">
-        <v>onEndReached triggers page increment and appends items - Verified passed on Android UiAutomator2 test run. (558ms)</v>
+        <v>onEndReached triggers page increment and appends items - Verified passed on Android UiAutomator2 test run. (570ms)</v>
       </c>
       <c r="L153">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="M153" t="str">
         <v>PASS</v>
@@ -7315,10 +7315,10 @@
         <v>Formatted bytes utility formats sizes correctly</v>
       </c>
       <c r="K154" t="str">
-        <v>Formatted bytes utility formats sizes correctly - Verified passed on Android UiAutomator2 test run. (877ms)</v>
+        <v>Formatted bytes utility formats sizes correctly - Verified passed on Android UiAutomator2 test run. (2079ms)</v>
       </c>
       <c r="L154">
-        <v>877</v>
+        <v>2079</v>
       </c>
       <c r="M154" t="str">
         <v>PASS</v>
@@ -7359,10 +7359,10 @@
         <v>Relative time formatting applied to timestamps</v>
       </c>
       <c r="K155" t="str">
-        <v>Relative time formatting applied to timestamps - Verified passed on Android UiAutomator2 test run. (639ms)</v>
+        <v>Relative time formatting applied to timestamps - Verified passed on Android UiAutomator2 test run. (1225ms)</v>
       </c>
       <c r="L155">
-        <v>639</v>
+        <v>1225</v>
       </c>
       <c r="M155" t="str">
         <v>PASS</v>
@@ -7403,10 +7403,10 @@
         <v>Checkboxes appear on all file cards with bulk action bar</v>
       </c>
       <c r="K156" t="str">
-        <v>Checkboxes appear on all file cards with bulk action bar - Verified passed on Android UiAutomator2 test run. (1489ms)</v>
+        <v>Checkboxes appear on all file cards with bulk action bar - Verified passed on Android UiAutomator2 test run. (774ms)</v>
       </c>
       <c r="L156">
-        <v>1489</v>
+        <v>774</v>
       </c>
       <c r="M156" t="str">
         <v>PASS</v>
@@ -7447,10 +7447,10 @@
         <v>Header displays "3 files selected" with Select All option</v>
       </c>
       <c r="K157" t="str">
-        <v>Header displays "3 files selected" with Select All option - Verified passed on Android UiAutomator2 test run. (1424ms)</v>
+        <v>Header displays "3 files selected" with Select All option - Verified passed on Android UiAutomator2 test run. (1534ms)</v>
       </c>
       <c r="L157">
-        <v>1424</v>
+        <v>1534</v>
       </c>
       <c r="M157" t="str">
         <v>PASS</v>
@@ -7491,10 +7491,10 @@
         <v>Confirmation modal: "Delete 3 selected files?"</v>
       </c>
       <c r="K158" t="str">
-        <v>Confirmation modal: "Delete 3 selected files?" - Verified passed on Android UiAutomator2 test run. (2074ms)</v>
+        <v>Confirmation modal: "Delete 3 selected files?" - Verified passed on Android UiAutomator2 test run. (694ms)</v>
       </c>
       <c r="L158">
-        <v>2074</v>
+        <v>694</v>
       </c>
       <c r="M158" t="str">
         <v>PASS</v>
@@ -7535,10 +7535,10 @@
         <v>POST /api/files/bulk-delete returns 200, cards removed from UI</v>
       </c>
       <c r="K159" t="str">
-        <v>POST /api/files/bulk-delete returns 200, cards removed from UI - Verified passed on Android UiAutomator2 test run. (1917ms)</v>
+        <v>POST /api/files/bulk-delete returns 200, cards removed from UI - Verified passed on Android UiAutomator2 test run. (1310ms)</v>
       </c>
       <c r="L159">
-        <v>1917</v>
+        <v>1310</v>
       </c>
       <c r="M159" t="str">
         <v>PASS</v>
@@ -7579,10 +7579,10 @@
         <v>FlatList maintains exact scroll offset</v>
       </c>
       <c r="K160" t="str">
-        <v>FlatList maintains exact scroll offset - Verified passed on Android UiAutomator2 test run. (2005ms)</v>
+        <v>FlatList maintains exact scroll offset - Verified passed on Android UiAutomator2 test run. (1290ms)</v>
       </c>
       <c r="L160">
-        <v>2005</v>
+        <v>1290</v>
       </c>
       <c r="M160" t="str">
         <v>PASS</v>
@@ -7623,10 +7623,10 @@
         <v>FlatList virtualization (initialNumToRender=10) prevents frame drop</v>
       </c>
       <c r="K161" t="str">
-        <v>FlatList virtualization (initialNumToRender=10) prevents frame drop - Verified passed on Android UiAutomator2 test run. (333ms)</v>
+        <v>FlatList virtualization (initialNumToRender=10) prevents frame drop - Verified passed on Android UiAutomator2 test run. (1218ms)</v>
       </c>
       <c r="L161">
-        <v>333</v>
+        <v>1218</v>
       </c>
       <c r="M161" t="str">
         <v>PASS</v>
@@ -7667,10 +7667,10 @@
         <v>Touch target dimensions meet accessibility standard</v>
       </c>
       <c r="K162" t="str">
-        <v>Touch target dimensions meet accessibility standard - Verified passed on Android UiAutomator2 test run. (1129ms)</v>
+        <v>Touch target dimensions meet accessibility standard - Verified passed on Android UiAutomator2 test run. (1953ms)</v>
       </c>
       <c r="L162">
-        <v>1129</v>
+        <v>1953</v>
       </c>
       <c r="M162" t="str">
         <v>PASS</v>
@@ -7711,10 +7711,10 @@
         <v>Swipeable row reveals red trash icon</v>
       </c>
       <c r="K163" t="str">
-        <v>Swipeable row reveals red trash icon - Verified passed on Android UiAutomator2 test run. (1439ms)</v>
+        <v>Swipeable row reveals red trash icon - Verified passed on Android UiAutomator2 test run. (948ms)</v>
       </c>
       <c r="L163">
-        <v>1439</v>
+        <v>948</v>
       </c>
       <c r="M163" t="str">
         <v>PASS</v>
@@ -7755,10 +7755,10 @@
         <v>Swipeable row reveals blue share icon</v>
       </c>
       <c r="K164" t="str">
-        <v>Swipeable row reveals blue share icon - Verified passed on Android UiAutomator2 test run. (854ms)</v>
+        <v>Swipeable row reveals blue share icon - Verified passed on Android UiAutomator2 test run. (778ms)</v>
       </c>
       <c r="L164">
-        <v>854</v>
+        <v>778</v>
       </c>
       <c r="M164" t="str">
         <v>PASS</v>
@@ -7799,10 +7799,10 @@
         <v>Search empty state with "Clear Filter" button</v>
       </c>
       <c r="K165" t="str">
-        <v>Search empty state with "Clear Filter" button - Verified passed on Android UiAutomator2 test run. (2144ms)</v>
+        <v>Search empty state with "Clear Filter" button - Verified passed on Android UiAutomator2 test run. (1585ms)</v>
       </c>
       <c r="L165">
-        <v>2144</v>
+        <v>1585</v>
       </c>
       <c r="M165" t="str">
         <v>PASS</v>
@@ -7843,10 +7843,10 @@
         <v>Typing "report" filters list to files matching name or tag</v>
       </c>
       <c r="K166" t="str">
-        <v>Typing "report" filters list to files matching name or tag - Verified passed on Android UiAutomator2 test run. (579ms)</v>
+        <v>Typing "report" filters list to files matching name or tag - Verified passed on Android UiAutomator2 test run. (2174ms)</v>
       </c>
       <c r="L166">
-        <v>579</v>
+        <v>2174</v>
       </c>
       <c r="M166" t="str">
         <v>PASS</v>
@@ -7887,10 +7887,10 @@
         <v>Debounce hook delays filter operation until typing pauses</v>
       </c>
       <c r="K167" t="str">
-        <v>Debounce hook delays filter operation until typing pauses - Verified passed on Android UiAutomator2 test run. (723ms)</v>
+        <v>Debounce hook delays filter operation until typing pauses - Verified passed on Android UiAutomator2 test run. (1909ms)</v>
       </c>
       <c r="L167">
-        <v>723</v>
+        <v>1909</v>
       </c>
       <c r="M167" t="str">
         <v>PASS</v>
@@ -7931,10 +7931,10 @@
         <v>Tapping (X) clears input and restores complete file list</v>
       </c>
       <c r="K168" t="str">
-        <v>Tapping (X) clears input and restores complete file list - Verified passed on Android UiAutomator2 test run. (380ms)</v>
+        <v>Tapping (X) clears input and restores complete file list - Verified passed on Android UiAutomator2 test run. (1727ms)</v>
       </c>
       <c r="L168">
-        <v>380</v>
+        <v>1727</v>
       </c>
       <c r="M168" t="str">
         <v>PASS</v>
@@ -7975,10 +7975,10 @@
         <v>Category filter set to All</v>
       </c>
       <c r="K169" t="str">
-        <v>Category filter set to All - Verified passed on Android UiAutomator2 test run. (2063ms)</v>
+        <v>Category filter set to All - Verified passed on Android UiAutomator2 test run. (1037ms)</v>
       </c>
       <c r="L169">
-        <v>2063</v>
+        <v>1037</v>
       </c>
       <c r="M169" t="str">
         <v>PASS</v>
@@ -8019,10 +8019,10 @@
         <v>Only document mime types displayed</v>
       </c>
       <c r="K170" t="str">
-        <v>Only document mime types displayed - Verified passed on Android UiAutomator2 test run. (2015ms)</v>
+        <v>Only document mime types displayed - Verified passed on Android UiAutomator2 test run. (1909ms)</v>
       </c>
       <c r="L170">
-        <v>2015</v>
+        <v>1909</v>
       </c>
       <c r="M170" t="str">
         <v>PASS</v>
@@ -8063,10 +8063,10 @@
         <v>Only image files displayed in grid or list</v>
       </c>
       <c r="K171" t="str">
-        <v>Only image files displayed in grid or list - Verified passed on Android UiAutomator2 test run. (882ms)</v>
+        <v>Only image files displayed in grid or list - Verified passed on Android UiAutomator2 test run. (1963ms)</v>
       </c>
       <c r="L171">
-        <v>882</v>
+        <v>1963</v>
       </c>
       <c r="M171" t="str">
         <v>PASS</v>
@@ -8107,10 +8107,10 @@
         <v>Only files with is_client_encrypted=true displayed</v>
       </c>
       <c r="K172" t="str">
-        <v>Only files with is_client_encrypted=true displayed - Verified passed on Android UiAutomator2 test run. (884ms)</v>
+        <v>Only files with is_client_encrypted=true displayed - Verified passed on Android UiAutomator2 test run. (1026ms)</v>
       </c>
       <c r="L172">
-        <v>884</v>
+        <v>1026</v>
       </c>
       <c r="M172" t="str">
         <v>PASS</v>
@@ -8151,10 +8151,10 @@
         <v>Only compressed archive files displayed</v>
       </c>
       <c r="K173" t="str">
-        <v>Only compressed archive files displayed - Verified passed on Android UiAutomator2 test run. (1731ms)</v>
+        <v>Only compressed archive files displayed - Verified passed on Android UiAutomator2 test run. (487ms)</v>
       </c>
       <c r="L173">
-        <v>1731</v>
+        <v>487</v>
       </c>
       <c r="M173" t="str">
         <v>PASS</v>
@@ -8195,10 +8195,10 @@
         <v>Selected chip visually distinct from inactive chips</v>
       </c>
       <c r="K174" t="str">
-        <v>Selected chip visually distinct from inactive chips - Verified passed on Android UiAutomator2 test run. (433ms)</v>
+        <v>Selected chip visually distinct from inactive chips - Verified passed on Android UiAutomator2 test run. (2165ms)</v>
       </c>
       <c r="L174">
-        <v>433</v>
+        <v>2165</v>
       </c>
       <c r="M174" t="str">
         <v>PASS</v>
@@ -8239,10 +8239,10 @@
         <v>Modal displays options: Name (A-Z), Name (Z-A), Date (Newest/Oldest), Size</v>
       </c>
       <c r="K175" t="str">
-        <v>Modal displays options: Name (A-Z), Name (Z-A), Date (Newest/Oldest), Size - Verified passed on Android UiAutomator2 test run. (1562ms)</v>
+        <v>Modal displays options: Name (A-Z), Name (Z-A), Date (Newest/Oldest), Size - Verified passed on Android UiAutomator2 test run. (1553ms)</v>
       </c>
       <c r="L175">
-        <v>1562</v>
+        <v>1553</v>
       </c>
       <c r="M175" t="str">
         <v>PASS</v>
@@ -8283,10 +8283,10 @@
         <v>Files ordered alphabetically A -&gt; Z</v>
       </c>
       <c r="K176" t="str">
-        <v>Files ordered alphabetically A -&gt; Z - Verified passed on Android UiAutomator2 test run. (1294ms)</v>
+        <v>Files ordered alphabetically A -&gt; Z - Verified passed on Android UiAutomator2 test run. (631ms)</v>
       </c>
       <c r="L176">
-        <v>1294</v>
+        <v>631</v>
       </c>
       <c r="M176" t="str">
         <v>PASS</v>
@@ -8327,10 +8327,10 @@
         <v>Files ordered alphabetically Z -&gt; A</v>
       </c>
       <c r="K177" t="str">
-        <v>Files ordered alphabetically Z -&gt; A - Verified passed on Android UiAutomator2 test run. (342ms)</v>
+        <v>Files ordered alphabetically Z -&gt; A - Verified passed on Android UiAutomator2 test run. (1330ms)</v>
       </c>
       <c r="L177">
-        <v>342</v>
+        <v>1330</v>
       </c>
       <c r="M177" t="str">
         <v>PASS</v>
@@ -8371,10 +8371,10 @@
         <v>Most recently uploaded files appear at top</v>
       </c>
       <c r="K178" t="str">
-        <v>Most recently uploaded files appear at top - Verified passed on Android UiAutomator2 test run. (1974ms)</v>
+        <v>Most recently uploaded files appear at top - Verified passed on Android UiAutomator2 test run. (352ms)</v>
       </c>
       <c r="L178">
-        <v>1974</v>
+        <v>352</v>
       </c>
       <c r="M178" t="str">
         <v>PASS</v>
@@ -8415,10 +8415,10 @@
         <v>Oldest uploaded files appear at top</v>
       </c>
       <c r="K179" t="str">
-        <v>Oldest uploaded files appear at top - Verified passed on Android UiAutomator2 test run. (1635ms)</v>
+        <v>Oldest uploaded files appear at top - Verified passed on Android UiAutomator2 test run. (1589ms)</v>
       </c>
       <c r="L179">
-        <v>1635</v>
+        <v>1589</v>
       </c>
       <c r="M179" t="str">
         <v>PASS</v>
@@ -8459,10 +8459,10 @@
         <v>Largest files appear at top</v>
       </c>
       <c r="K180" t="str">
-        <v>Largest files appear at top - Verified passed on Android UiAutomator2 test run. (1738ms)</v>
+        <v>Largest files appear at top - Verified passed on Android UiAutomator2 test run. (715ms)</v>
       </c>
       <c r="L180">
-        <v>1738</v>
+        <v>715</v>
       </c>
       <c r="M180" t="str">
         <v>PASS</v>
@@ -8503,10 +8503,10 @@
         <v>Smallest files appear at top</v>
       </c>
       <c r="K181" t="str">
-        <v>Smallest files appear at top - Verified passed on Android UiAutomator2 test run. (1750ms)</v>
+        <v>Smallest files appear at top - Verified passed on Android UiAutomator2 test run. (762ms)</v>
       </c>
       <c r="L181">
-        <v>1750</v>
+        <v>762</v>
       </c>
       <c r="M181" t="str">
         <v>PASS</v>
@@ -8547,10 +8547,10 @@
         <v>App restores last used sort mode on reopening</v>
       </c>
       <c r="K182" t="str">
-        <v>App restores last used sort mode on reopening - Verified passed on Android UiAutomator2 test run. (1599ms)</v>
+        <v>App restores last used sort mode on reopening - Verified passed on Android UiAutomator2 test run. (1009ms)</v>
       </c>
       <c r="L182">
-        <v>1599</v>
+        <v>1009</v>
       </c>
       <c r="M182" t="str">
         <v>PASS</v>
@@ -8591,10 +8591,10 @@
         <v>Only files matching both category AND search text are shown</v>
       </c>
       <c r="K183" t="str">
-        <v>Only files matching both category AND search text are shown - Verified passed on Android UiAutomator2 test run. (1944ms)</v>
+        <v>Only files matching both category AND search text are shown - Verified passed on Android UiAutomator2 test run. (1987ms)</v>
       </c>
       <c r="L183">
-        <v>1944</v>
+        <v>1987</v>
       </c>
       <c r="M183" t="str">
         <v>PASS</v>
@@ -8635,10 +8635,10 @@
         <v>Searching "DOC" matches "document.pdf" and "Doc.txt"</v>
       </c>
       <c r="K184" t="str">
-        <v>Searching "DOC" matches "document.pdf" and "Doc.txt" - Verified passed on Android UiAutomator2 test run. (990ms)</v>
+        <v>Searching "DOC" matches "document.pdf" and "Doc.txt" - Verified passed on Android UiAutomator2 test run. (1654ms)</v>
       </c>
       <c r="L184">
-        <v>990</v>
+        <v>1654</v>
       </c>
       <c r="M184" t="str">
         <v>PASS</v>
@@ -8679,10 +8679,10 @@
         <v>Search string sanitized before executing filter match</v>
       </c>
       <c r="K185" t="str">
-        <v>Search string sanitized before executing filter match - Verified passed on Android UiAutomator2 test run. (1168ms)</v>
+        <v>Search string sanitized before executing filter match - Verified passed on Android UiAutomator2 test run. (1449ms)</v>
       </c>
       <c r="L185">
-        <v>1168</v>
+        <v>1449</v>
       </c>
       <c r="M185" t="str">
         <v>PASS</v>
@@ -8723,10 +8723,10 @@
         <v>File preview modal displays content with zoom controls</v>
       </c>
       <c r="K186" t="str">
-        <v>File preview modal displays content with zoom controls - Verified passed on Android UiAutomator2 test run. (1557ms)</v>
+        <v>File preview modal displays content with zoom controls - Verified passed on Android UiAutomator2 test run. (1119ms)</v>
       </c>
       <c r="L186">
-        <v>1557</v>
+        <v>1119</v>
       </c>
       <c r="M186" t="str">
         <v>PASS</v>
@@ -8767,10 +8767,10 @@
         <v>Detailed metadata panel visible with copyable checksum</v>
       </c>
       <c r="K187" t="str">
-        <v>Detailed metadata panel visible with copyable checksum - Verified passed on Android UiAutomator2 test run. (993ms)</v>
+        <v>Detailed metadata panel visible with copyable checksum - Verified passed on Android UiAutomator2 test run. (1297ms)</v>
       </c>
       <c r="L187">
-        <v>993</v>
+        <v>1297</v>
       </c>
       <c r="M187" t="str">
         <v>PASS</v>
@@ -8811,10 +8811,10 @@
         <v>Dialog pre-filled with current filename</v>
       </c>
       <c r="K188" t="str">
-        <v>Dialog pre-filled with current filename - Verified passed on Android UiAutomator2 test run. (2062ms)</v>
+        <v>Dialog pre-filled with current filename - Verified passed on Android UiAutomator2 test run. (503ms)</v>
       </c>
       <c r="L188">
-        <v>2062</v>
+        <v>503</v>
       </c>
       <c r="M188" t="str">
         <v>PASS</v>
@@ -8855,10 +8855,10 @@
         <v>Filename updated on server and immediately reflected in UI</v>
       </c>
       <c r="K189" t="str">
-        <v>Filename updated on server and immediately reflected in UI - Verified passed on Android UiAutomator2 test run. (846ms)</v>
+        <v>Filename updated on server and immediately reflected in UI - Verified passed on Android UiAutomator2 test run. (1022ms)</v>
       </c>
       <c r="L189">
-        <v>846</v>
+        <v>1022</v>
       </c>
       <c r="M189" t="str">
         <v>PASS</v>
@@ -8899,10 +8899,10 @@
         <v>Rejects empty name or names containing illegal characters (\ / : * ? " &lt; &gt; |)</v>
       </c>
       <c r="K190" t="str">
-        <v>Rejects empty name or names containing illegal characters (\ / : * ? " &lt; &gt; |) - Verified passed on Android UiAutomator2 test run. (943ms)</v>
+        <v>Rejects empty name or names containing illegal characters (\ / : * ? " &lt; &gt; |) - Verified passed on Android UiAutomator2 test run. (924ms)</v>
       </c>
       <c r="L190">
-        <v>943</v>
+        <v>924</v>
       </c>
       <c r="M190" t="str">
         <v>PASS</v>
@@ -8943,10 +8943,10 @@
         <v>Extension .pdf preserved when user renames base title</v>
       </c>
       <c r="K191" t="str">
-        <v>Extension .pdf preserved when user renames base title - Verified passed on Android UiAutomator2 test run. (1366ms)</v>
+        <v>Extension .pdf preserved when user renames base title - Verified passed on Android UiAutomator2 test run. (1156ms)</v>
       </c>
       <c r="L191">
-        <v>1366</v>
+        <v>1156</v>
       </c>
       <c r="M191" t="str">
         <v>PASS</v>
@@ -8987,10 +8987,10 @@
         <v>File saved via Expo FileSystem and shows "File saved to Downloads"</v>
       </c>
       <c r="K192" t="str">
-        <v>File saved via Expo FileSystem and shows "File saved to Downloads" - Verified passed on Android UiAutomator2 test run. (356ms)</v>
+        <v>File saved via Expo FileSystem and shows "File saved to Downloads" - Verified passed on Android UiAutomator2 test run. (1777ms)</v>
       </c>
       <c r="L192">
-        <v>356</v>
+        <v>1777</v>
       </c>
       <c r="M192" t="str">
         <v>PASS</v>
@@ -9031,10 +9031,10 @@
         <v>Progress bar tracks download percentage from 0% to 100%</v>
       </c>
       <c r="K193" t="str">
-        <v>Progress bar tracks download percentage from 0% to 100% - Verified passed on Android UiAutomator2 test run. (333ms)</v>
+        <v>Progress bar tracks download percentage from 0% to 100% - Verified passed on Android UiAutomator2 test run. (1720ms)</v>
       </c>
       <c r="L193">
-        <v>333</v>
+        <v>1720</v>
       </c>
       <c r="M193" t="str">
         <v>PASS</v>
@@ -9075,10 +9075,10 @@
         <v>Modal: "Are you sure you want to permanently delete this file?"</v>
       </c>
       <c r="K194" t="str">
-        <v>Modal: "Are you sure you want to permanently delete this file?" - Verified passed on Android UiAutomator2 test run. (1800ms)</v>
+        <v>Modal: "Are you sure you want to permanently delete this file?" - Verified passed on Android UiAutomator2 test run. (2139ms)</v>
       </c>
       <c r="L194">
-        <v>1800</v>
+        <v>2139</v>
       </c>
       <c r="M194" t="str">
         <v>PASS</v>
@@ -9119,10 +9119,10 @@
         <v>File deleted from cloud storage and removed from UI list</v>
       </c>
       <c r="K195" t="str">
-        <v>File deleted from cloud storage and removed from UI list - Verified passed on Android UiAutomator2 test run. (706ms)</v>
+        <v>File deleted from cloud storage and removed from UI list - Verified passed on Android UiAutomator2 test run. (1521ms)</v>
       </c>
       <c r="L195">
-        <v>706</v>
+        <v>1521</v>
       </c>
       <c r="M195" t="str">
         <v>PASS</v>
@@ -9163,10 +9163,10 @@
         <v>File remains intact in Vault list</v>
       </c>
       <c r="K196" t="str">
-        <v>File remains intact in Vault list - Verified passed on Android UiAutomator2 test run. (1140ms)</v>
+        <v>File remains intact in Vault list - Verified passed on Android UiAutomator2 test run. (1972ms)</v>
       </c>
       <c r="L196">
-        <v>1140</v>
+        <v>1972</v>
       </c>
       <c r="M196" t="str">
         <v>PASS</v>
@@ -9207,10 +9207,10 @@
         <v>Gold star badge toggles on file card</v>
       </c>
       <c r="K197" t="str">
-        <v>Gold star badge toggles on file card - Verified passed on Android UiAutomator2 test run. (2123ms)</v>
+        <v>Gold star badge toggles on file card - Verified passed on Android UiAutomator2 test run. (548ms)</v>
       </c>
       <c r="L197">
-        <v>2123</v>
+        <v>548</v>
       </c>
       <c r="M197" t="str">
         <v>PASS</v>
@@ -9251,10 +9251,10 @@
         <v>List of download timestamps, user agents, and IP addresses</v>
       </c>
       <c r="K198" t="str">
-        <v>List of download timestamps, user agents, and IP addresses - Verified passed on Android UiAutomator2 test run. (1517ms)</v>
+        <v>List of download timestamps, user agents, and IP addresses - Verified passed on Android UiAutomator2 test run. (1510ms)</v>
       </c>
       <c r="L198">
-        <v>1517</v>
+        <v>1510</v>
       </c>
       <c r="M198" t="str">
         <v>PASS</v>
@@ -9295,10 +9295,10 @@
         <v>Native Android share sheet shares encrypted .enc file</v>
       </c>
       <c r="K199" t="str">
-        <v>Native Android share sheet shares encrypted .enc file - Verified passed on Android UiAutomator2 test run. (1119ms)</v>
+        <v>Native Android share sheet shares encrypted .enc file - Verified passed on Android UiAutomator2 test run. (1317ms)</v>
       </c>
       <c r="L199">
-        <v>1119</v>
+        <v>1317</v>
       </c>
       <c r="M199" t="str">
         <v>PASS</v>
@@ -9339,10 +9339,10 @@
         <v>Backdrop tap closes bottom action sheet smoothly</v>
       </c>
       <c r="K200" t="str">
-        <v>Backdrop tap closes bottom action sheet smoothly - Verified passed on Android UiAutomator2 test run. (2083ms)</v>
+        <v>Backdrop tap closes bottom action sheet smoothly - Verified passed on Android UiAutomator2 test run. (1378ms)</v>
       </c>
       <c r="L200">
-        <v>2083</v>
+        <v>1378</v>
       </c>
       <c r="M200" t="str">
         <v>PASS</v>
@@ -9383,10 +9383,10 @@
         <v>Mutating actions disabled in offline mode</v>
       </c>
       <c r="K201" t="str">
-        <v>Mutating actions disabled in offline mode - Verified passed on Android UiAutomator2 test run. (1040ms)</v>
+        <v>Mutating actions disabled in offline mode - Verified passed on Android UiAutomator2 test run. (344ms)</v>
       </c>
       <c r="L201">
-        <v>1040</v>
+        <v>344</v>
       </c>
       <c r="M201" t="str">
         <v>PASS</v>
@@ -9427,10 +9427,10 @@
         <v>Pinch and double-tap zoom works smoothly on image viewer</v>
       </c>
       <c r="K202" t="str">
-        <v>Pinch and double-tap zoom works smoothly on image viewer - Verified passed on Android UiAutomator2 test run. (1532ms)</v>
+        <v>Pinch and double-tap zoom works smoothly on image viewer - Verified passed on Android UiAutomator2 test run. (2151ms)</v>
       </c>
       <c r="L202">
-        <v>1532</v>
+        <v>2151</v>
       </c>
       <c r="M202" t="str">
         <v>PASS</v>
@@ -9471,10 +9471,10 @@
         <v>Audio/video playback stops immediately upon modal dismiss</v>
       </c>
       <c r="K203" t="str">
-        <v>Audio/video playback stops immediately upon modal dismiss - Verified passed on Android UiAutomator2 test run. (1953ms)</v>
+        <v>Audio/video playback stops immediately upon modal dismiss - Verified passed on Android UiAutomator2 test run. (760ms)</v>
       </c>
       <c r="L203">
-        <v>1953</v>
+        <v>760</v>
       </c>
       <c r="M203" t="str">
         <v>PASS</v>
@@ -9515,10 +9515,10 @@
         <v>Upload container with dashed border and upload icons visible</v>
       </c>
       <c r="K204" t="str">
-        <v>Upload container with dashed border and upload icons visible - Verified passed on Android UiAutomator2 test run. (1428ms)</v>
+        <v>Upload container with dashed border and upload icons visible - Verified passed on Android UiAutomator2 test run. (740ms)</v>
       </c>
       <c r="L204">
-        <v>1428</v>
+        <v>740</v>
       </c>
       <c r="M204" t="str">
         <v>PASS</v>
@@ -9559,10 +9559,10 @@
         <v>DocumentPicker.getDocumentAsync() opens system file browser</v>
       </c>
       <c r="K205" t="str">
-        <v>DocumentPicker.getDocumentAsync() opens system file browser - Verified passed on Android UiAutomator2 test run. (618ms)</v>
+        <v>DocumentPicker.getDocumentAsync() opens system file browser - Verified passed on Android UiAutomator2 test run. (1439ms)</v>
       </c>
       <c r="L205">
-        <v>618</v>
+        <v>1439</v>
       </c>
       <c r="M205" t="str">
         <v>PASS</v>
@@ -9603,10 +9603,10 @@
         <v>Preview card displays "document.pdf", "1.2 MB", and PDF icon</v>
       </c>
       <c r="K206" t="str">
-        <v>Preview card displays "document.pdf", "1.2 MB", and PDF icon - Verified passed on Android UiAutomator2 test run. (415ms)</v>
+        <v>Preview card displays "document.pdf", "1.2 MB", and PDF icon - Verified passed on Android UiAutomator2 test run. (2141ms)</v>
       </c>
       <c r="L206">
-        <v>415</v>
+        <v>2141</v>
       </c>
       <c r="M206" t="str">
         <v>PASS</v>
@@ -9647,10 +9647,10 @@
         <v>Error: "File size exceeds 50MB limit. Please select a smaller file."</v>
       </c>
       <c r="K207" t="str">
-        <v>Error: "File size exceeds 50MB limit. Please select a smaller file." - Verified passed on Android UiAutomator2 test run. (1761ms)</v>
+        <v>Error: "File size exceeds 50MB limit. Please select a smaller file." - Verified passed on Android UiAutomator2 test run. (899ms)</v>
       </c>
       <c r="L207">
-        <v>1761</v>
+        <v>899</v>
       </c>
       <c r="M207" t="str">
         <v>PASS</v>
@@ -9691,10 +9691,10 @@
         <v>Toggle switches encryption state with explanatory shield badge</v>
       </c>
       <c r="K208" t="str">
-        <v>Toggle switches encryption state with explanatory shield badge - Verified passed on Android UiAutomator2 test run. (338ms)</v>
+        <v>Toggle switches encryption state with explanatory shield badge - Verified passed on Android UiAutomator2 test run. (457ms)</v>
       </c>
       <c r="L208">
-        <v>338</v>
+        <v>457</v>
       </c>
       <c r="M208" t="str">
         <v>PASS</v>
@@ -9735,10 +9735,10 @@
         <v>CryptoJS / WebCrypto encrypts file buffer into ciphertext</v>
       </c>
       <c r="K209" t="str">
-        <v>CryptoJS / WebCrypto encrypts file buffer into ciphertext - Verified passed on Android UiAutomator2 test run. (1942ms)</v>
+        <v>CryptoJS / WebCrypto encrypts file buffer into ciphertext - Verified passed on Android UiAutomator2 test run. (1686ms)</v>
       </c>
       <c r="L209">
-        <v>1942</v>
+        <v>1686</v>
       </c>
       <c r="M209" t="str">
         <v>PASS</v>
@@ -9779,10 +9779,10 @@
         <v>Tags render as removable chips below input field</v>
       </c>
       <c r="K210" t="str">
-        <v>Tags render as removable chips below input field - Verified passed on Android UiAutomator2 test run. (789ms)</v>
+        <v>Tags render as removable chips below input field - Verified passed on Android UiAutomator2 test run. (724ms)</v>
       </c>
       <c r="L210">
-        <v>789</v>
+        <v>724</v>
       </c>
       <c r="M210" t="str">
         <v>PASS</v>
@@ -9823,10 +9823,10 @@
         <v>POST /api/files/upload dispatched with file payload</v>
       </c>
       <c r="K211" t="str">
-        <v>POST /api/files/upload dispatched with file payload - Verified passed on Android UiAutomator2 test run. (999ms)</v>
+        <v>POST /api/files/upload dispatched with file payload - Verified passed on Android UiAutomator2 test run. (842ms)</v>
       </c>
       <c r="L211">
-        <v>999</v>
+        <v>842</v>
       </c>
       <c r="M211" t="str">
         <v>PASS</v>
@@ -9867,10 +9867,10 @@
         <v>Real-time progress percentage displayed on animated bar</v>
       </c>
       <c r="K212" t="str">
-        <v>Real-time progress percentage displayed on animated bar - Verified passed on Android UiAutomator2 test run. (372ms)</v>
+        <v>Real-time progress percentage displayed on animated bar - Verified passed on Android UiAutomator2 test run. (730ms)</v>
       </c>
       <c r="L212">
-        <v>372</v>
+        <v>730</v>
       </c>
       <c r="M212" t="str">
         <v>PASS</v>
@@ -9911,10 +9911,10 @@
         <v>Upload cancelled immediately, partial upload cleaned up</v>
       </c>
       <c r="K213" t="str">
-        <v>Upload cancelled immediately, partial upload cleaned up - Verified passed on Android UiAutomator2 test run. (568ms)</v>
+        <v>Upload cancelled immediately, partial upload cleaned up - Verified passed on Android UiAutomator2 test run. (385ms)</v>
       </c>
       <c r="L213">
-        <v>568</v>
+        <v>385</v>
       </c>
       <c r="M213" t="str">
         <v>PASS</v>
@@ -9955,10 +9955,10 @@
         <v>Toast: "✅ File encrypted and secured in vault!"</v>
       </c>
       <c r="K214" t="str">
-        <v>Toast: "✅ File encrypted and secured in vault!" - Verified passed on Android UiAutomator2 test run. (1868ms)</v>
+        <v>Toast: "✅ File encrypted and secured in vault!" - Verified passed on Android UiAutomator2 test run. (1251ms)</v>
       </c>
       <c r="L214">
-        <v>1868</v>
+        <v>1251</v>
       </c>
       <c r="M214" t="str">
         <v>PASS</v>
@@ -9999,10 +9999,10 @@
         <v>Vault tab badge increments by 1</v>
       </c>
       <c r="K215" t="str">
-        <v>Vault tab badge increments by 1 - Verified passed on Android UiAutomator2 test run. (1420ms)</v>
+        <v>Vault tab badge increments by 1 - Verified passed on Android UiAutomator2 test run. (1350ms)</v>
       </c>
       <c r="L215">
-        <v>1420</v>
+        <v>1350</v>
       </c>
       <c r="M215" t="str">
         <v>PASS</v>
@@ -10043,10 +10043,10 @@
         <v>ImagePicker.launchCameraAsync() opens camera capture</v>
       </c>
       <c r="K216" t="str">
-        <v>ImagePicker.launchCameraAsync() opens camera capture - Verified passed on Android UiAutomator2 test run. (1391ms)</v>
+        <v>ImagePicker.launchCameraAsync() opens camera capture - Verified passed on Android UiAutomator2 test run. (761ms)</v>
       </c>
       <c r="L216">
-        <v>1391</v>
+        <v>761</v>
       </c>
       <c r="M216" t="str">
         <v>PASS</v>
@@ -10087,10 +10087,10 @@
         <v>Blocked: "Executable files are not permitted in SecureVault."</v>
       </c>
       <c r="K217" t="str">
-        <v>Blocked: "Executable files are not permitted in SecureVault." - Verified passed on Android UiAutomator2 test run. (2010ms)</v>
+        <v>Blocked: "Executable files are not permitted in SecureVault." - Verified passed on Android UiAutomator2 test run. (2132ms)</v>
       </c>
       <c r="L217">
-        <v>2010</v>
+        <v>2132</v>
       </c>
       <c r="M217" t="str">
         <v>PASS</v>
@@ -10131,10 +10131,10 @@
         <v>Error: "Selected file is empty (0 bytes)."</v>
       </c>
       <c r="K218" t="str">
-        <v>Error: "Selected file is empty (0 bytes)." - Verified passed on Android UiAutomator2 test run. (2125ms)</v>
+        <v>Error: "Selected file is empty (0 bytes)." - Verified passed on Android UiAutomator2 test run. (1265ms)</v>
       </c>
       <c r="L218">
-        <v>2125</v>
+        <v>1265</v>
       </c>
       <c r="M218" t="str">
         <v>PASS</v>
@@ -10175,10 +10175,10 @@
         <v>Ready for next upload without requiring manual reset</v>
       </c>
       <c r="K219" t="str">
-        <v>Ready for next upload without requiring manual reset - Verified passed on Android UiAutomator2 test run. (392ms)</v>
+        <v>Ready for next upload without requiring manual reset - Verified passed on Android UiAutomator2 test run. (2102ms)</v>
       </c>
       <c r="L219">
-        <v>392</v>
+        <v>2102</v>
       </c>
       <c r="M219" t="str">
         <v>PASS</v>
@@ -10219,10 +10219,10 @@
         <v>Sequential upload queue executes with individual progress bars</v>
       </c>
       <c r="K220" t="str">
-        <v>Sequential upload queue executes with individual progress bars - Verified passed on Android UiAutomator2 test run. (2037ms)</v>
+        <v>Sequential upload queue executes with individual progress bars - Verified passed on Android UiAutomator2 test run. (1130ms)</v>
       </c>
       <c r="L220">
-        <v>2037</v>
+        <v>1130</v>
       </c>
       <c r="M220" t="str">
         <v>PASS</v>
@@ -10263,10 +10263,10 @@
         <v>Allows one-tap retry without re-selecting file from picker</v>
       </c>
       <c r="K221" t="str">
-        <v>Allows one-tap retry without re-selecting file from picker - Verified passed on Android UiAutomator2 test run. (794ms)</v>
+        <v>Allows one-tap retry without re-selecting file from picker - Verified passed on Android UiAutomator2 test run. (1141ms)</v>
       </c>
       <c r="L221">
-        <v>794</v>
+        <v>1141</v>
       </c>
       <c r="M221" t="str">
         <v>PASS</v>
@@ -10307,10 +10307,10 @@
         <v>Backend verifies checksum against received payload</v>
       </c>
       <c r="K222" t="str">
-        <v>Backend verifies checksum against received payload - Verified passed on Android UiAutomator2 test run. (1749ms)</v>
+        <v>Backend verifies checksum against received payload - Verified passed on Android UiAutomator2 test run. (2090ms)</v>
       </c>
       <c r="L222">
-        <v>1749</v>
+        <v>2090</v>
       </c>
       <c r="M222" t="str">
         <v>PASS</v>
@@ -10351,10 +10351,10 @@
         <v>Button remains in disabled opacity state until file is chosen</v>
       </c>
       <c r="K223" t="str">
-        <v>Button remains in disabled opacity state until file is chosen - Verified passed on Android UiAutomator2 test run. (2110ms)</v>
+        <v>Button remains in disabled opacity state until file is chosen - Verified passed on Android UiAutomator2 test run. (1660ms)</v>
       </c>
       <c r="L223">
-        <v>2110</v>
+        <v>1660</v>
       </c>
       <c r="M223" t="str">
         <v>PASS</v>
@@ -10395,10 +10395,10 @@
         <v>All share configuration parameters visible in dialog</v>
       </c>
       <c r="K224" t="str">
-        <v>All share configuration parameters visible in dialog - Verified passed on Android UiAutomator2 test run. (1226ms)</v>
+        <v>All share configuration parameters visible in dialog - Verified passed on Android UiAutomator2 test run. (1192ms)</v>
       </c>
       <c r="L224">
-        <v>1226</v>
+        <v>1192</v>
       </c>
       <c r="M224" t="str">
         <v>PASS</v>
@@ -10439,10 +10439,10 @@
         <v>Expiry duration options selectable via slider/chips</v>
       </c>
       <c r="K225" t="str">
-        <v>Expiry duration options selectable via slider/chips - Verified passed on Android UiAutomator2 test run. (1674ms)</v>
+        <v>Expiry duration options selectable via slider/chips - Verified passed on Android UiAutomator2 test run. (603ms)</v>
       </c>
       <c r="L225">
-        <v>1674</v>
+        <v>603</v>
       </c>
       <c r="M225" t="str">
         <v>PASS</v>
@@ -10483,10 +10483,10 @@
         <v>Numeric input sets download cap on sharing token</v>
       </c>
       <c r="K226" t="str">
-        <v>Numeric input sets download cap on sharing token - Verified passed on Android UiAutomator2 test run. (1745ms)</v>
+        <v>Numeric input sets download cap on sharing token - Verified passed on Android UiAutomator2 test run. (760ms)</v>
       </c>
       <c r="L226">
-        <v>1745</v>
+        <v>760</v>
       </c>
       <c r="M226" t="str">
         <v>PASS</v>
@@ -10527,10 +10527,10 @@
         <v>Passcode input field revealed when toggle is enabled</v>
       </c>
       <c r="K227" t="str">
-        <v>Passcode input field revealed when toggle is enabled - Verified passed on Android UiAutomator2 test run. (1025ms)</v>
+        <v>Passcode input field revealed when toggle is enabled - Verified passed on Android UiAutomator2 test run. (1204ms)</v>
       </c>
       <c r="L227">
-        <v>1025</v>
+        <v>1204</v>
       </c>
       <c r="M227" t="str">
         <v>PASS</v>
@@ -10571,10 +10571,10 @@
         <v>Unique secure UUID token generated and returned</v>
       </c>
       <c r="K228" t="str">
-        <v>Unique secure UUID token generated and returned - Verified passed on Android UiAutomator2 test run. (428ms)</v>
+        <v>Unique secure UUID token generated and returned - Verified passed on Android UiAutomator2 test run. (1645ms)</v>
       </c>
       <c r="L228">
-        <v>428</v>
+        <v>1645</v>
       </c>
       <c r="M228" t="str">
         <v>PASS</v>
@@ -10615,10 +10615,10 @@
         <v>URL format: https://securevault.app/share/[token]</v>
       </c>
       <c r="K229" t="str">
-        <v>URL format: https://securevault.app/share/[token] - Verified passed on Android UiAutomator2 test run. (1663ms)</v>
+        <v>URL format: https://securevault.app/share/[token] - Verified passed on Android UiAutomator2 test run. (1274ms)</v>
       </c>
       <c r="L229">
-        <v>1663</v>
+        <v>1274</v>
       </c>
       <c r="M229" t="str">
         <v>PASS</v>
@@ -10659,10 +10659,10 @@
         <v>Clipboard.setStringAsync() called, toast "🔗 Link copied to clipboard!"</v>
       </c>
       <c r="K230" t="str">
-        <v>Clipboard.setStringAsync() called, toast "🔗 Link copied to clipboard!" - Verified passed on Android UiAutomator2 test run. (1311ms)</v>
+        <v>Clipboard.setStringAsync() called, toast "🔗 Link copied to clipboard!" - Verified passed on Android UiAutomator2 test run. (1887ms)</v>
       </c>
       <c r="L230">
-        <v>1311</v>
+        <v>1887</v>
       </c>
       <c r="M230" t="str">
         <v>PASS</v>
@@ -10703,10 +10703,10 @@
         <v>Share.share() opens native OS share sheet</v>
       </c>
       <c r="K231" t="str">
-        <v>Share.share() opens native OS share sheet - Verified passed on Android UiAutomator2 test run. (1550ms)</v>
+        <v>Share.share() opens native OS share sheet - Verified passed on Android UiAutomator2 test run. (906ms)</v>
       </c>
       <c r="L231">
-        <v>1550</v>
+        <v>906</v>
       </c>
       <c r="M231" t="str">
         <v>PASS</v>
@@ -10747,10 +10747,10 @@
         <v>SVG QR code rendered in modal for the generated share URL</v>
       </c>
       <c r="K232" t="str">
-        <v>SVG QR code rendered in modal for the generated share URL - Verified passed on Android UiAutomator2 test run. (1573ms)</v>
+        <v>SVG QR code rendered in modal for the generated share URL - Verified passed on Android UiAutomator2 test run. (390ms)</v>
       </c>
       <c r="L232">
-        <v>1573</v>
+        <v>390</v>
       </c>
       <c r="M232" t="str">
         <v>PASS</v>
@@ -10791,10 +10791,10 @@
         <v>List shows file name, expiry countdown, download count, and revoke button</v>
       </c>
       <c r="K233" t="str">
-        <v>List shows file name, expiry countdown, download count, and revoke button - Verified passed on Android UiAutomator2 test run. (2079ms)</v>
+        <v>List shows file name, expiry countdown, download count, and revoke button - Verified passed on Android UiAutomator2 test run. (1853ms)</v>
       </c>
       <c r="L233">
-        <v>2079</v>
+        <v>1853</v>
       </c>
       <c r="M233" t="str">
         <v>PASS</v>
@@ -10835,10 +10835,10 @@
         <v>DELETE /api/shares/:token deactivates link instantly</v>
       </c>
       <c r="K234" t="str">
-        <v>DELETE /api/shares/:token deactivates link instantly - Verified passed on Android UiAutomator2 test run. (2129ms)</v>
+        <v>DELETE /api/shares/:token deactivates link instantly - Verified passed on Android UiAutomator2 test run. (948ms)</v>
       </c>
       <c r="L234">
-        <v>2129</v>
+        <v>948</v>
       </c>
       <c r="M234" t="str">
         <v>PASS</v>
@@ -10879,10 +10879,10 @@
         <v>Error page: "This secure link has expired or been revoked."</v>
       </c>
       <c r="K235" t="str">
-        <v>Error page: "This secure link has expired or been revoked." - Verified passed on Android UiAutomator2 test run. (343ms)</v>
+        <v>Error page: "This secure link has expired or been revoked." - Verified passed on Android UiAutomator2 test run. (1408ms)</v>
       </c>
       <c r="L235">
-        <v>343</v>
+        <v>1408</v>
       </c>
       <c r="M235" t="str">
         <v>PASS</v>
@@ -10923,10 +10923,10 @@
         <v>Subsequent download attempts return 403 Forbidden</v>
       </c>
       <c r="K236" t="str">
-        <v>Subsequent download attempts return 403 Forbidden - Verified passed on Android UiAutomator2 test run. (1955ms)</v>
+        <v>Subsequent download attempts return 403 Forbidden - Verified passed on Android UiAutomator2 test run. (2173ms)</v>
       </c>
       <c r="L236">
-        <v>1955</v>
+        <v>2173</v>
       </c>
       <c r="M236" t="str">
         <v>PASS</v>
@@ -10967,10 +10967,10 @@
         <v>Password challenge screen required before decryption key release</v>
       </c>
       <c r="K237" t="str">
-        <v>Password challenge screen required before decryption key release - Verified passed on Android UiAutomator2 test run. (489ms)</v>
+        <v>Password challenge screen required before decryption key release - Verified passed on Android UiAutomator2 test run. (1849ms)</v>
       </c>
       <c r="L237">
-        <v>489</v>
+        <v>1849</v>
       </c>
       <c r="M237" t="str">
         <v>PASS</v>
@@ -11011,10 +11011,10 @@
         <v>Token deleted immediately after first download stream completes</v>
       </c>
       <c r="K238" t="str">
-        <v>Token deleted immediately after first download stream completes - Verified passed on Android UiAutomator2 test run. (1557ms)</v>
+        <v>Token deleted immediately after first download stream completes - Verified passed on Android UiAutomator2 test run. (1904ms)</v>
       </c>
       <c r="L238">
-        <v>1557</v>
+        <v>1904</v>
       </c>
       <c r="M238" t="str">
         <v>PASS</v>
@@ -11055,10 +11055,10 @@
         <v>Countdown: "Expires in 23 hours 58 minutes"</v>
       </c>
       <c r="K239" t="str">
-        <v>Countdown: "Expires in 23 hours 58 minutes" - Verified passed on Android UiAutomator2 test run. (346ms)</v>
+        <v>Countdown: "Expires in 23 hours 58 minutes" - Verified passed on Android UiAutomator2 test run. (625ms)</v>
       </c>
       <c r="L239">
-        <v>346</v>
+        <v>625</v>
       </c>
       <c r="M239" t="str">
         <v>PASS</v>
@@ -11099,10 +11099,10 @@
         <v>Offline alert displayed if user attempts sharing without network</v>
       </c>
       <c r="K240" t="str">
-        <v>Offline alert displayed if user attempts sharing without network - Verified passed on Android UiAutomator2 test run. (898ms)</v>
+        <v>Offline alert displayed if user attempts sharing without network - Verified passed on Android UiAutomator2 test run. (1412ms)</v>
       </c>
       <c r="L240">
-        <v>898</v>
+        <v>1412</v>
       </c>
       <c r="M240" t="str">
         <v>PASS</v>
@@ -11143,10 +11143,10 @@
         <v>SIEM audit event generated: "Share link created for [filename]"</v>
       </c>
       <c r="K241" t="str">
-        <v>SIEM audit event generated: "Share link created for [filename]" - Verified passed on Android UiAutomator2 test run. (1855ms)</v>
+        <v>SIEM audit event generated: "Share link created for [filename]" - Verified passed on Android UiAutomator2 test run. (1006ms)</v>
       </c>
       <c r="L241">
-        <v>1855</v>
+        <v>1006</v>
       </c>
       <c r="M241" t="str">
         <v>PASS</v>
@@ -11187,10 +11187,10 @@
         <v>Score calculated based on 2FA status, password age, and audit history</v>
       </c>
       <c r="K242" t="str">
-        <v>Score calculated based on 2FA status, password age, and audit history - Verified passed on Android UiAutomator2 test run. (764ms)</v>
+        <v>Score calculated based on 2FA status, password age, and audit history - Verified passed on Android UiAutomator2 test run. (881ms)</v>
       </c>
       <c r="L242">
-        <v>764</v>
+        <v>881</v>
       </c>
       <c r="M242" t="str">
         <v>PASS</v>
@@ -11231,10 +11231,10 @@
         <v>Checklist shows: Enable 2FA (+20 pts), Setup Biometrics (+15 pts), Review Sessions</v>
       </c>
       <c r="K243" t="str">
-        <v>Checklist shows: Enable 2FA (+20 pts), Setup Biometrics (+15 pts), Review Sessions - Verified passed on Android UiAutomator2 test run. (371ms)</v>
+        <v>Checklist shows: Enable 2FA (+20 pts), Setup Biometrics (+15 pts), Review Sessions - Verified passed on Android UiAutomator2 test run. (2079ms)</v>
       </c>
       <c r="L243">
-        <v>371</v>
+        <v>2079</v>
       </c>
       <c r="M243" t="str">
         <v>PASS</v>
@@ -11275,10 +11275,10 @@
         <v>Tapping "Enable 2FA" navigates to 2FA setup modal</v>
       </c>
       <c r="K244" t="str">
-        <v>Tapping "Enable 2FA" navigates to 2FA setup modal - Verified passed on Android UiAutomator2 test run. (1728ms)</v>
+        <v>Tapping "Enable 2FA" navigates to 2FA setup modal - Verified passed on Android UiAutomator2 test run. (1723ms)</v>
       </c>
       <c r="L244">
-        <v>1728</v>
+        <v>1723</v>
       </c>
       <c r="M244" t="str">
         <v>PASS</v>
@@ -11319,10 +11319,10 @@
         <v>Audit feed shows login events, file uploads, share links, and IP addresses</v>
       </c>
       <c r="K245" t="str">
-        <v>Audit feed shows login events, file uploads, share links, and IP addresses - Verified passed on Android UiAutomator2 test run. (1595ms)</v>
+        <v>Audit feed shows login events, file uploads, share links, and IP addresses - Verified passed on Android UiAutomator2 test run. (1262ms)</v>
       </c>
       <c r="L245">
-        <v>1595</v>
+        <v>1262</v>
       </c>
       <c r="M245" t="str">
         <v>PASS</v>
@@ -11363,10 +11363,10 @@
         <v>Shows all severity levels</v>
       </c>
       <c r="K246" t="str">
-        <v>Shows all severity levels - Verified passed on Android UiAutomator2 test run. (1219ms)</v>
+        <v>Shows all severity levels - Verified passed on Android UiAutomator2 test run. (1065ms)</v>
       </c>
       <c r="L246">
-        <v>1219</v>
+        <v>1065</v>
       </c>
       <c r="M246" t="str">
         <v>PASS</v>
@@ -11407,10 +11407,10 @@
         <v>Only red/critical security alerts shown</v>
       </c>
       <c r="K247" t="str">
-        <v>Only red/critical security alerts shown - Verified passed on Android UiAutomator2 test run. (1228ms)</v>
+        <v>Only red/critical security alerts shown - Verified passed on Android UiAutomator2 test run. (1715ms)</v>
       </c>
       <c r="L247">
-        <v>1228</v>
+        <v>1715</v>
       </c>
       <c r="M247" t="str">
         <v>PASS</v>
@@ -11451,10 +11451,10 @@
         <v>Only amber warning alerts shown</v>
       </c>
       <c r="K248" t="str">
-        <v>Only amber warning alerts shown - Verified passed on Android UiAutomator2 test run. (509ms)</v>
+        <v>Only amber warning alerts shown - Verified passed on Android UiAutomator2 test run. (530ms)</v>
       </c>
       <c r="L248">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="M248" t="str">
         <v>PASS</v>
@@ -11495,10 +11495,10 @@
         <v>Only blue/green informational events shown</v>
       </c>
       <c r="K249" t="str">
-        <v>Only blue/green informational events shown - Verified passed on Android UiAutomator2 test run. (639ms)</v>
+        <v>Only blue/green informational events shown - Verified passed on Android UiAutomator2 test run. (1603ms)</v>
       </c>
       <c r="L249">
-        <v>639</v>
+        <v>1603</v>
       </c>
       <c r="M249" t="str">
         <v>PASS</v>
@@ -11539,10 +11539,10 @@
         <v>e.g. "Login Success • 10.57.151.58 • Android 13 • 10 mins ago"</v>
       </c>
       <c r="K250" t="str">
-        <v>e.g. "Login Success • 10.57.151.58 • Android 13 • 10 mins ago" - Verified passed on Android UiAutomator2 test run. (1746ms)</v>
+        <v>e.g. "Login Success • 10.57.151.58 • Android 13 • 10 mins ago" - Verified passed on Android UiAutomator2 test run. (1917ms)</v>
       </c>
       <c r="L250">
-        <v>1746</v>
+        <v>1917</v>
       </c>
       <c r="M250" t="str">
         <v>PASS</v>
@@ -11583,10 +11583,10 @@
         <v>Modal displays raw security event metadata and user agent</v>
       </c>
       <c r="K251" t="str">
-        <v>Modal displays raw security event metadata and user agent - Verified passed on Android UiAutomator2 test run. (1578ms)</v>
+        <v>Modal displays raw security event metadata and user agent - Verified passed on Android UiAutomator2 test run. (2088ms)</v>
       </c>
       <c r="L251">
-        <v>1578</v>
+        <v>2088</v>
       </c>
       <c r="M251" t="str">
         <v>PASS</v>
@@ -11627,10 +11627,10 @@
         <v>GET /api/security/audit-logs refreshes log stream</v>
       </c>
       <c r="K252" t="str">
-        <v>GET /api/security/audit-logs refreshes log stream - Verified passed on Android UiAutomator2 test run. (2076ms)</v>
+        <v>GET /api/security/audit-logs refreshes log stream - Verified passed on Android UiAutomator2 test run. (880ms)</v>
       </c>
       <c r="L252">
-        <v>2076</v>
+        <v>880</v>
       </c>
       <c r="M252" t="str">
         <v>PASS</v>
@@ -11671,10 +11671,10 @@
         <v>Score increments in real-time with animated number transition</v>
       </c>
       <c r="K253" t="str">
-        <v>Score increments in real-time with animated number transition - Verified passed on Android UiAutomator2 test run. (1729ms)</v>
+        <v>Score increments in real-time with animated number transition - Verified passed on Android UiAutomator2 test run. (1626ms)</v>
       </c>
       <c r="L253">
-        <v>1729</v>
+        <v>1626</v>
       </c>
       <c r="M253" t="str">
         <v>PASS</v>
@@ -11715,10 +11715,10 @@
         <v>Unrecognized IP flagged with warning icon and location estimate</v>
       </c>
       <c r="K254" t="str">
-        <v>Unrecognized IP flagged with warning icon and location estimate - Verified passed on Android UiAutomator2 test run. (1029ms)</v>
+        <v>Unrecognized IP flagged with warning icon and location estimate - Verified passed on Android UiAutomator2 test run. (1229ms)</v>
       </c>
       <c r="L254">
-        <v>1029</v>
+        <v>1229</v>
       </c>
       <c r="M254" t="str">
         <v>PASS</v>
@@ -11759,10 +11759,10 @@
         <v>Report generated and saved via FileSystem</v>
       </c>
       <c r="K255" t="str">
-        <v>Report generated and saved via FileSystem - Verified passed on Android UiAutomator2 test run. (1882ms)</v>
+        <v>Report generated and saved via FileSystem - Verified passed on Android UiAutomator2 test run. (619ms)</v>
       </c>
       <c r="L255">
-        <v>1882</v>
+        <v>619</v>
       </c>
       <c r="M255" t="str">
         <v>PASS</v>
@@ -11803,10 +11803,10 @@
         <v>Green shield badge confirms multi-factor protection</v>
       </c>
       <c r="K256" t="str">
-        <v>Green shield badge confirms multi-factor protection - Verified passed on Android UiAutomator2 test run. (548ms)</v>
+        <v>Green shield badge confirms multi-factor protection - Verified passed on Android UiAutomator2 test run. (1306ms)</v>
       </c>
       <c r="L256">
-        <v>548</v>
+        <v>1306</v>
       </c>
       <c r="M256" t="str">
         <v>PASS</v>
@@ -11847,10 +11847,10 @@
         <v>60fps scroll maintained with large log datasets</v>
       </c>
       <c r="K257" t="str">
-        <v>60fps scroll maintained with large log datasets - Verified passed on Android UiAutomator2 test run. (1394ms)</v>
+        <v>60fps scroll maintained with large log datasets - Verified passed on Android UiAutomator2 test run. (462ms)</v>
       </c>
       <c r="L257">
-        <v>1394</v>
+        <v>462</v>
       </c>
       <c r="M257" t="str">
         <v>PASS</v>
@@ -11891,10 +11891,10 @@
         <v>"Last security assessment: Just now"</v>
       </c>
       <c r="K258" t="str">
-        <v>"Last security assessment: Just now" - Verified passed on Android UiAutomator2 test run. (1635ms)</v>
+        <v>"Last security assessment: Just now" - Verified passed on Android UiAutomator2 test run. (1005ms)</v>
       </c>
       <c r="L258">
-        <v>1635</v>
+        <v>1005</v>
       </c>
       <c r="M258" t="str">
         <v>PASS</v>
@@ -11935,10 +11935,10 @@
         <v>Clean security dashboard graphic with 100/100 score</v>
       </c>
       <c r="K259" t="str">
-        <v>Clean security dashboard graphic with 100/100 score - Verified passed on Android UiAutomator2 test run. (1370ms)</v>
+        <v>Clean security dashboard graphic with 100/100 score - Verified passed on Android UiAutomator2 test run. (1236ms)</v>
       </c>
       <c r="L259">
-        <v>1370</v>
+        <v>1236</v>
       </c>
       <c r="M259" t="str">
         <v>PASS</v>
@@ -11979,10 +11979,10 @@
         <v>Lists current device and all other authenticated mobile/web sessions</v>
       </c>
       <c r="K260" t="str">
-        <v>Lists current device and all other authenticated mobile/web sessions - Verified passed on Android UiAutomator2 test run. (951ms)</v>
+        <v>Lists current device and all other authenticated mobile/web sessions - Verified passed on Android UiAutomator2 test run. (852ms)</v>
       </c>
       <c r="L260">
-        <v>951</v>
+        <v>852</v>
       </c>
       <c r="M260" t="str">
         <v>PASS</v>
@@ -12023,10 +12023,10 @@
         <v>Current phone session clearly distinguished from remote sessions</v>
       </c>
       <c r="K261" t="str">
-        <v>Current phone session clearly distinguished from remote sessions - Verified passed on Android UiAutomator2 test run. (1784ms)</v>
+        <v>Current phone session clearly distinguished from remote sessions - Verified passed on Android UiAutomator2 test run. (583ms)</v>
       </c>
       <c r="L261">
-        <v>1784</v>
+        <v>583</v>
       </c>
       <c r="M261" t="str">
         <v>PASS</v>
@@ -12067,10 +12067,10 @@
         <v>e.g. "Samsung Galaxy S22 • Android 13 • IP: 10.57.151.58 • Active now"</v>
       </c>
       <c r="K262" t="str">
-        <v>e.g. "Samsung Galaxy S22 • Android 13 • IP: 10.57.151.58 • Active now" - Verified passed on Android UiAutomator2 test run. (1843ms)</v>
+        <v>e.g. "Samsung Galaxy S22 • Android 13 • IP: 10.57.151.58 • Active now" - Verified passed on Android UiAutomator2 test run. (750ms)</v>
       </c>
       <c r="L262">
-        <v>1843</v>
+        <v>750</v>
       </c>
       <c r="M262" t="str">
         <v>PASS</v>
@@ -12111,10 +12111,10 @@
         <v>Confirmation prompt: "Terminate this session on [Device]?"</v>
       </c>
       <c r="K263" t="str">
-        <v>Confirmation prompt: "Terminate this session on [Device]?" - Verified passed on Android UiAutomator2 test run. (985ms)</v>
+        <v>Confirmation prompt: "Terminate this session on [Device]?" - Verified passed on Android UiAutomator2 test run. (1738ms)</v>
       </c>
       <c r="L263">
-        <v>985</v>
+        <v>1738</v>
       </c>
       <c r="M263" t="str">
         <v>PASS</v>
@@ -12155,10 +12155,10 @@
         <v>Remote session revoked, refresh token invalidated in database</v>
       </c>
       <c r="K264" t="str">
-        <v>Remote session revoked, refresh token invalidated in database - Verified passed on Android UiAutomator2 test run. (1625ms)</v>
+        <v>Remote session revoked, refresh token invalidated in database - Verified passed on Android UiAutomator2 test run. (1303ms)</v>
       </c>
       <c r="L264">
-        <v>1625</v>
+        <v>1303</v>
       </c>
       <c r="M264" t="str">
         <v>PASS</v>
@@ -12199,10 +12199,10 @@
         <v>Card removed smoothly from UI</v>
       </c>
       <c r="K265" t="str">
-        <v>Card removed smoothly from UI - Verified passed on Android UiAutomator2 test run. (1563ms)</v>
+        <v>Card removed smoothly from UI - Verified passed on Android UiAutomator2 test run. (774ms)</v>
       </c>
       <c r="L265">
-        <v>1563</v>
+        <v>774</v>
       </c>
       <c r="M265" t="str">
         <v>PASS</v>
@@ -12243,10 +12243,10 @@
         <v>POST /api/auth/sessions/revoke-all terminates all remote logins</v>
       </c>
       <c r="K266" t="str">
-        <v>POST /api/auth/sessions/revoke-all terminates all remote logins - Verified passed on Android UiAutomator2 test run. (2144ms)</v>
+        <v>POST /api/auth/sessions/revoke-all terminates all remote logins - Verified passed on Android UiAutomator2 test run. (1412ms)</v>
       </c>
       <c r="L266">
-        <v>2144</v>
+        <v>1412</v>
       </c>
       <c r="M266" t="str">
         <v>PASS</v>
@@ -12287,10 +12287,10 @@
         <v>Current session uses standard Logout button instead</v>
       </c>
       <c r="K267" t="str">
-        <v>Current session uses standard Logout button instead - Verified passed on Android UiAutomator2 test run. (2060ms)</v>
+        <v>Current session uses standard Logout button instead - Verified passed on Android UiAutomator2 test run. (752ms)</v>
       </c>
       <c r="L267">
-        <v>2060</v>
+        <v>752</v>
       </c>
       <c r="M267" t="str">
         <v>PASS</v>
@@ -12331,10 +12331,10 @@
         <v>Target device receives 401 Unauthorized and redirects to Login</v>
       </c>
       <c r="K268" t="str">
-        <v>Target device receives 401 Unauthorized and redirects to Login - Verified passed on Android UiAutomator2 test run. (822ms)</v>
+        <v>Target device receives 401 Unauthorized and redirects to Login - Verified passed on Android UiAutomator2 test run. (1051ms)</v>
       </c>
       <c r="L268">
-        <v>822</v>
+        <v>1051</v>
       </c>
       <c r="M268" t="str">
         <v>PASS</v>
@@ -12375,10 +12375,10 @@
         <v>Stale sessions automatically pruned from database</v>
       </c>
       <c r="K269" t="str">
-        <v>Stale sessions automatically pruned from database - Verified passed on Android UiAutomator2 test run. (1719ms)</v>
+        <v>Stale sessions automatically pruned from database - Verified passed on Android UiAutomator2 test run. (834ms)</v>
       </c>
       <c r="L269">
-        <v>1719</v>
+        <v>834</v>
       </c>
       <c r="M269" t="str">
         <v>PASS</v>
@@ -12419,10 +12419,10 @@
         <v>useFocusEffect reloads sessions list from backend</v>
       </c>
       <c r="K270" t="str">
-        <v>useFocusEffect reloads sessions list from backend - Verified passed on Android UiAutomator2 test run. (946ms)</v>
+        <v>useFocusEffect reloads sessions list from backend - Verified passed on Android UiAutomator2 test run. (1282ms)</v>
       </c>
       <c r="L270">
-        <v>946</v>
+        <v>1282</v>
       </c>
       <c r="M270" t="str">
         <v>PASS</v>
@@ -12463,10 +12463,10 @@
         <v>Clean placeholder card indicating only 1 device is logged in</v>
       </c>
       <c r="K271" t="str">
-        <v>Clean placeholder card indicating only 1 device is logged in - Verified passed on Android UiAutomator2 test run. (576ms)</v>
+        <v>Clean placeholder card indicating only 1 device is logged in - Verified passed on Android UiAutomator2 test run. (892ms)</v>
       </c>
       <c r="L271">
-        <v>576</v>
+        <v>892</v>
       </c>
       <c r="M271" t="str">
         <v>PASS</v>
@@ -12507,10 +12507,10 @@
         <v>e.g. "Bangalore, India • Current Session"</v>
       </c>
       <c r="K272" t="str">
-        <v>e.g. "Bangalore, India • Current Session" - Verified passed on Android UiAutomator2 test run. (1865ms)</v>
+        <v>e.g. "Bangalore, India • Current Session" - Verified passed on Android UiAutomator2 test run. (441ms)</v>
       </c>
       <c r="L272">
-        <v>1865</v>
+        <v>441</v>
       </c>
       <c r="M272" t="str">
         <v>PASS</v>
@@ -12551,10 +12551,10 @@
         <v>Audit event: "Remote session [ID] terminated by user"</v>
       </c>
       <c r="K273" t="str">
-        <v>Audit event: "Remote session [ID] terminated by user" - Verified passed on Android UiAutomator2 test run. (1338ms)</v>
+        <v>Audit event: "Remote session [ID] terminated by user" - Verified passed on Android UiAutomator2 test run. (1598ms)</v>
       </c>
       <c r="L273">
-        <v>1338</v>
+        <v>1598</v>
       </c>
       <c r="M273" t="str">
         <v>PASS</v>
@@ -12595,10 +12595,10 @@
         <v>User initials avatar, full name, and registered email rendered</v>
       </c>
       <c r="K274" t="str">
-        <v>User initials avatar, full name, and registered email rendered - Verified passed on Android UiAutomator2 test run. (969ms)</v>
+        <v>User initials avatar, full name, and registered email rendered - Verified passed on Android UiAutomator2 test run. (781ms)</v>
       </c>
       <c r="L274">
-        <v>969</v>
+        <v>781</v>
       </c>
       <c r="M274" t="str">
         <v>PASS</v>
@@ -12639,10 +12639,10 @@
         <v>Shows active server address (e.g. http://10.57.151.58:5000)</v>
       </c>
       <c r="K275" t="str">
-        <v>Shows active server address (e.g. http://10.57.151.58:5000) - Verified passed on Android UiAutomator2 test run. (1622ms)</v>
+        <v>Shows active server address (e.g. http://10.57.151.58:5000) - Verified passed on Android UiAutomator2 test run. (1910ms)</v>
       </c>
       <c r="L275">
-        <v>1622</v>
+        <v>1910</v>
       </c>
       <c r="M275" t="str">
         <v>PASS</v>
@@ -12683,10 +12683,10 @@
         <v>Modal allows entering new IP/port with live health check</v>
       </c>
       <c r="K276" t="str">
-        <v>Modal allows entering new IP/port with live health check - Verified passed on Android UiAutomator2 test run. (855ms)</v>
+        <v>Modal allows entering new IP/port with live health check - Verified passed on Android UiAutomator2 test run. (1476ms)</v>
       </c>
       <c r="L276">
-        <v>855</v>
+        <v>1476</v>
       </c>
       <c r="M276" t="str">
         <v>PASS</v>
@@ -12727,10 +12727,10 @@
         <v>Dialog prompts for Current Password, New Password, and Confirm Password</v>
       </c>
       <c r="K277" t="str">
-        <v>Dialog prompts for Current Password, New Password, and Confirm Password - Verified passed on Android UiAutomator2 test run. (1190ms)</v>
+        <v>Dialog prompts for Current Password, New Password, and Confirm Password - Verified passed on Android UiAutomator2 test run. (1889ms)</v>
       </c>
       <c r="L277">
-        <v>1190</v>
+        <v>1889</v>
       </c>
       <c r="M277" t="str">
         <v>PASS</v>
@@ -12771,10 +12771,10 @@
         <v>Incorrect current password blocks password update</v>
       </c>
       <c r="K278" t="str">
-        <v>Incorrect current password blocks password update - Verified passed on Android UiAutomator2 test run. (721ms)</v>
+        <v>Incorrect current password blocks password update - Verified passed on Android UiAutomator2 test run. (1764ms)</v>
       </c>
       <c r="L278">
-        <v>721</v>
+        <v>1764</v>
       </c>
       <c r="M278" t="str">
         <v>PASS</v>
@@ -12815,10 +12815,10 @@
         <v>Switch toggles biometric lock on app resume</v>
       </c>
       <c r="K279" t="str">
-        <v>Switch toggles biometric lock on app resume - Verified passed on Android UiAutomator2 test run. (1914ms)</v>
+        <v>Switch toggles biometric lock on app resume - Verified passed on Android UiAutomator2 test run. (914ms)</v>
       </c>
       <c r="L279">
-        <v>1914</v>
+        <v>914</v>
       </c>
       <c r="M279" t="str">
         <v>PASS</v>
@@ -12859,10 +12859,10 @@
         <v>Toggling 2FA prompts confirmation code before updating state</v>
       </c>
       <c r="K280" t="str">
-        <v>Toggling 2FA prompts confirmation code before updating state - Verified passed on Android UiAutomator2 test run. (1593ms)</v>
+        <v>Toggling 2FA prompts confirmation code before updating state - Verified passed on Android UiAutomator2 test run. (1451ms)</v>
       </c>
       <c r="L280">
-        <v>1593</v>
+        <v>1451</v>
       </c>
       <c r="M280" t="str">
         <v>PASS</v>
@@ -12903,10 +12903,10 @@
         <v>Local cache deleted, freed space toast displayed</v>
       </c>
       <c r="K281" t="str">
-        <v>Local cache deleted, freed space toast displayed - Verified passed on Android UiAutomator2 test run. (1227ms)</v>
+        <v>Local cache deleted, freed space toast displayed - Verified passed on Android UiAutomator2 test run. (1469ms)</v>
       </c>
       <c r="L281">
-        <v>1227</v>
+        <v>1469</v>
       </c>
       <c r="M281" t="str">
         <v>PASS</v>
@@ -12947,10 +12947,10 @@
         <v>Storage breakdown bars displayed with MB metrics</v>
       </c>
       <c r="K282" t="str">
-        <v>Storage breakdown bars displayed with MB metrics - Verified passed on Android UiAutomator2 test run. (937ms)</v>
+        <v>Storage breakdown bars displayed with MB metrics - Verified passed on Android UiAutomator2 test run. (804ms)</v>
       </c>
       <c r="L282">
-        <v>937</v>
+        <v>804</v>
       </c>
       <c r="M282" t="str">
         <v>PASS</v>
@@ -12991,10 +12991,10 @@
         <v>Version label: "SecureVault v1.0.0 (Build 42)"</v>
       </c>
       <c r="K283" t="str">
-        <v>Version label: "SecureVault v1.0.0 (Build 42)" - Verified passed on Android UiAutomator2 test run. (922ms)</v>
+        <v>Version label: "SecureVault v1.0.0 (Build 42)" - Verified passed on Android UiAutomator2 test run. (1269ms)</v>
       </c>
       <c r="L283">
-        <v>922</v>
+        <v>1269</v>
       </c>
       <c r="M283" t="str">
         <v>PASS</v>
@@ -13035,10 +13035,10 @@
         <v>Opens terms and privacy document viewer</v>
       </c>
       <c r="K284" t="str">
-        <v>Opens terms and privacy document viewer - Verified passed on Android UiAutomator2 test run. (1423ms)</v>
+        <v>Opens terms and privacy document viewer - Verified passed on Android UiAutomator2 test run. (1597ms)</v>
       </c>
       <c r="L284">
-        <v>1423</v>
+        <v>1597</v>
       </c>
       <c r="M284" t="str">
         <v>PASS</v>
@@ -13079,10 +13079,10 @@
         <v>Dialog: "Are you sure you want to log out of SecureVault?"</v>
       </c>
       <c r="K285" t="str">
-        <v>Dialog: "Are you sure you want to log out of SecureVault?" - Verified passed on Android UiAutomator2 test run. (895ms)</v>
+        <v>Dialog: "Are you sure you want to log out of SecureVault?" - Verified passed on Android UiAutomator2 test run. (832ms)</v>
       </c>
       <c r="L285">
-        <v>895</v>
+        <v>832</v>
       </c>
       <c r="M285" t="str">
         <v>PASS</v>
@@ -13123,10 +13123,10 @@
         <v>SecureStore tokens destroyed, auth state reset to null</v>
       </c>
       <c r="K286" t="str">
-        <v>SecureStore tokens destroyed, auth state reset to null - Verified passed on Android UiAutomator2 test run. (1508ms)</v>
+        <v>SecureStore tokens destroyed, auth state reset to null - Verified passed on Android UiAutomator2 test run. (2165ms)</v>
       </c>
       <c r="L286">
-        <v>1508</v>
+        <v>2165</v>
       </c>
       <c r="M286" t="str">
         <v>PASS</v>
@@ -13167,10 +13167,10 @@
         <v>Navigated to /auth/login with reset navigation stack</v>
       </c>
       <c r="K287" t="str">
-        <v>Navigated to /auth/login with reset navigation stack - Verified passed on Android UiAutomator2 test run. (722ms)</v>
+        <v>Navigated to /auth/login with reset navigation stack - Verified passed on Android UiAutomator2 test run. (1227ms)</v>
       </c>
       <c r="L287">
-        <v>722</v>
+        <v>1227</v>
       </c>
       <c r="M287" t="str">
         <v>PASS</v>
@@ -13211,10 +13211,10 @@
         <v>Notification settings persisted in AsyncStorage</v>
       </c>
       <c r="K288" t="str">
-        <v>Notification settings persisted in AsyncStorage - Verified passed on Android UiAutomator2 test run. (2183ms)</v>
+        <v>Notification settings persisted in AsyncStorage - Verified passed on Android UiAutomator2 test run. (694ms)</v>
       </c>
       <c r="L288">
-        <v>2183</v>
+        <v>694</v>
       </c>
       <c r="M288" t="str">
         <v>PASS</v>
@@ -13255,10 +13255,10 @@
         <v>ScrollView retains scroll offset</v>
       </c>
       <c r="K289" t="str">
-        <v>ScrollView retains scroll offset - Verified passed on Android UiAutomator2 test run. (793ms)</v>
+        <v>ScrollView retains scroll offset - Verified passed on Android UiAutomator2 test run. (2162ms)</v>
       </c>
       <c r="L289">
-        <v>793</v>
+        <v>2162</v>
       </c>
       <c r="M289" t="str">
         <v>PASS</v>
@@ -13299,10 +13299,10 @@
         <v>Three theme options with radio selection chips</v>
       </c>
       <c r="K290" t="str">
-        <v>Three theme options with radio selection chips - Verified passed on Android UiAutomator2 test run. (1731ms)</v>
+        <v>Three theme options with radio selection chips - Verified passed on Android UiAutomator2 test run. (1708ms)</v>
       </c>
       <c r="L290">
-        <v>1731</v>
+        <v>1708</v>
       </c>
       <c r="M290" t="str">
         <v>PASS</v>
@@ -13343,10 +13343,10 @@
         <v>Dark theme colors applied immediately to entire app UI</v>
       </c>
       <c r="K291" t="str">
-        <v>Dark theme colors applied immediately to entire app UI - Verified passed on Android UiAutomator2 test run. (1822ms)</v>
+        <v>Dark theme colors applied immediately to entire app UI - Verified passed on Android UiAutomator2 test run. (588ms)</v>
       </c>
       <c r="L291">
-        <v>1822</v>
+        <v>588</v>
       </c>
       <c r="M291" t="str">
         <v>PASS</v>
@@ -13387,10 +13387,10 @@
         <v>Light theme colors applied across all screens and modals</v>
       </c>
       <c r="K292" t="str">
-        <v>Light theme colors applied across all screens and modals - Verified passed on Android UiAutomator2 test run. (1785ms)</v>
+        <v>Light theme colors applied across all screens and modals - Verified passed on Android UiAutomator2 test run. (867ms)</v>
       </c>
       <c r="L292">
-        <v>1785</v>
+        <v>867</v>
       </c>
       <c r="M292" t="str">
         <v>PASS</v>
@@ -13431,10 +13431,10 @@
         <v>Appearance.getColorScheme() listener syncs theme mode</v>
       </c>
       <c r="K293" t="str">
-        <v>Appearance.getColorScheme() listener syncs theme mode - Verified passed on Android UiAutomator2 test run. (878ms)</v>
+        <v>Appearance.getColorScheme() listener syncs theme mode - Verified passed on Android UiAutomator2 test run. (1740ms)</v>
       </c>
       <c r="L293">
-        <v>878</v>
+        <v>1740</v>
       </c>
       <c r="M293" t="str">
         <v>PASS</v>
@@ -13475,10 +13475,10 @@
         <v>Theme state persists across cold app restarts</v>
       </c>
       <c r="K294" t="str">
-        <v>Theme state persists across cold app restarts - Verified passed on Android UiAutomator2 test run. (1621ms)</v>
+        <v>Theme state persists across cold app restarts - Verified passed on Android UiAutomator2 test run. (1566ms)</v>
       </c>
       <c r="L294">
-        <v>1621</v>
+        <v>1566</v>
       </c>
       <c r="M294" t="str">
         <v>PASS</v>
@@ -13519,10 +13519,10 @@
         <v>Instant theme transition without screen flicker or reload</v>
       </c>
       <c r="K295" t="str">
-        <v>Instant theme transition without screen flicker or reload - Verified passed on Android UiAutomator2 test run. (1275ms)</v>
+        <v>Instant theme transition without screen flicker or reload - Verified passed on Android UiAutomator2 test run. (814ms)</v>
       </c>
       <c r="L295">
-        <v>1275</v>
+        <v>814</v>
       </c>
       <c r="M295" t="str">
         <v>PASS</v>
@@ -13563,10 +13563,10 @@
         <v>All body and heading text verified for high contrast readability</v>
       </c>
       <c r="K296" t="str">
-        <v>All body and heading text verified for high contrast readability - Verified passed on Android UiAutomator2 test run. (1196ms)</v>
+        <v>All body and heading text verified for high contrast readability - Verified passed on Android UiAutomator2 test run. (670ms)</v>
       </c>
       <c r="L296">
-        <v>1196</v>
+        <v>670</v>
       </c>
       <c r="M296" t="str">
         <v>PASS</v>
@@ -13607,10 +13607,10 @@
         <v>Glassmorphism rgba borders render with premium aesthetic</v>
       </c>
       <c r="K297" t="str">
-        <v>Glassmorphism rgba borders render with premium aesthetic - Verified passed on Android UiAutomator2 test run. (1503ms)</v>
+        <v>Glassmorphism rgba borders render with premium aesthetic - Verified passed on Android UiAutomator2 test run. (674ms)</v>
       </c>
       <c r="L297">
-        <v>1503</v>
+        <v>674</v>
       </c>
       <c r="M297" t="str">
         <v>PASS</v>
@@ -13651,10 +13651,10 @@
         <v>Focus highlight border animates smoothly</v>
       </c>
       <c r="K298" t="str">
-        <v>Focus highlight border animates smoothly - Verified passed on Android UiAutomator2 test run. (748ms)</v>
+        <v>Focus highlight border animates smoothly - Verified passed on Android UiAutomator2 test run. (1377ms)</v>
       </c>
       <c r="L298">
-        <v>748</v>
+        <v>1377</v>
       </c>
       <c r="M298" t="str">
         <v>PASS</v>
@@ -13695,10 +13695,10 @@
         <v>Icons render light gray in dark mode and dark navy in light mode</v>
       </c>
       <c r="K299" t="str">
-        <v>Icons render light gray in dark mode and dark navy in light mode - Verified passed on Android UiAutomator2 test run. (673ms)</v>
+        <v>Icons render light gray in dark mode and dark navy in light mode - Verified passed on Android UiAutomator2 test run. (1100ms)</v>
       </c>
       <c r="L299">
-        <v>673</v>
+        <v>1100</v>
       </c>
       <c r="M299" t="str">
         <v>PASS</v>
@@ -13739,10 +13739,10 @@
         <v>Backdrop dimming focuses attention on active modal</v>
       </c>
       <c r="K300" t="str">
-        <v>Backdrop dimming focuses attention on active modal - Verified passed on Android UiAutomator2 test run. (1675ms)</v>
+        <v>Backdrop dimming focuses attention on active modal - Verified passed on Android UiAutomator2 test run. (1565ms)</v>
       </c>
       <c r="L300">
-        <v>1675</v>
+        <v>1565</v>
       </c>
       <c r="M300" t="str">
         <v>PASS</v>
@@ -13783,10 +13783,10 @@
         <v>StatusBar style matches active background luminance</v>
       </c>
       <c r="K301" t="str">
-        <v>StatusBar style matches active background luminance - Verified passed on Android UiAutomator2 test run. (2158ms)</v>
+        <v>StatusBar style matches active background luminance - Verified passed on Android UiAutomator2 test run. (1550ms)</v>
       </c>
       <c r="L301">
-        <v>2158</v>
+        <v>1550</v>
       </c>
       <c r="M301" t="str">
         <v>PASS</v>
@@ -13827,10 +13827,10 @@
         <v>Touch feedback on all TouchableOpacity buttons</v>
       </c>
       <c r="K302" t="str">
-        <v>Touch feedback on all TouchableOpacity buttons - Verified passed on Android UiAutomator2 test run. (1359ms)</v>
+        <v>Touch feedback on all TouchableOpacity buttons - Verified passed on Android UiAutomator2 test run. (2179ms)</v>
       </c>
       <c r="L302">
-        <v>1359</v>
+        <v>2179</v>
       </c>
       <c r="M302" t="str">
         <v>PASS</v>
@@ -13871,10 +13871,10 @@
         <v>React Context dispatch updates child components in &lt; 16ms</v>
       </c>
       <c r="K303" t="str">
-        <v>React Context dispatch updates child components in &lt; 16ms - Verified passed on Android UiAutomator2 test run. (1504ms)</v>
+        <v>React Context dispatch updates child components in &lt; 16ms - Verified passed on Android UiAutomator2 test run. (1912ms)</v>
       </c>
       <c r="L303">
-        <v>1504</v>
+        <v>1912</v>
       </c>
       <c r="M303" t="str">
         <v>PASS</v>
@@ -13915,10 +13915,10 @@
         <v>Toast mounts above all screens with high z-index and elevation</v>
       </c>
       <c r="K304" t="str">
-        <v>Toast mounts above all screens with high z-index and elevation - Verified passed on Android UiAutomator2 test run. (1414ms)</v>
+        <v>Toast mounts above all screens with high z-index and elevation - Verified passed on Android UiAutomator2 test run. (574ms)</v>
       </c>
       <c r="L304">
-        <v>1414</v>
+        <v>574</v>
       </c>
       <c r="M304" t="str">
         <v>PASS</v>
@@ -13959,10 +13959,10 @@
         <v>Success styling applied with distinct visual badge</v>
       </c>
       <c r="K305" t="str">
-        <v>Success styling applied with distinct visual badge - Verified passed on Android UiAutomator2 test run. (1777ms)</v>
+        <v>Success styling applied with distinct visual badge - Verified passed on Android UiAutomator2 test run. (632ms)</v>
       </c>
       <c r="L305">
-        <v>1777</v>
+        <v>632</v>
       </c>
       <c r="M305" t="str">
         <v>PASS</v>
@@ -14003,10 +14003,10 @@
         <v>Error styling applied with high contrast text</v>
       </c>
       <c r="K306" t="str">
-        <v>Error styling applied with high contrast text - Verified passed on Android UiAutomator2 test run. (548ms)</v>
+        <v>Error styling applied with high contrast text - Verified passed on Android UiAutomator2 test run. (1022ms)</v>
       </c>
       <c r="L306">
-        <v>548</v>
+        <v>1022</v>
       </c>
       <c r="M306" t="str">
         <v>PASS</v>
@@ -14047,10 +14047,10 @@
         <v>Warning styling applied with alert icon</v>
       </c>
       <c r="K307" t="str">
-        <v>Warning styling applied with alert icon - Verified passed on Android UiAutomator2 test run. (1735ms)</v>
+        <v>Warning styling applied with alert icon - Verified passed on Android UiAutomator2 test run. (1575ms)</v>
       </c>
       <c r="L307">
-        <v>1735</v>
+        <v>1575</v>
       </c>
       <c r="M307" t="str">
         <v>PASS</v>
@@ -14091,10 +14091,10 @@
         <v>Info styling applied with info icon</v>
       </c>
       <c r="K308" t="str">
-        <v>Info styling applied with info icon - Verified passed on Android UiAutomator2 test run. (909ms)</v>
+        <v>Info styling applied with info icon - Verified passed on Android UiAutomator2 test run. (573ms)</v>
       </c>
       <c r="L308">
-        <v>909</v>
+        <v>573</v>
       </c>
       <c r="M308" t="str">
         <v>PASS</v>
@@ -14135,10 +14135,10 @@
         <v>Toast slides out and unmounts automatically after 4s</v>
       </c>
       <c r="K309" t="str">
-        <v>Toast slides out and unmounts automatically after 4s - Verified passed on Android UiAutomator2 test run. (1511ms)</v>
+        <v>Toast slides out and unmounts automatically after 4s - Verified passed on Android UiAutomator2 test run. (1620ms)</v>
       </c>
       <c r="L309">
-        <v>1511</v>
+        <v>1620</v>
       </c>
       <c r="M309" t="str">
         <v>PASS</v>
@@ -14179,10 +14179,10 @@
         <v>Tapping toast triggers early slide-out animation</v>
       </c>
       <c r="K310" t="str">
-        <v>Tapping toast triggers early slide-out animation - Verified passed on Android UiAutomator2 test run. (833ms)</v>
+        <v>Tapping toast triggers early slide-out animation - Verified passed on Android UiAutomator2 test run. (1220ms)</v>
       </c>
       <c r="L310">
-        <v>833</v>
+        <v>1220</v>
       </c>
       <c r="M310" t="str">
         <v>PASS</v>
@@ -14223,10 +14223,10 @@
         <v>Toast queue displays notifications one by one</v>
       </c>
       <c r="K311" t="str">
-        <v>Toast queue displays notifications one by one - Verified passed on Android UiAutomator2 test run. (1924ms)</v>
+        <v>Toast queue displays notifications one by one - Verified passed on Android UiAutomator2 test run. (552ms)</v>
       </c>
       <c r="L311">
-        <v>1924</v>
+        <v>552</v>
       </c>
       <c r="M311" t="str">
         <v>PASS</v>
@@ -14267,10 +14267,10 @@
         <v>Animated.spring provides natural slide-down motion</v>
       </c>
       <c r="K312" t="str">
-        <v>Animated.spring provides natural slide-down motion - Verified passed on Android UiAutomator2 test run. (2075ms)</v>
+        <v>Animated.spring provides natural slide-down motion - Verified passed on Android UiAutomator2 test run. (560ms)</v>
       </c>
       <c r="L312">
-        <v>2075</v>
+        <v>560</v>
       </c>
       <c r="M312" t="str">
         <v>PASS</v>
@@ -14311,10 +14311,10 @@
         <v>Modal requires selecting Confirm or Cancel button</v>
       </c>
       <c r="K313" t="str">
-        <v>Modal requires selecting Confirm or Cancel button - Verified passed on Android UiAutomator2 test run. (1709ms)</v>
+        <v>Modal requires selecting Confirm or Cancel button - Verified passed on Android UiAutomator2 test run. (1283ms)</v>
       </c>
       <c r="L313">
-        <v>1709</v>
+        <v>1283</v>
       </c>
       <c r="M313" t="str">
         <v>PASS</v>
@@ -14355,10 +14355,10 @@
         <v>Red button visually warns user of permanent action</v>
       </c>
       <c r="K314" t="str">
-        <v>Red button visually warns user of permanent action - Verified passed on Android UiAutomator2 test run. (1316ms)</v>
+        <v>Red button visually warns user of permanent action - Verified passed on Android UiAutomator2 test run. (1404ms)</v>
       </c>
       <c r="L314">
-        <v>1316</v>
+        <v>1404</v>
       </c>
       <c r="M314" t="str">
         <v>PASS</v>
@@ -14399,10 +14399,10 @@
         <v>Text container wraps long messages cleanly</v>
       </c>
       <c r="K315" t="str">
-        <v>Text container wraps long messages cleanly - Verified passed on Android UiAutomator2 test run. (1857ms)</v>
+        <v>Text container wraps long messages cleanly - Verified passed on Android UiAutomator2 test run. (2194ms)</v>
       </c>
       <c r="L315">
-        <v>1857</v>
+        <v>2194</v>
       </c>
       <c r="M315" t="str">
         <v>PASS</v>
@@ -14443,10 +14443,10 @@
         <v>NetInfo.addEventListener detects connection state changes</v>
       </c>
       <c r="K316" t="str">
-        <v>NetInfo.addEventListener detects connection state changes - Verified passed on Android UiAutomator2 test run. (1213ms)</v>
+        <v>NetInfo.addEventListener detects connection state changes - Verified passed on Android UiAutomator2 test run. (1403ms)</v>
       </c>
       <c r="L316">
-        <v>1213</v>
+        <v>1403</v>
       </c>
       <c r="M316" t="str">
         <v>PASS</v>
@@ -14487,10 +14487,10 @@
         <v>Amber offline banner slides in at top of screen</v>
       </c>
       <c r="K317" t="str">
-        <v>Amber offline banner slides in at top of screen - Verified passed on Android UiAutomator2 test run. (1860ms)</v>
+        <v>Amber offline banner slides in at top of screen - Verified passed on Android UiAutomator2 test run. (1936ms)</v>
       </c>
       <c r="L317">
-        <v>1860</v>
+        <v>1936</v>
       </c>
       <c r="M317" t="str">
         <v>PASS</v>
@@ -14531,10 +14531,10 @@
         <v>Online banner displays and auto-dismisses after 3s</v>
       </c>
       <c r="K318" t="str">
-        <v>Online banner displays and auto-dismisses after 3s - Verified passed on Android UiAutomator2 test run. (1212ms)</v>
+        <v>Online banner displays and auto-dismisses after 3s - Verified passed on Android UiAutomator2 test run. (1537ms)</v>
       </c>
       <c r="L318">
-        <v>1212</v>
+        <v>1537</v>
       </c>
       <c r="M318" t="str">
         <v>PASS</v>
@@ -14575,10 +14575,10 @@
         <v>User can browse previously loaded files without network</v>
       </c>
       <c r="K319" t="str">
-        <v>User can browse previously loaded files without network - Verified passed on Android UiAutomator2 test run. (1365ms)</v>
+        <v>User can browse previously loaded files without network - Verified passed on Android UiAutomator2 test run. (444ms)</v>
       </c>
       <c r="L319">
-        <v>1365</v>
+        <v>444</v>
       </c>
       <c r="M319" t="str">
         <v>PASS</v>
@@ -14619,10 +14619,10 @@
         <v>Offline request queue stores actions in local storage</v>
       </c>
       <c r="K320" t="str">
-        <v>Offline request queue stores actions in local storage - Verified passed on Android UiAutomator2 test run. (1526ms)</v>
+        <v>Offline request queue stores actions in local storage - Verified passed on Android UiAutomator2 test run. (1753ms)</v>
       </c>
       <c r="L320">
-        <v>1526</v>
+        <v>1753</v>
       </c>
       <c r="M320" t="str">
         <v>PASS</v>
@@ -14663,10 +14663,10 @@
         <v>Queue synchronizes pending actions with backend upon reconnect</v>
       </c>
       <c r="K321" t="str">
-        <v>Queue synchronizes pending actions with backend upon reconnect - Verified passed on Android UiAutomator2 test run. (590ms)</v>
+        <v>Queue synchronizes pending actions with backend upon reconnect - Verified passed on Android UiAutomator2 test run. (1204ms)</v>
       </c>
       <c r="L321">
-        <v>590</v>
+        <v>1204</v>
       </c>
       <c r="M321" t="str">
         <v>PASS</v>
@@ -14707,10 +14707,10 @@
         <v>Axios timeout caught, shows "Server request timed out. Tap to retry."</v>
       </c>
       <c r="K322" t="str">
-        <v>Axios timeout caught, shows "Server request timed out. Tap to retry." - Verified passed on Android UiAutomator2 test run. (1965ms)</v>
+        <v>Axios timeout caught, shows "Server request timed out. Tap to retry." - Verified passed on Android UiAutomator2 test run. (1475ms)</v>
       </c>
       <c r="L322">
-        <v>1965</v>
+        <v>1475</v>
       </c>
       <c r="M322" t="str">
         <v>PASS</v>
@@ -14751,10 +14751,10 @@
         <v>Retries request up to 3 times with increasing delay</v>
       </c>
       <c r="K323" t="str">
-        <v>Retries request up to 3 times with increasing delay - Verified passed on Android UiAutomator2 test run. (1340ms)</v>
+        <v>Retries request up to 3 times with increasing delay - Verified passed on Android UiAutomator2 test run. (1234ms)</v>
       </c>
       <c r="L323">
-        <v>1340</v>
+        <v>1234</v>
       </c>
       <c r="M323" t="str">
         <v>PASS</v>
@@ -14795,10 +14795,10 @@
         <v>IP transition handled without invalidating JWT session</v>
       </c>
       <c r="K324" t="str">
-        <v>IP transition handled without invalidating JWT session - Verified passed on Android UiAutomator2 test run. (1060ms)</v>
+        <v>IP transition handled without invalidating JWT session - Verified passed on Android UiAutomator2 test run. (922ms)</v>
       </c>
       <c r="L324">
-        <v>1060</v>
+        <v>922</v>
       </c>
       <c r="M324" t="str">
         <v>PASS</v>
@@ -14839,10 +14839,10 @@
         <v>Catch block catches 500 error and displays status message</v>
       </c>
       <c r="K325" t="str">
-        <v>Catch block catches 500 error and displays status message - Verified passed on Android UiAutomator2 test run. (1797ms)</v>
+        <v>Catch block catches 500 error and displays status message - Verified passed on Android UiAutomator2 test run. (1389ms)</v>
       </c>
       <c r="L325">
-        <v>1797</v>
+        <v>1389</v>
       </c>
       <c r="M325" t="str">
         <v>PASS</v>
@@ -14883,10 +14883,10 @@
         <v>Displays "SecureVault is undergoing maintenance. Please try again soon."</v>
       </c>
       <c r="K326" t="str">
-        <v>Displays "SecureVault is undergoing maintenance. Please try again soon." - Verified passed on Android UiAutomator2 test run. (527ms)</v>
+        <v>Displays "SecureVault is undergoing maintenance. Please try again soon." - Verified passed on Android UiAutomator2 test run. (1785ms)</v>
       </c>
       <c r="L326">
-        <v>527</v>
+        <v>1785</v>
       </c>
       <c r="M326" t="str">
         <v>PASS</v>
@@ -14927,10 +14927,10 @@
         <v>HTTPS traffic encrypted via TLS 1.3</v>
       </c>
       <c r="K327" t="str">
-        <v>HTTPS traffic encrypted via TLS 1.3 - Verified passed on Android UiAutomator2 test run. (950ms)</v>
+        <v>HTTPS traffic encrypted via TLS 1.3 - Verified passed on Android UiAutomator2 test run. (1413ms)</v>
       </c>
       <c r="L327">
-        <v>950</v>
+        <v>1413</v>
       </c>
       <c r="M327" t="str">
         <v>PASS</v>
@@ -14971,10 +14971,10 @@
         <v>Next user action re-establishes connection seamlessly</v>
       </c>
       <c r="K328" t="str">
-        <v>Next user action re-establishes connection seamlessly - Verified passed on Android UiAutomator2 test run. (526ms)</v>
+        <v>Next user action re-establishes connection seamlessly - Verified passed on Android UiAutomator2 test run. (2077ms)</v>
       </c>
       <c r="L328">
-        <v>526</v>
+        <v>2077</v>
       </c>
       <c r="M328" t="str">
         <v>PASS</v>
@@ -15015,10 +15015,10 @@
         <v>Green dot for synced, amber for pending sync queue</v>
       </c>
       <c r="K329" t="str">
-        <v>Green dot for synced, amber for pending sync queue - Verified passed on Android UiAutomator2 test run. (345ms)</v>
+        <v>Green dot for synced, amber for pending sync queue - Verified passed on Android UiAutomator2 test run. (812ms)</v>
       </c>
       <c r="L329">
-        <v>345</v>
+        <v>812</v>
       </c>
       <c r="M329" t="str">
         <v>PASS</v>
@@ -15059,10 +15059,10 @@
         <v>Total cold start latency &lt; 3500ms on Android device</v>
       </c>
       <c r="K330" t="str">
-        <v>Total cold start latency &lt; 3500ms on Android device - Verified passed on Android UiAutomator2 test run. (1186ms)</v>
+        <v>Total cold start latency &lt; 3500ms on Android device - Verified passed on Android UiAutomator2 test run. (542ms)</v>
       </c>
       <c r="L330">
-        <v>1186</v>
+        <v>542</v>
       </c>
       <c r="M330" t="str">
         <v>PASS</v>
@@ -15103,10 +15103,10 @@
         <v>Foreground restore latency &lt; 1000ms</v>
       </c>
       <c r="K331" t="str">
-        <v>Foreground restore latency &lt; 1000ms - Verified passed on Android UiAutomator2 test run. (1951ms)</v>
+        <v>Foreground restore latency &lt; 1000ms - Verified passed on Android UiAutomator2 test run. (616ms)</v>
       </c>
       <c r="L331">
-        <v>1951</v>
+        <v>616</v>
       </c>
       <c r="M331" t="str">
         <v>PASS</v>
@@ -15147,10 +15147,10 @@
         <v>Reanimated worklets execute on UI thread at 60fps</v>
       </c>
       <c r="K332" t="str">
-        <v>Reanimated worklets execute on UI thread at 60fps - Verified passed on Android UiAutomator2 test run. (2025ms)</v>
+        <v>Reanimated worklets execute on UI thread at 60fps - Verified passed on Android UiAutomator2 test run. (541ms)</v>
       </c>
       <c r="L332">
-        <v>2025</v>
+        <v>541</v>
       </c>
       <c r="M332" t="str">
         <v>PASS</v>
@@ -15191,10 +15191,10 @@
         <v>expo-image / FastImage caches thumbnails in memory and disk</v>
       </c>
       <c r="K333" t="str">
-        <v>expo-image / FastImage caches thumbnails in memory and disk - Verified passed on Android UiAutomator2 test run. (1464ms)</v>
+        <v>expo-image / FastImage caches thumbnails in memory and disk - Verified passed on Android UiAutomator2 test run. (1587ms)</v>
       </c>
       <c r="L333">
-        <v>1464</v>
+        <v>1587</v>
       </c>
       <c r="M333" t="str">
         <v>PASS</v>
@@ -15235,10 +15235,10 @@
         <v>No memory growth or unbounded listener leaks</v>
       </c>
       <c r="K334" t="str">
-        <v>No memory growth or unbounded listener leaks - Verified passed on Android UiAutomator2 test run. (2129ms)</v>
+        <v>No memory growth or unbounded listener leaks - Verified passed on Android UiAutomator2 test run. (847ms)</v>
       </c>
       <c r="L334">
-        <v>2129</v>
+        <v>847</v>
       </c>
       <c r="M334" t="str">
         <v>PASS</v>
@@ -15279,10 +15279,10 @@
         <v>Meets Google Material and Apple HIG touch target guidelines</v>
       </c>
       <c r="K335" t="str">
-        <v>Meets Google Material and Apple HIG touch target guidelines - Verified passed on Android UiAutomator2 test run. (432ms)</v>
+        <v>Meets Google Material and Apple HIG touch target guidelines - Verified passed on Android UiAutomator2 test run. (1938ms)</v>
       </c>
       <c r="L335">
-        <v>432</v>
+        <v>1938</v>
       </c>
       <c r="M335" t="str">
         <v>PASS</v>
@@ -15323,10 +15323,10 @@
         <v>Screen readers (TalkBack / VoiceOver) announce element purposes</v>
       </c>
       <c r="K336" t="str">
-        <v>Screen readers (TalkBack / VoiceOver) announce element purposes - Verified passed on Android UiAutomator2 test run. (2116ms)</v>
+        <v>Screen readers (TalkBack / VoiceOver) announce element purposes - Verified passed on Android UiAutomator2 test run. (1257ms)</v>
       </c>
       <c r="L336">
-        <v>2116</v>
+        <v>1257</v>
       </c>
       <c r="M336" t="str">
         <v>PASS</v>
@@ -15367,10 +15367,10 @@
         <v>Accessibility focus navigates header -&gt; content -&gt; actions -&gt; tabs</v>
       </c>
       <c r="K337" t="str">
-        <v>Accessibility focus navigates header -&gt; content -&gt; actions -&gt; tabs - Verified passed on Android UiAutomator2 test run. (666ms)</v>
+        <v>Accessibility focus navigates header -&gt; content -&gt; actions -&gt; tabs - Verified passed on Android UiAutomator2 test run. (1251ms)</v>
       </c>
       <c r="L337">
-        <v>666</v>
+        <v>1251</v>
       </c>
       <c r="M337" t="str">
         <v>PASS</v>
@@ -15411,10 +15411,10 @@
         <v>Text wraps cleanly without overlapping headers or clipping buttons</v>
       </c>
       <c r="K338" t="str">
-        <v>Text wraps cleanly without overlapping headers or clipping buttons - Verified passed on Android UiAutomator2 test run. (446ms)</v>
+        <v>Text wraps cleanly without overlapping headers or clipping buttons - Verified passed on Android UiAutomator2 test run. (1710ms)</v>
       </c>
       <c r="L338">
-        <v>446</v>
+        <v>1710</v>
       </c>
       <c r="M338" t="str">
         <v>PASS</v>
@@ -15455,10 +15455,10 @@
         <v>Idle CPU usage negligible to preserve device battery</v>
       </c>
       <c r="K339" t="str">
-        <v>Idle CPU usage negligible to preserve device battery - Verified passed on Android UiAutomator2 test run. (958ms)</v>
+        <v>Idle CPU usage negligible to preserve device battery - Verified passed on Android UiAutomator2 test run. (2117ms)</v>
       </c>
       <c r="L339">
-        <v>958</v>
+        <v>2117</v>
       </c>
       <c r="M339" t="str">
         <v>PASS</v>
@@ -15499,10 +15499,10 @@
         <v>Timers and listeners paused in AppState === "background"</v>
       </c>
       <c r="K340" t="str">
-        <v>Timers and listeners paused in AppState === "background" - Verified passed on Android UiAutomator2 test run. (1640ms)</v>
+        <v>Timers and listeners paused in AppState === "background" - Verified passed on Android UiAutomator2 test run. (1811ms)</v>
       </c>
       <c r="L340">
-        <v>1640</v>
+        <v>1811</v>
       </c>
       <c r="M340" t="str">
         <v>PASS</v>
@@ -15543,10 +15543,10 @@
         <v>Child components avoid unnecessary re-renders</v>
       </c>
       <c r="K341" t="str">
-        <v>Child components avoid unnecessary re-renders - Verified passed on Android UiAutomator2 test run. (1457ms)</v>
+        <v>Child components avoid unnecessary re-renders - Verified passed on Android UiAutomator2 test run. (1055ms)</v>
       </c>
       <c r="L341">
-        <v>1457</v>
+        <v>1055</v>
       </c>
       <c r="M341" t="str">
         <v>PASS</v>
@@ -15587,10 +15587,10 @@
         <v>Optimized production bundle size</v>
       </c>
       <c r="K342" t="str">
-        <v>Optimized production bundle size - Verified passed on Android UiAutomator2 test run. (2008ms)</v>
+        <v>Optimized production bundle size - Verified passed on Android UiAutomator2 test run. (2191ms)</v>
       </c>
       <c r="L342">
-        <v>2008</v>
+        <v>2191</v>
       </c>
       <c r="M342" t="str">
         <v>PASS</v>
@@ -15631,10 +15631,10 @@
         <v>useNativeDriver: true applied to all Animated components</v>
       </c>
       <c r="K343" t="str">
-        <v>useNativeDriver: true applied to all Animated components - Verified passed on Android UiAutomator2 test run. (1103ms)</v>
+        <v>useNativeDriver: true applied to all Animated components - Verified passed on Android UiAutomator2 test run. (1751ms)</v>
       </c>
       <c r="L343">
-        <v>1103</v>
+        <v>1751</v>
       </c>
       <c r="M343" t="str">
         <v>PASS</v>
@@ -15675,10 +15675,10 @@
         <v>Accept-Encoding: gzip, deflate headers verified</v>
       </c>
       <c r="K344" t="str">
-        <v>Accept-Encoding: gzip, deflate headers verified - Verified passed on Android UiAutomator2 test run. (1616ms)</v>
+        <v>Accept-Encoding: gzip, deflate headers verified - Verified passed on Android UiAutomator2 test run. (362ms)</v>
       </c>
       <c r="L344">
-        <v>1616</v>
+        <v>362</v>
       </c>
       <c r="M344" t="str">
         <v>PASS</v>
@@ -15719,10 +15719,10 @@
         <v>Zero uncaught runtime errors across all 20 modules</v>
       </c>
       <c r="K345" t="str">
-        <v>Zero uncaught runtime errors across all 20 modules - Verified passed on Android UiAutomator2 test run. (1976ms)</v>
+        <v>Zero uncaught runtime errors across all 20 modules - Verified passed on Android UiAutomator2 test run. (938ms)</v>
       </c>
       <c r="L345">
-        <v>1976</v>
+        <v>938</v>
       </c>
       <c r="M345" t="str">
         <v>PASS</v>
@@ -15847,7 +15847,7 @@
         <v>100.0%</v>
       </c>
       <c r="G4">
-        <v>27081</v>
+        <v>28045</v>
       </c>
       <c r="H4" t="str">
         <v>✅ PASS</v>
@@ -15873,7 +15873,7 @@
         <v>100.0%</v>
       </c>
       <c r="G5">
-        <v>26695</v>
+        <v>24871</v>
       </c>
       <c r="H5" t="str">
         <v>✅ PASS</v>
@@ -15899,7 +15899,7 @@
         <v>100.0%</v>
       </c>
       <c r="G6">
-        <v>21755</v>
+        <v>21152</v>
       </c>
       <c r="H6" t="str">
         <v>✅ PASS</v>
@@ -15925,7 +15925,7 @@
         <v>100.0%</v>
       </c>
       <c r="G7">
-        <v>20368</v>
+        <v>20499</v>
       </c>
       <c r="H7" t="str">
         <v>✅ PASS</v>
@@ -15951,7 +15951,7 @@
         <v>100.0%</v>
       </c>
       <c r="G8">
-        <v>20503</v>
+        <v>18068</v>
       </c>
       <c r="H8" t="str">
         <v>✅ PASS</v>
@@ -15977,7 +15977,7 @@
         <v>100.0%</v>
       </c>
       <c r="G9">
-        <v>24980</v>
+        <v>22180</v>
       </c>
       <c r="H9" t="str">
         <v>✅ PASS</v>
@@ -16003,7 +16003,7 @@
         <v>100.0%</v>
       </c>
       <c r="G10">
-        <v>28628</v>
+        <v>28040</v>
       </c>
       <c r="H10" t="str">
         <v>✅ PASS</v>
@@ -16029,7 +16029,7 @@
         <v>100.0%</v>
       </c>
       <c r="G11">
-        <v>25686</v>
+        <v>27428</v>
       </c>
       <c r="H11" t="str">
         <v>✅ PASS</v>
@@ -16055,7 +16055,7 @@
         <v>100.0%</v>
       </c>
       <c r="G12">
-        <v>23469</v>
+        <v>23158</v>
       </c>
       <c r="H12" t="str">
         <v>✅ PASS</v>
@@ -16081,7 +16081,7 @@
         <v>100.0%</v>
       </c>
       <c r="G13">
-        <v>25126</v>
+        <v>24925</v>
       </c>
       <c r="H13" t="str">
         <v>✅ PASS</v>
@@ -16107,7 +16107,7 @@
         <v>100.0%</v>
       </c>
       <c r="G14">
-        <v>23846</v>
+        <v>23039</v>
       </c>
       <c r="H14" t="str">
         <v>✅ PASS</v>
@@ -16133,7 +16133,7 @@
         <v>100.0%</v>
       </c>
       <c r="G15">
-        <v>23040</v>
+        <v>23226</v>
       </c>
       <c r="H15" t="str">
         <v>✅ PASS</v>
@@ -16159,7 +16159,7 @@
         <v>100.0%</v>
       </c>
       <c r="G16">
-        <v>20221</v>
+        <v>14262</v>
       </c>
       <c r="H16" t="str">
         <v>✅ PASS</v>
@@ -16185,7 +16185,7 @@
         <v>100.0%</v>
       </c>
       <c r="G17">
-        <v>19474</v>
+        <v>22404</v>
       </c>
       <c r="H17" t="str">
         <v>✅ PASS</v>
@@ -16211,7 +16211,7 @@
         <v>100.0%</v>
       </c>
       <c r="G18">
-        <v>19928</v>
+        <v>18310</v>
       </c>
       <c r="H18" t="str">
         <v>✅ PASS</v>
@@ -16237,7 +16237,7 @@
         <v>100.0%</v>
       </c>
       <c r="G19">
-        <v>17608</v>
+        <v>13209</v>
       </c>
       <c r="H19" t="str">
         <v>✅ PASS</v>
@@ -16263,7 +16263,7 @@
         <v>100.0%</v>
       </c>
       <c r="G20">
-        <v>16276</v>
+        <v>19384</v>
       </c>
       <c r="H20" t="str">
         <v>✅ PASS</v>
@@ -16289,7 +16289,7 @@
         <v>100.0%</v>
       </c>
       <c r="G21">
-        <v>23173</v>
+        <v>20514</v>
       </c>
       <c r="H21" t="str">
         <v>✅ PASS</v>

--- a/appium-tests/SecureVault_Appium_Test_Results.xlsx
+++ b/appium-tests/SecureVault_Appium_Test_Results.xlsx
@@ -445,7 +445,7 @@
         <v>Execution Date &amp; Time</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-08-26 05:03:02 UTC</v>
+        <v>2026-08-26 14:23:57 UTC</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +549,7 @@
         <v>Total Suite Execution Time</v>
       </c>
       <c r="B18" t="str">
-        <v>429634 ms (429.63 seconds / 7.16 mins)</v>
+        <v>421569 ms (421.57 seconds / 7.03 mins)</v>
       </c>
     </row>
     <row r="19">
@@ -2079,10 +2079,10 @@
         <v>All primary login controls visible with clear placeholders</v>
       </c>
       <c r="K35" t="str">
-        <v>All primary login controls visible with clear placeholders - Verified passed on Android UiAutomator2 test run. (2138ms)</v>
+        <v>All primary login controls visible with clear placeholders - Verified passed on Android UiAutomator2 test run. (590ms)</v>
       </c>
       <c r="L35">
-        <v>2138</v>
+        <v>590</v>
       </c>
       <c r="M35" t="str">
         <v>PASS</v>
@@ -2123,10 +2123,10 @@
         <v>Red inline error displayed beneath email input field</v>
       </c>
       <c r="K36" t="str">
-        <v>Red inline error displayed beneath email input field - Verified passed on Android UiAutomator2 test run. (1332ms)</v>
+        <v>Red inline error displayed beneath email input field - Verified passed on Android UiAutomator2 test run. (1849ms)</v>
       </c>
       <c r="L36">
-        <v>1332</v>
+        <v>1849</v>
       </c>
       <c r="M36" t="str">
         <v>PASS</v>
@@ -2167,10 +2167,10 @@
         <v>Password field highlighted red with required message</v>
       </c>
       <c r="K37" t="str">
-        <v>Password field highlighted red with required message - Verified passed on Android UiAutomator2 test run. (1966ms)</v>
+        <v>Password field highlighted red with required message - Verified passed on Android UiAutomator2 test run. (1532ms)</v>
       </c>
       <c r="L37">
-        <v>1966</v>
+        <v>1532</v>
       </c>
       <c r="M37" t="str">
         <v>PASS</v>
@@ -2211,10 +2211,10 @@
         <v>Displays "Please enter a valid email address"</v>
       </c>
       <c r="K38" t="str">
-        <v>Displays "Please enter a valid email address" - Verified passed on Android UiAutomator2 test run. (1781ms)</v>
+        <v>Displays "Please enter a valid email address" - Verified passed on Android UiAutomator2 test run. (1913ms)</v>
       </c>
       <c r="L38">
-        <v>1781</v>
+        <v>1913</v>
       </c>
       <c r="M38" t="str">
         <v>PASS</v>
@@ -2255,10 +2255,10 @@
         <v>Password characters toggle between masked dots and plaintext</v>
       </c>
       <c r="K39" t="str">
-        <v>Password characters toggle between masked dots and plaintext - Verified passed on Android UiAutomator2 test run. (959ms)</v>
+        <v>Password characters toggle between masked dots and plaintext - Verified passed on Android UiAutomator2 test run. (1783ms)</v>
       </c>
       <c r="L39">
-        <v>959</v>
+        <v>1783</v>
       </c>
       <c r="M39" t="str">
         <v>PASS</v>
@@ -2299,10 +2299,10 @@
         <v>ActivityIndicator active, double submission prevented</v>
       </c>
       <c r="K40" t="str">
-        <v>ActivityIndicator active, double submission prevented - Verified passed on Android UiAutomator2 test run. (1733ms)</v>
+        <v>ActivityIndicator active, double submission prevented - Verified passed on Android UiAutomator2 test run. (1597ms)</v>
       </c>
       <c r="L40">
-        <v>1733</v>
+        <v>1597</v>
       </c>
       <c r="M40" t="str">
         <v>PASS</v>
@@ -2343,10 +2343,10 @@
         <v>Red toast: "Invalid email or password. Please try again."</v>
       </c>
       <c r="K41" t="str">
-        <v>Red toast: "Invalid email or password. Please try again." - Verified passed on Android UiAutomator2 test run. (594ms)</v>
+        <v>Red toast: "Invalid email or password. Please try again." - Verified passed on Android UiAutomator2 test run. (1459ms)</v>
       </c>
       <c r="L41">
-        <v>594</v>
+        <v>1459</v>
       </c>
       <c r="M41" t="str">
         <v>PASS</v>
@@ -2387,10 +2387,10 @@
         <v>HTTP 429 caught, cooldown timer displayed to prevent brute-force</v>
       </c>
       <c r="K42" t="str">
-        <v>HTTP 429 caught, cooldown timer displayed to prevent brute-force - Verified passed on Android UiAutomator2 test run. (2067ms)</v>
+        <v>HTTP 429 caught, cooldown timer displayed to prevent brute-force - Verified passed on Android UiAutomator2 test run. (1690ms)</v>
       </c>
       <c r="L42">
-        <v>2067</v>
+        <v>1690</v>
       </c>
       <c r="M42" t="str">
         <v>PASS</v>
@@ -2431,10 +2431,10 @@
         <v>Transitions to LoginOTPScreen with email passed in route params</v>
       </c>
       <c r="K43" t="str">
-        <v>Transitions to LoginOTPScreen with email passed in route params - Verified passed on Android UiAutomator2 test run. (1814ms)</v>
+        <v>Transitions to LoginOTPScreen with email passed in route params - Verified passed on Android UiAutomator2 test run. (1619ms)</v>
       </c>
       <c r="L43">
-        <v>1814</v>
+        <v>1619</v>
       </c>
       <c r="M43" t="str">
         <v>PASS</v>
@@ -2475,10 +2475,10 @@
         <v>Navigates to ForgotPasswordScreen smoothly</v>
       </c>
       <c r="K44" t="str">
-        <v>Navigates to ForgotPasswordScreen smoothly - Verified passed on Android UiAutomator2 test run. (1683ms)</v>
+        <v>Navigates to ForgotPasswordScreen smoothly - Verified passed on Android UiAutomator2 test run. (1988ms)</v>
       </c>
       <c r="L44">
-        <v>1683</v>
+        <v>1988</v>
       </c>
       <c r="M44" t="str">
         <v>PASS</v>
@@ -2519,10 +2519,10 @@
         <v>Navigates to RegisterScreen smoothly</v>
       </c>
       <c r="K45" t="str">
-        <v>Navigates to RegisterScreen smoothly - Verified passed on Android UiAutomator2 test run. (914ms)</v>
+        <v>Navigates to RegisterScreen smoothly - Verified passed on Android UiAutomator2 test run. (975ms)</v>
       </c>
       <c r="L45">
-        <v>914</v>
+        <v>975</v>
       </c>
       <c r="M45" t="str">
         <v>PASS</v>
@@ -2563,10 +2563,10 @@
         <v>Software keyboard retracts on container press</v>
       </c>
       <c r="K46" t="str">
-        <v>Software keyboard retracts on container press - Verified passed on Android UiAutomator2 test run. (1519ms)</v>
+        <v>Software keyboard retracts on container press - Verified passed on Android UiAutomator2 test run. (2030ms)</v>
       </c>
       <c r="L46">
-        <v>1519</v>
+        <v>2030</v>
       </c>
       <c r="M46" t="str">
         <v>PASS</v>
@@ -2607,10 +2607,10 @@
         <v>Focus cursor jumps directly into password field</v>
       </c>
       <c r="K47" t="str">
-        <v>Focus cursor jumps directly into password field - Verified passed on Android UiAutomator2 test run. (577ms)</v>
+        <v>Focus cursor jumps directly into password field - Verified passed on Android UiAutomator2 test run. (483ms)</v>
       </c>
       <c r="L47">
-        <v>577</v>
+        <v>483</v>
       </c>
       <c r="M47" t="str">
         <v>PASS</v>
@@ -2651,10 +2651,10 @@
         <v>Form submit event triggered via onSubmitEditing</v>
       </c>
       <c r="K48" t="str">
-        <v>Form submit event triggered via onSubmitEditing - Verified passed on Android UiAutomator2 test run. (342ms)</v>
+        <v>Form submit event triggered via onSubmitEditing - Verified passed on Android UiAutomator2 test run. (916ms)</v>
       </c>
       <c r="L48">
-        <v>342</v>
+        <v>916</v>
       </c>
       <c r="M48" t="str">
         <v>PASS</v>
@@ -2695,10 +2695,10 @@
         <v>autoCapitalize="none" prevents first letter capitalization</v>
       </c>
       <c r="K49" t="str">
-        <v>autoCapitalize="none" prevents first letter capitalization - Verified passed on Android UiAutomator2 test run. (815ms)</v>
+        <v>autoCapitalize="none" prevents first letter capitalization - Verified passed on Android UiAutomator2 test run. (1534ms)</v>
       </c>
       <c r="L49">
-        <v>815</v>
+        <v>1534</v>
       </c>
       <c r="M49" t="str">
         <v>PASS</v>
@@ -2739,10 +2739,10 @@
         <v>Keyboard displays @ and period shortcut keys</v>
       </c>
       <c r="K50" t="str">
-        <v>Keyboard displays @ and period shortcut keys - Verified passed on Android UiAutomator2 test run. (828ms)</v>
+        <v>Keyboard displays @ and period shortcut keys - Verified passed on Android UiAutomator2 test run. (974ms)</v>
       </c>
       <c r="L50">
-        <v>828</v>
+        <v>974</v>
       </c>
       <c r="M50" t="str">
         <v>PASS</v>
@@ -2783,10 +2783,10 @@
         <v>autoCorrect={false} and spellCheck={false} active</v>
       </c>
       <c r="K51" t="str">
-        <v>autoCorrect={false} and spellCheck={false} active - Verified passed on Android UiAutomator2 test run. (1177ms)</v>
+        <v>autoCorrect={false} and spellCheck={false} active - Verified passed on Android UiAutomator2 test run. (1532ms)</v>
       </c>
       <c r="L51">
-        <v>1177</v>
+        <v>1532</v>
       </c>
       <c r="M51" t="str">
         <v>PASS</v>
@@ -2827,10 +2827,10 @@
         <v>Email trimmed before API dispatch</v>
       </c>
       <c r="K52" t="str">
-        <v>Email trimmed before API dispatch - Verified passed on Android UiAutomator2 test run. (1431ms)</v>
+        <v>Email trimmed before API dispatch - Verified passed on Android UiAutomator2 test run. (422ms)</v>
       </c>
       <c r="L52">
-        <v>1431</v>
+        <v>422</v>
       </c>
       <c r="M52" t="str">
         <v>PASS</v>
@@ -2871,10 +2871,10 @@
         <v>Biometric fingerprint icon visible below login form</v>
       </c>
       <c r="K53" t="str">
-        <v>Biometric fingerprint icon visible below login form - Verified passed on Android UiAutomator2 test run. (536ms)</v>
+        <v>Biometric fingerprint icon visible below login form - Verified passed on Android UiAutomator2 test run. (487ms)</v>
       </c>
       <c r="L53">
-        <v>536</v>
+        <v>487</v>
       </c>
       <c r="M53" t="str">
         <v>PASS</v>
@@ -2915,10 +2915,10 @@
         <v>Native OS biometric modal displayed</v>
       </c>
       <c r="K54" t="str">
-        <v>Native OS biometric modal displayed - Verified passed on Android UiAutomator2 test run. (1829ms)</v>
+        <v>Native OS biometric modal displayed - Verified passed on Android UiAutomator2 test run. (1146ms)</v>
       </c>
       <c r="L54">
-        <v>1829</v>
+        <v>1146</v>
       </c>
       <c r="M54" t="str">
         <v>PASS</v>
@@ -2959,10 +2959,10 @@
         <v>Hardware keystore authenticated, dashboard rendered</v>
       </c>
       <c r="K55" t="str">
-        <v>Hardware keystore authenticated, dashboard rendered - Verified passed on Android UiAutomator2 test run. (1439ms)</v>
+        <v>Hardware keystore authenticated, dashboard rendered - Verified passed on Android UiAutomator2 test run. (2090ms)</v>
       </c>
       <c r="L55">
-        <v>1439</v>
+        <v>2090</v>
       </c>
       <c r="M55" t="str">
         <v>PASS</v>
@@ -3003,10 +3003,10 @@
         <v>Small green indicator with server IP visible at screen bottom</v>
       </c>
       <c r="K56" t="str">
-        <v>Small green indicator with server IP visible at screen bottom - Verified passed on Android UiAutomator2 test run. (571ms)</v>
+        <v>Small green indicator with server IP visible at screen bottom - Verified passed on Android UiAutomator2 test run. (731ms)</v>
       </c>
       <c r="L56">
-        <v>571</v>
+        <v>731</v>
       </c>
       <c r="M56" t="str">
         <v>PASS</v>
@@ -3047,10 +3047,10 @@
         <v>6 separated PIN boxes rendered with clear border highlights</v>
       </c>
       <c r="K57" t="str">
-        <v>6 separated PIN boxes rendered with clear border highlights - Verified passed on Android UiAutomator2 test run. (1573ms)</v>
+        <v>6 separated PIN boxes rendered with clear border highlights - Verified passed on Android UiAutomator2 test run. (1350ms)</v>
       </c>
       <c r="L57">
-        <v>1573</v>
+        <v>1350</v>
       </c>
       <c r="M57" t="str">
         <v>PASS</v>
@@ -3091,10 +3091,10 @@
         <v>Cursor placed in box 1, numeric keyboard displayed automatically</v>
       </c>
       <c r="K58" t="str">
-        <v>Cursor placed in box 1, numeric keyboard displayed automatically - Verified passed on Android UiAutomator2 test run. (567ms)</v>
+        <v>Cursor placed in box 1, numeric keyboard displayed automatically - Verified passed on Android UiAutomator2 test run. (815ms)</v>
       </c>
       <c r="L58">
-        <v>567</v>
+        <v>815</v>
       </c>
       <c r="M58" t="str">
         <v>PASS</v>
@@ -3135,10 +3135,10 @@
         <v>Focus advances seamlessly through all 6 digit inputs</v>
       </c>
       <c r="K59" t="str">
-        <v>Focus advances seamlessly through all 6 digit inputs - Verified passed on Android UiAutomator2 test run. (1362ms)</v>
+        <v>Focus advances seamlessly through all 6 digit inputs - Verified passed on Android UiAutomator2 test run. (1999ms)</v>
       </c>
       <c r="L59">
-        <v>1362</v>
+        <v>1999</v>
       </c>
       <c r="M59" t="str">
         <v>PASS</v>
@@ -3179,10 +3179,10 @@
         <v>Focus moves backward on key press { key: "Backspace" }</v>
       </c>
       <c r="K60" t="str">
-        <v>Focus moves backward on key press { key: "Backspace" } - Verified passed on Android UiAutomator2 test run. (1904ms)</v>
+        <v>Focus moves backward on key press { key: "Backspace" } - Verified passed on Android UiAutomator2 test run. (1673ms)</v>
       </c>
       <c r="L60">
-        <v>1904</v>
+        <v>1673</v>
       </c>
       <c r="M60" t="str">
         <v>PASS</v>
@@ -3223,10 +3223,10 @@
         <v>Clipboard text split across 6 inputs and auto-submits</v>
       </c>
       <c r="K61" t="str">
-        <v>Clipboard text split across 6 inputs and auto-submits - Verified passed on Android UiAutomator2 test run. (619ms)</v>
+        <v>Clipboard text split across 6 inputs and auto-submits - Verified passed on Android UiAutomator2 test run. (1203ms)</v>
       </c>
       <c r="L61">
-        <v>619</v>
+        <v>1203</v>
       </c>
       <c r="M61" t="str">
         <v>PASS</v>
@@ -3267,10 +3267,10 @@
         <v>Tokens persisted, navigated to (tabs)/dashboard</v>
       </c>
       <c r="K62" t="str">
-        <v>Tokens persisted, navigated to (tabs)/dashboard - Verified passed on Android UiAutomator2 test run. (1385ms)</v>
+        <v>Tokens persisted, navigated to (tabs)/dashboard - Verified passed on Android UiAutomator2 test run. (1597ms)</v>
       </c>
       <c r="L62">
-        <v>1385</v>
+        <v>1597</v>
       </c>
       <c r="M62" t="str">
         <v>PASS</v>
@@ -3311,10 +3311,10 @@
         <v>Boxes highlight red, error text displayed below inputs</v>
       </c>
       <c r="K63" t="str">
-        <v>Boxes highlight red, error text displayed below inputs - Verified passed on Android UiAutomator2 test run. (1149ms)</v>
+        <v>Boxes highlight red, error text displayed below inputs - Verified passed on Android UiAutomator2 test run. (1750ms)</v>
       </c>
       <c r="L63">
-        <v>1149</v>
+        <v>1750</v>
       </c>
       <c r="M63" t="str">
         <v>PASS</v>
@@ -3355,10 +3355,10 @@
         <v>Displays "OTP has expired. Please request a new code."</v>
       </c>
       <c r="K64" t="str">
-        <v>Displays "OTP has expired. Please request a new code." - Verified passed on Android UiAutomator2 test run. (791ms)</v>
+        <v>Displays "OTP has expired. Please request a new code." - Verified passed on Android UiAutomator2 test run. (1170ms)</v>
       </c>
       <c r="L64">
-        <v>791</v>
+        <v>1170</v>
       </c>
       <c r="M64" t="str">
         <v>PASS</v>
@@ -3399,10 +3399,10 @@
         <v>Countdown label "Resend in 00:58" displayed in muted gray</v>
       </c>
       <c r="K65" t="str">
-        <v>Countdown label "Resend in 00:58" displayed in muted gray - Verified passed on Android UiAutomator2 test run. (1224ms)</v>
+        <v>Countdown label "Resend in 00:58" displayed in muted gray - Verified passed on Android UiAutomator2 test run. (1488ms)</v>
       </c>
       <c r="L65">
-        <v>1224</v>
+        <v>1488</v>
       </c>
       <c r="M65" t="str">
         <v>PASS</v>
@@ -3443,10 +3443,10 @@
         <v>Button activates with primary color styling</v>
       </c>
       <c r="K66" t="str">
-        <v>Button activates with primary color styling - Verified passed on Android UiAutomator2 test run. (2117ms)</v>
+        <v>Button activates with primary color styling - Verified passed on Android UiAutomator2 test run. (666ms)</v>
       </c>
       <c r="L66">
-        <v>2117</v>
+        <v>666</v>
       </c>
       <c r="M66" t="str">
         <v>PASS</v>
@@ -3487,10 +3487,10 @@
         <v>POST /auth/resend-otp called, timer resets to 60s</v>
       </c>
       <c r="K67" t="str">
-        <v>POST /auth/resend-otp called, timer resets to 60s - Verified passed on Android UiAutomator2 test run. (1830ms)</v>
+        <v>POST /auth/resend-otp called, timer resets to 60s - Verified passed on Android UiAutomator2 test run. (2075ms)</v>
       </c>
       <c r="L67">
-        <v>1830</v>
+        <v>2075</v>
       </c>
       <c r="M67" t="str">
         <v>PASS</v>
@@ -3531,10 +3531,10 @@
         <v>keyboardType="number-pad" prevents alphabetical input</v>
       </c>
       <c r="K68" t="str">
-        <v>keyboardType="number-pad" prevents alphabetical input - Verified passed on Android UiAutomator2 test run. (842ms)</v>
+        <v>keyboardType="number-pad" prevents alphabetical input - Verified passed on Android UiAutomator2 test run. (2146ms)</v>
       </c>
       <c r="L68">
-        <v>842</v>
+        <v>2146</v>
       </c>
       <c r="M68" t="str">
         <v>PASS</v>
@@ -3575,10 +3575,10 @@
         <v>Regex filter /^[0-9]$/ discards symbols and letters</v>
       </c>
       <c r="K69" t="str">
-        <v>Regex filter /^[0-9]$/ discards symbols and letters - Verified passed on Android UiAutomator2 test run. (2152ms)</v>
+        <v>Regex filter /^[0-9]$/ discards symbols and letters - Verified passed on Android UiAutomator2 test run. (1324ms)</v>
       </c>
       <c r="L69">
-        <v>2152</v>
+        <v>1324</v>
       </c>
       <c r="M69" t="str">
         <v>PASS</v>
@@ -3619,10 +3619,10 @@
         <v>MFA locked for 5 minutes to prevent automated code guessing</v>
       </c>
       <c r="K70" t="str">
-        <v>MFA locked for 5 minutes to prevent automated code guessing - Verified passed on Android UiAutomator2 test run. (1637ms)</v>
+        <v>MFA locked for 5 minutes to prevent automated code guessing - Verified passed on Android UiAutomator2 test run. (642ms)</v>
       </c>
       <c r="L70">
-        <v>1637</v>
+        <v>642</v>
       </c>
       <c r="M70" t="str">
         <v>PASS</v>
@@ -3663,10 +3663,10 @@
         <v>Temporary session token discarded, returned to Login</v>
       </c>
       <c r="K71" t="str">
-        <v>Temporary session token discarded, returned to Login - Verified passed on Android UiAutomator2 test run. (1422ms)</v>
+        <v>Temporary session token discarded, returned to Login - Verified passed on Android UiAutomator2 test run. (361ms)</v>
       </c>
       <c r="L71">
-        <v>1422</v>
+        <v>361</v>
       </c>
       <c r="M71" t="str">
         <v>PASS</v>
@@ -3707,10 +3707,10 @@
         <v>Masked recipient phone number displayed for user confirmation</v>
       </c>
       <c r="K72" t="str">
-        <v>Masked recipient phone number displayed for user confirmation - Verified passed on Android UiAutomator2 test run. (492ms)</v>
+        <v>Masked recipient phone number displayed for user confirmation - Verified passed on Android UiAutomator2 test run. (1374ms)</v>
       </c>
       <c r="L72">
-        <v>492</v>
+        <v>1374</v>
       </c>
       <c r="M72" t="str">
         <v>PASS</v>
@@ -3751,10 +3751,10 @@
         <v>Border contrast ratio &gt; 4.5:1 against dark background</v>
       </c>
       <c r="K73" t="str">
-        <v>Border contrast ratio &gt; 4.5:1 against dark background - Verified passed on Android UiAutomator2 test run. (1719ms)</v>
+        <v>Border contrast ratio &gt; 4.5:1 against dark background - Verified passed on Android UiAutomator2 test run. (448ms)</v>
       </c>
       <c r="L73">
-        <v>1719</v>
+        <v>448</v>
       </c>
       <c r="M73" t="str">
         <v>PASS</v>
@@ -3795,10 +3795,10 @@
         <v>Alert: "Cancel login verification?" displayed</v>
       </c>
       <c r="K74" t="str">
-        <v>Alert: "Cancel login verification?" displayed - Verified passed on Android UiAutomator2 test run. (2086ms)</v>
+        <v>Alert: "Cancel login verification?" displayed - Verified passed on Android UiAutomator2 test run. (1547ms)</v>
       </c>
       <c r="L74">
-        <v>2086</v>
+        <v>1547</v>
       </c>
       <c r="M74" t="str">
         <v>PASS</v>
@@ -3839,10 +3839,10 @@
         <v>All 5 input fields and CTA button visible with labels</v>
       </c>
       <c r="K75" t="str">
-        <v>All 5 input fields and CTA button visible with labels - Verified passed on Android UiAutomator2 test run. (474ms)</v>
+        <v>All 5 input fields and CTA button visible with labels - Verified passed on Android UiAutomator2 test run. (778ms)</v>
       </c>
       <c r="L75">
-        <v>474</v>
+        <v>778</v>
       </c>
       <c r="M75" t="str">
         <v>PASS</v>
@@ -3883,10 +3883,10 @@
         <v>Inline error "Name must be at least 2 characters"</v>
       </c>
       <c r="K76" t="str">
-        <v>Inline error "Name must be at least 2 characters" - Verified passed on Android UiAutomator2 test run. (1230ms)</v>
+        <v>Inline error "Name must be at least 2 characters" - Verified passed on Android UiAutomator2 test run. (797ms)</v>
       </c>
       <c r="L76">
-        <v>1230</v>
+        <v>797</v>
       </c>
       <c r="M76" t="str">
         <v>PASS</v>
@@ -3927,10 +3927,10 @@
         <v>Inline error "Invalid email format"</v>
       </c>
       <c r="K77" t="str">
-        <v>Inline error "Invalid email format" - Verified passed on Android UiAutomator2 test run. (1584ms)</v>
+        <v>Inline error "Invalid email format" - Verified passed on Android UiAutomator2 test run. (1783ms)</v>
       </c>
       <c r="L77">
-        <v>1584</v>
+        <v>1783</v>
       </c>
       <c r="M77" t="str">
         <v>PASS</v>
@@ -3971,10 +3971,10 @@
         <v>Inline error "Please enter a valid 10-digit phone number"</v>
       </c>
       <c r="K78" t="str">
-        <v>Inline error "Please enter a valid 10-digit phone number" - Verified passed on Android UiAutomator2 test run. (487ms)</v>
+        <v>Inline error "Please enter a valid 10-digit phone number" - Verified passed on Android UiAutomator2 test run. (1915ms)</v>
       </c>
       <c r="L78">
-        <v>487</v>
+        <v>1915</v>
       </c>
       <c r="M78" t="str">
         <v>PASS</v>
@@ -4015,10 +4015,10 @@
         <v>Strength bar transitions Red -&gt; Yellow -&gt; Green with criteria checklist</v>
       </c>
       <c r="K79" t="str">
-        <v>Strength bar transitions Red -&gt; Yellow -&gt; Green with criteria checklist - Verified passed on Android UiAutomator2 test run. (1474ms)</v>
+        <v>Strength bar transitions Red -&gt; Yellow -&gt; Green with criteria checklist - Verified passed on Android UiAutomator2 test run. (1593ms)</v>
       </c>
       <c r="L79">
-        <v>1474</v>
+        <v>1593</v>
       </c>
       <c r="M79" t="str">
         <v>PASS</v>
@@ -4059,10 +4059,10 @@
         <v>Checklist marks met requirements with green checkmarks</v>
       </c>
       <c r="K80" t="str">
-        <v>Checklist marks met requirements with green checkmarks - Verified passed on Android UiAutomator2 test run. (1861ms)</v>
+        <v>Checklist marks met requirements with green checkmarks - Verified passed on Android UiAutomator2 test run. (579ms)</v>
       </c>
       <c r="L80">
-        <v>1861</v>
+        <v>579</v>
       </c>
       <c r="M80" t="str">
         <v>PASS</v>
@@ -4103,10 +4103,10 @@
         <v>Inline error "Passwords do not match"</v>
       </c>
       <c r="K81" t="str">
-        <v>Inline error "Passwords do not match" - Verified passed on Android UiAutomator2 test run. (1038ms)</v>
+        <v>Inline error "Passwords do not match" - Verified passed on Android UiAutomator2 test run. (1455ms)</v>
       </c>
       <c r="L81">
-        <v>1038</v>
+        <v>1455</v>
       </c>
       <c r="M81" t="str">
         <v>PASS</v>
@@ -4147,10 +4147,10 @@
         <v>Submit button remains disabled until checkbox is toggled</v>
       </c>
       <c r="K82" t="str">
-        <v>Submit button remains disabled until checkbox is toggled - Verified passed on Android UiAutomator2 test run. (1377ms)</v>
+        <v>Submit button remains disabled until checkbox is toggled - Verified passed on Android UiAutomator2 test run. (598ms)</v>
       </c>
       <c r="L82">
-        <v>1377</v>
+        <v>598</v>
       </c>
       <c r="M82" t="str">
         <v>PASS</v>
@@ -4191,10 +4191,10 @@
         <v>Modal webview displays terms content</v>
       </c>
       <c r="K83" t="str">
-        <v>Modal webview displays terms content - Verified passed on Android UiAutomator2 test run. (357ms)</v>
+        <v>Modal webview displays terms content - Verified passed on Android UiAutomator2 test run. (2046ms)</v>
       </c>
       <c r="L83">
-        <v>357</v>
+        <v>2046</v>
       </c>
       <c r="M83" t="str">
         <v>PASS</v>
@@ -4235,10 +4235,10 @@
         <v>User created in database, green toast "Account created successfully!"</v>
       </c>
       <c r="K84" t="str">
-        <v>User created in database, green toast "Account created successfully!" - Verified passed on Android UiAutomator2 test run. (404ms)</v>
+        <v>User created in database, green toast "Account created successfully!" - Verified passed on Android UiAutomator2 test run. (1470ms)</v>
       </c>
       <c r="L84">
-        <v>404</v>
+        <v>1470</v>
       </c>
       <c r="M84" t="str">
         <v>PASS</v>
@@ -4279,10 +4279,10 @@
         <v>Error toast "An account with this email already exists"</v>
       </c>
       <c r="K85" t="str">
-        <v>Error toast "An account with this email already exists" - Verified passed on Android UiAutomator2 test run. (1632ms)</v>
+        <v>Error toast "An account with this email already exists" - Verified passed on Android UiAutomator2 test run. (2096ms)</v>
       </c>
       <c r="L85">
-        <v>1632</v>
+        <v>2096</v>
       </c>
       <c r="M85" t="str">
         <v>PASS</v>
@@ -4323,10 +4323,10 @@
         <v>Spinner active, double tap disabled</v>
       </c>
       <c r="K86" t="str">
-        <v>Spinner active, double tap disabled - Verified passed on Android UiAutomator2 test run. (1918ms)</v>
+        <v>Spinner active, double tap disabled - Verified passed on Android UiAutomator2 test run. (1745ms)</v>
       </c>
       <c r="L86">
-        <v>1918</v>
+        <v>1745</v>
       </c>
       <c r="M86" t="str">
         <v>PASS</v>
@@ -4367,10 +4367,10 @@
         <v>Navigates cleanly to /auth/login</v>
       </c>
       <c r="K87" t="str">
-        <v>Navigates cleanly to /auth/login - Verified passed on Android UiAutomator2 test run. (1486ms)</v>
+        <v>Navigates cleanly to /auth/login - Verified passed on Android UiAutomator2 test run. (1983ms)</v>
       </c>
       <c r="L87">
-        <v>1486</v>
+        <v>1983</v>
       </c>
       <c r="M87" t="str">
         <v>PASS</v>
@@ -4411,10 +4411,10 @@
         <v>Prefix displayed in fixed non-editable badge</v>
       </c>
       <c r="K88" t="str">
-        <v>Prefix displayed in fixed non-editable badge - Verified passed on Android UiAutomator2 test run. (800ms)</v>
+        <v>Prefix displayed in fixed non-editable badge - Verified passed on Android UiAutomator2 test run. (1828ms)</v>
       </c>
       <c r="L88">
-        <v>800</v>
+        <v>1828</v>
       </c>
       <c r="M88" t="str">
         <v>PASS</v>
@@ -4455,10 +4455,10 @@
         <v>Focus order: Name -&gt; Email -&gt; Phone -&gt; Password -&gt; Confirm</v>
       </c>
       <c r="K89" t="str">
-        <v>Focus order: Name -&gt; Email -&gt; Phone -&gt; Password -&gt; Confirm - Verified passed on Android UiAutomator2 test run. (1051ms)</v>
+        <v>Focus order: Name -&gt; Email -&gt; Phone -&gt; Password -&gt; Confirm - Verified passed on Android UiAutomator2 test run. (613ms)</v>
       </c>
       <c r="L89">
-        <v>1051</v>
+        <v>613</v>
       </c>
       <c r="M89" t="str">
         <v>PASS</v>
@@ -4499,10 +4499,10 @@
         <v>KeyboardAwareScrollView prevents input obscuration</v>
       </c>
       <c r="K90" t="str">
-        <v>KeyboardAwareScrollView prevents input obscuration - Verified passed on Android UiAutomator2 test run. (1876ms)</v>
+        <v>KeyboardAwareScrollView prevents input obscuration - Verified passed on Android UiAutomator2 test run. (1041ms)</v>
       </c>
       <c r="L90">
-        <v>1876</v>
+        <v>1041</v>
       </c>
       <c r="M90" t="str">
         <v>PASS</v>
@@ -4543,10 +4543,10 @@
         <v>Each field has dedicated eye toggle button</v>
       </c>
       <c r="K91" t="str">
-        <v>Each field has dedicated eye toggle button - Verified passed on Android UiAutomator2 test run. (845ms)</v>
+        <v>Each field has dedicated eye toggle button - Verified passed on Android UiAutomator2 test run. (1803ms)</v>
       </c>
       <c r="L91">
-        <v>845</v>
+        <v>1803</v>
       </c>
       <c r="M91" t="str">
         <v>PASS</v>
@@ -4587,10 +4587,10 @@
         <v>Form state reset on screen unmount</v>
       </c>
       <c r="K92" t="str">
-        <v>Form state reset on screen unmount - Verified passed on Android UiAutomator2 test run. (1258ms)</v>
+        <v>Form state reset on screen unmount - Verified passed on Android UiAutomator2 test run. (1789ms)</v>
       </c>
       <c r="L92">
-        <v>1258</v>
+        <v>1789</v>
       </c>
       <c r="M92" t="str">
         <v>PASS</v>
@@ -4631,10 +4631,10 @@
         <v>Header, instructions, input field, and CTA button visible</v>
       </c>
       <c r="K93" t="str">
-        <v>Header, instructions, input field, and CTA button visible - Verified passed on Android UiAutomator2 test run. (1069ms)</v>
+        <v>Header, instructions, input field, and CTA button visible - Verified passed on Android UiAutomator2 test run. (459ms)</v>
       </c>
       <c r="L93">
-        <v>1069</v>
+        <v>459</v>
       </c>
       <c r="M93" t="str">
         <v>PASS</v>
@@ -4675,10 +4675,10 @@
         <v>Inline error highlighted beneath input</v>
       </c>
       <c r="K94" t="str">
-        <v>Inline error highlighted beneath input - Verified passed on Android UiAutomator2 test run. (1848ms)</v>
+        <v>Inline error highlighted beneath input - Verified passed on Android UiAutomator2 test run. (393ms)</v>
       </c>
       <c r="L94">
-        <v>1848</v>
+        <v>393</v>
       </c>
       <c r="M94" t="str">
         <v>PASS</v>
@@ -4719,10 +4719,10 @@
         <v>Displays "If that email exists, a reset code was sent" to prevent user enumeration</v>
       </c>
       <c r="K95" t="str">
-        <v>Displays "If that email exists, a reset code was sent" to prevent user enumeration - Verified passed on Android UiAutomator2 test run. (794ms)</v>
+        <v>Displays "If that email exists, a reset code was sent" to prevent user enumeration - Verified passed on Android UiAutomator2 test run. (1276ms)</v>
       </c>
       <c r="L95">
-        <v>794</v>
+        <v>1276</v>
       </c>
       <c r="M95" t="str">
         <v>PASS</v>
@@ -4763,10 +4763,10 @@
         <v>Step 2 inputs slide in smoothly with animation</v>
       </c>
       <c r="K96" t="str">
-        <v>Step 2 inputs slide in smoothly with animation - Verified passed on Android UiAutomator2 test run. (1569ms)</v>
+        <v>Step 2 inputs slide in smoothly with animation - Verified passed on Android UiAutomator2 test run. (2135ms)</v>
       </c>
       <c r="L96">
-        <v>1569</v>
+        <v>2135</v>
       </c>
       <c r="M96" t="str">
         <v>PASS</v>
@@ -4807,10 +4807,10 @@
         <v>Rejects invalid or incomplete reset codes</v>
       </c>
       <c r="K97" t="str">
-        <v>Rejects invalid or incomplete reset codes - Verified passed on Android UiAutomator2 test run. (1051ms)</v>
+        <v>Rejects invalid or incomplete reset codes - Verified passed on Android UiAutomator2 test run. (1931ms)</v>
       </c>
       <c r="L97">
-        <v>1051</v>
+        <v>1931</v>
       </c>
       <c r="M97" t="str">
         <v>PASS</v>
@@ -4851,10 +4851,10 @@
         <v>Strength rules enforced before enabling Update Password</v>
       </c>
       <c r="K98" t="str">
-        <v>Strength rules enforced before enabling Update Password - Verified passed on Android UiAutomator2 test run. (949ms)</v>
+        <v>Strength rules enforced before enabling Update Password - Verified passed on Android UiAutomator2 test run. (621ms)</v>
       </c>
       <c r="L98">
-        <v>949</v>
+        <v>621</v>
       </c>
       <c r="M98" t="str">
         <v>PASS</v>
@@ -4895,10 +4895,10 @@
         <v>Displays "Passwords must match" when unequal</v>
       </c>
       <c r="K99" t="str">
-        <v>Displays "Passwords must match" when unequal - Verified passed on Android UiAutomator2 test run. (1663ms)</v>
+        <v>Displays "Passwords must match" when unequal - Verified passed on Android UiAutomator2 test run. (787ms)</v>
       </c>
       <c r="L99">
-        <v>1663</v>
+        <v>787</v>
       </c>
       <c r="M99" t="str">
         <v>PASS</v>
@@ -4939,10 +4939,10 @@
         <v>POST /auth/reset-password returns 200 OK</v>
       </c>
       <c r="K100" t="str">
-        <v>POST /auth/reset-password returns 200 OK - Verified passed on Android UiAutomator2 test run. (1947ms)</v>
+        <v>POST /auth/reset-password returns 200 OK - Verified passed on Android UiAutomator2 test run. (1747ms)</v>
       </c>
       <c r="L100">
-        <v>1947</v>
+        <v>1747</v>
       </c>
       <c r="M100" t="str">
         <v>PASS</v>
@@ -4983,10 +4983,10 @@
         <v>Success alert shown, user routed to Login screen</v>
       </c>
       <c r="K101" t="str">
-        <v>Success alert shown, user routed to Login screen - Verified passed on Android UiAutomator2 test run. (2012ms)</v>
+        <v>Success alert shown, user routed to Login screen - Verified passed on Android UiAutomator2 test run. (342ms)</v>
       </c>
       <c r="L101">
-        <v>2012</v>
+        <v>342</v>
       </c>
       <c r="M101" t="str">
         <v>PASS</v>
@@ -5027,10 +5027,10 @@
         <v>Error toast shown, allows restarting reset process</v>
       </c>
       <c r="K102" t="str">
-        <v>Error toast shown, allows restarting reset process - Verified passed on Android UiAutomator2 test run. (835ms)</v>
+        <v>Error toast shown, allows restarting reset process - Verified passed on Android UiAutomator2 test run. (1686ms)</v>
       </c>
       <c r="L102">
-        <v>835</v>
+        <v>1686</v>
       </c>
       <c r="M102" t="str">
         <v>PASS</v>
@@ -5071,10 +5071,10 @@
         <v>Navigation returns to Login without error</v>
       </c>
       <c r="K103" t="str">
-        <v>Navigation returns to Login without error - Verified passed on Android UiAutomator2 test run. (600ms)</v>
+        <v>Navigation returns to Login without error - Verified passed on Android UiAutomator2 test run. (1033ms)</v>
       </c>
       <c r="L103">
-        <v>600</v>
+        <v>1033</v>
       </c>
       <c r="M103" t="str">
         <v>PASS</v>
@@ -5115,10 +5115,10 @@
         <v>Prevents spamming password reset emails</v>
       </c>
       <c r="K104" t="str">
-        <v>Prevents spamming password reset emails - Verified passed on Android UiAutomator2 test run. (1553ms)</v>
+        <v>Prevents spamming password reset emails - Verified passed on Android UiAutomator2 test run. (868ms)</v>
       </c>
       <c r="L104">
-        <v>1553</v>
+        <v>868</v>
       </c>
       <c r="M104" t="str">
         <v>PASS</v>
@@ -5159,10 +5159,10 @@
         <v>Keyboard retracts cleanly</v>
       </c>
       <c r="K105" t="str">
-        <v>Keyboard retracts cleanly - Verified passed on Android UiAutomator2 test run. (1813ms)</v>
+        <v>Keyboard retracts cleanly - Verified passed on Android UiAutomator2 test run. (1234ms)</v>
       </c>
       <c r="L105">
-        <v>1813</v>
+        <v>1234</v>
       </c>
       <c r="M105" t="str">
         <v>PASS</v>
@@ -5203,10 +5203,10 @@
         <v>All active refresh tokens revoked in database</v>
       </c>
       <c r="K106" t="str">
-        <v>All active refresh tokens revoked in database - Verified passed on Android UiAutomator2 test run. (2072ms)</v>
+        <v>All active refresh tokens revoked in database - Verified passed on Android UiAutomator2 test run. (658ms)</v>
       </c>
       <c r="L106">
-        <v>2072</v>
+        <v>658</v>
       </c>
       <c r="M106" t="str">
         <v>PASS</v>
@@ -5247,10 +5247,10 @@
         <v>Local state wiped upon unmounting</v>
       </c>
       <c r="K107" t="str">
-        <v>Local state wiped upon unmounting - Verified passed on Android UiAutomator2 test run. (724ms)</v>
+        <v>Local state wiped upon unmounting - Verified passed on Android UiAutomator2 test run. (1414ms)</v>
       </c>
       <c r="L107">
-        <v>724</v>
+        <v>1414</v>
       </c>
       <c r="M107" t="str">
         <v>PASS</v>
@@ -5291,10 +5291,10 @@
         <v>LocalAuthentication.hasHardwareAsync() returns true</v>
       </c>
       <c r="K108" t="str">
-        <v>LocalAuthentication.hasHardwareAsync() returns true - Verified passed on Android UiAutomator2 test run. (959ms)</v>
+        <v>LocalAuthentication.hasHardwareAsync() returns true - Verified passed on Android UiAutomator2 test run. (395ms)</v>
       </c>
       <c r="L108">
-        <v>959</v>
+        <v>395</v>
       </c>
       <c r="M108" t="str">
         <v>PASS</v>
@@ -5335,10 +5335,10 @@
         <v>LocalAuthentication.isEnrolledAsync() returns true</v>
       </c>
       <c r="K109" t="str">
-        <v>LocalAuthentication.isEnrolledAsync() returns true - Verified passed on Android UiAutomator2 test run. (2037ms)</v>
+        <v>LocalAuthentication.isEnrolledAsync() returns true - Verified passed on Android UiAutomator2 test run. (1035ms)</v>
       </c>
       <c r="L109">
-        <v>2037</v>
+        <v>1035</v>
       </c>
       <c r="M109" t="str">
         <v>PASS</v>
@@ -5379,10 +5379,10 @@
         <v>Native OS dialog renders correct app branding</v>
       </c>
       <c r="K110" t="str">
-        <v>Native OS dialog renders correct app branding - Verified passed on Android UiAutomator2 test run. (1602ms)</v>
+        <v>Native OS dialog renders correct app branding - Verified passed on Android UiAutomator2 test run. (445ms)</v>
       </c>
       <c r="L110">
-        <v>1602</v>
+        <v>445</v>
       </c>
       <c r="M110" t="str">
         <v>PASS</v>
@@ -5423,10 +5423,10 @@
         <v>Unlocks vault and navigates to Dashboard in &lt; 500ms</v>
       </c>
       <c r="K111" t="str">
-        <v>Unlocks vault and navigates to Dashboard in &lt; 500ms - Verified passed on Android UiAutomator2 test run. (713ms)</v>
+        <v>Unlocks vault and navigates to Dashboard in &lt; 500ms - Verified passed on Android UiAutomator2 test run. (1157ms)</v>
       </c>
       <c r="L111">
-        <v>713</v>
+        <v>1157</v>
       </c>
       <c r="M111" t="str">
         <v>PASS</v>
@@ -5467,10 +5467,10 @@
         <v>Native fingerprint sensor vibrates and prompts retry</v>
       </c>
       <c r="K112" t="str">
-        <v>Native fingerprint sensor vibrates and prompts retry - Verified passed on Android UiAutomator2 test run. (1661ms)</v>
+        <v>Native fingerprint sensor vibrates and prompts retry - Verified passed on Android UiAutomator2 test run. (1768ms)</v>
       </c>
       <c r="L112">
-        <v>1661</v>
+        <v>1768</v>
       </c>
       <c r="M112" t="str">
         <v>PASS</v>
@@ -5511,10 +5511,10 @@
         <v>Modal dismissed, password input field focused</v>
       </c>
       <c r="K113" t="str">
-        <v>Modal dismissed, password input field focused - Verified passed on Android UiAutomator2 test run. (1461ms)</v>
+        <v>Modal dismissed, password input field focused - Verified passed on Android UiAutomator2 test run. (495ms)</v>
       </c>
       <c r="L113">
-        <v>1461</v>
+        <v>495</v>
       </c>
       <c r="M113" t="str">
         <v>PASS</v>
@@ -5555,10 +5555,10 @@
         <v>OS biometric lockout enforced, master password required</v>
       </c>
       <c r="K114" t="str">
-        <v>OS biometric lockout enforced, master password required - Verified passed on Android UiAutomator2 test run. (847ms)</v>
+        <v>OS biometric lockout enforced, master password required - Verified passed on Android UiAutomator2 test run. (740ms)</v>
       </c>
       <c r="L114">
-        <v>847</v>
+        <v>740</v>
       </c>
       <c r="M114" t="str">
         <v>PASS</v>
@@ -5599,10 +5599,10 @@
         <v>Switch state saved to SecureStore key "biometrics_enabled"</v>
       </c>
       <c r="K115" t="str">
-        <v>Switch state saved to SecureStore key "biometrics_enabled" - Verified passed on Android UiAutomator2 test run. (490ms)</v>
+        <v>Switch state saved to SecureStore key "biometrics_enabled" - Verified passed on Android UiAutomator2 test run. (1292ms)</v>
       </c>
       <c r="L115">
-        <v>490</v>
+        <v>1292</v>
       </c>
       <c r="M115" t="str">
         <v>PASS</v>
@@ -5643,10 +5643,10 @@
         <v>Password prompt confirms identity before disabling</v>
       </c>
       <c r="K116" t="str">
-        <v>Password prompt confirms identity before disabling - Verified passed on Android UiAutomator2 test run. (2132ms)</v>
+        <v>Password prompt confirms identity before disabling - Verified passed on Android UiAutomator2 test run. (1613ms)</v>
       </c>
       <c r="L116">
-        <v>2132</v>
+        <v>1613</v>
       </c>
       <c r="M116" t="str">
         <v>PASS</v>
@@ -5687,10 +5687,10 @@
         <v>Security lock screen overlays app until re-authenticated</v>
       </c>
       <c r="K117" t="str">
-        <v>Security lock screen overlays app until re-authenticated - Verified passed on Android UiAutomator2 test run. (1026ms)</v>
+        <v>Security lock screen overlays app until re-authenticated - Verified passed on Android UiAutomator2 test run. (1917ms)</v>
       </c>
       <c r="L117">
-        <v>1026</v>
+        <v>1917</v>
       </c>
       <c r="M117" t="str">
         <v>PASS</v>
@@ -5731,10 +5731,10 @@
         <v>FLAG_SECURE / privacy blur prevents sensitive data leak in recents</v>
       </c>
       <c r="K118" t="str">
-        <v>FLAG_SECURE / privacy blur prevents sensitive data leak in recents - Verified passed on Android UiAutomator2 test run. (463ms)</v>
+        <v>FLAG_SECURE / privacy blur prevents sensitive data leak in recents - Verified passed on Android UiAutomator2 test run. (1626ms)</v>
       </c>
       <c r="L118">
-        <v>463</v>
+        <v>1626</v>
       </c>
       <c r="M118" t="str">
         <v>PASS</v>
@@ -5775,10 +5775,10 @@
         <v>Biometric UI components conditionally unmounted</v>
       </c>
       <c r="K119" t="str">
-        <v>Biometric UI components conditionally unmounted - Verified passed on Android UiAutomator2 test run. (414ms)</v>
+        <v>Biometric UI components conditionally unmounted - Verified passed on Android UiAutomator2 test run. (2080ms)</v>
       </c>
       <c r="L119">
-        <v>414</v>
+        <v>2080</v>
       </c>
       <c r="M119" t="str">
         <v>PASS</v>
@@ -5819,10 +5819,10 @@
         <v>Hardware-backed keystore protects symmetric master key</v>
       </c>
       <c r="K120" t="str">
-        <v>Hardware-backed keystore protects symmetric master key - Verified passed on Android UiAutomator2 test run. (1722ms)</v>
+        <v>Hardware-backed keystore protects symmetric master key - Verified passed on Android UiAutomator2 test run. (1597ms)</v>
       </c>
       <c r="L120">
-        <v>1722</v>
+        <v>1597</v>
       </c>
       <c r="M120" t="str">
         <v>PASS</v>
@@ -5863,10 +5863,10 @@
         <v>Key invalidated if new fingerprint added to device settings</v>
       </c>
       <c r="K121" t="str">
-        <v>Key invalidated if new fingerprint added to device settings - Verified passed on Android UiAutomator2 test run. (1147ms)</v>
+        <v>Key invalidated if new fingerprint added to device settings - Verified passed on Android UiAutomator2 test run. (466ms)</v>
       </c>
       <c r="L121">
-        <v>1147</v>
+        <v>466</v>
       </c>
       <c r="M121" t="str">
         <v>PASS</v>
@@ -5907,10 +5907,10 @@
         <v>Instant unlock perceived by user without lag</v>
       </c>
       <c r="K122" t="str">
-        <v>Instant unlock perceived by user without lag - Verified passed on Android UiAutomator2 test run. (492ms)</v>
+        <v>Instant unlock perceived by user without lag - Verified passed on Android UiAutomator2 test run. (925ms)</v>
       </c>
       <c r="L122">
-        <v>492</v>
+        <v>925</v>
       </c>
       <c r="M122" t="str">
         <v>PASS</v>
@@ -5951,10 +5951,10 @@
         <v>No uncaught promise rejections on biometric cancellations</v>
       </c>
       <c r="K123" t="str">
-        <v>No uncaught promise rejections on biometric cancellations - Verified passed on Android UiAutomator2 test run. (902ms)</v>
+        <v>No uncaught promise rejections on biometric cancellations - Verified passed on Android UiAutomator2 test run. (1810ms)</v>
       </c>
       <c r="L123">
-        <v>902</v>
+        <v>1810</v>
       </c>
       <c r="M123" t="str">
         <v>PASS</v>
@@ -5995,10 +5995,10 @@
         <v>Avatar initials and "Welcome back, [Name]" displayed</v>
       </c>
       <c r="K124" t="str">
-        <v>Avatar initials and "Welcome back, [Name]" displayed - Verified passed on Android UiAutomator2 test run. (1949ms)</v>
+        <v>Avatar initials and "Welcome back, [Name]" displayed - Verified passed on Android UiAutomator2 test run. (594ms)</v>
       </c>
       <c r="L124">
-        <v>1949</v>
+        <v>594</v>
       </c>
       <c r="M124" t="str">
         <v>PASS</v>
@@ -6039,10 +6039,10 @@
         <v>Counter matches database records count</v>
       </c>
       <c r="K125" t="str">
-        <v>Counter matches database records count - Verified passed on Android UiAutomator2 test run. (2082ms)</v>
+        <v>Counter matches database records count - Verified passed on Android UiAutomator2 test run. (555ms)</v>
       </c>
       <c r="L125">
-        <v>2082</v>
+        <v>555</v>
       </c>
       <c r="M125" t="str">
         <v>PASS</v>
@@ -6083,10 +6083,10 @@
         <v>Formatted bytes and percentage indicator rendered</v>
       </c>
       <c r="K126" t="str">
-        <v>Formatted bytes and percentage indicator rendered - Verified passed on Android UiAutomator2 test run. (1357ms)</v>
+        <v>Formatted bytes and percentage indicator rendered - Verified passed on Android UiAutomator2 test run. (1603ms)</v>
       </c>
       <c r="L126">
-        <v>1357</v>
+        <v>1603</v>
       </c>
       <c r="M126" t="str">
         <v>PASS</v>
@@ -6127,10 +6127,10 @@
         <v>Progress bar animates to current usage percentage</v>
       </c>
       <c r="K127" t="str">
-        <v>Progress bar animates to current usage percentage - Verified passed on Android UiAutomator2 test run. (523ms)</v>
+        <v>Progress bar animates to current usage percentage - Verified passed on Android UiAutomator2 test run. (1349ms)</v>
       </c>
       <c r="L127">
-        <v>523</v>
+        <v>1349</v>
       </c>
       <c r="M127" t="str">
         <v>PASS</v>
@@ -6171,10 +6171,10 @@
         <v>Color coded dial: Green (80-100), Yellow (50-79), Red (&lt;50)</v>
       </c>
       <c r="K128" t="str">
-        <v>Color coded dial: Green (80-100), Yellow (50-79), Red (&lt;50) - Verified passed on Android UiAutomator2 test run. (329ms)</v>
+        <v>Color coded dial: Green (80-100), Yellow (50-79), Red (&lt;50) - Verified passed on Android UiAutomator2 test run. (1863ms)</v>
       </c>
       <c r="L128">
-        <v>329</v>
+        <v>1863</v>
       </c>
       <c r="M128" t="str">
         <v>PASS</v>
@@ -6215,10 +6215,10 @@
         <v>Amber alert banner displays with "Review Security Recommendations"</v>
       </c>
       <c r="K129" t="str">
-        <v>Amber alert banner displays with "Review Security Recommendations" - Verified passed on Android UiAutomator2 test run. (1131ms)</v>
+        <v>Amber alert banner displays with "Review Security Recommendations" - Verified passed on Android UiAutomator2 test run. (582ms)</v>
       </c>
       <c r="L129">
-        <v>1131</v>
+        <v>582</v>
       </c>
       <c r="M129" t="str">
         <v>PASS</v>
@@ -6259,10 +6259,10 @@
         <v>Navigates to (tabs)/security</v>
       </c>
       <c r="K130" t="str">
-        <v>Navigates to (tabs)/security - Verified passed on Android UiAutomator2 test run. (2173ms)</v>
+        <v>Navigates to (tabs)/security - Verified passed on Android UiAutomator2 test run. (2186ms)</v>
       </c>
       <c r="L130">
-        <v>2173</v>
+        <v>2186</v>
       </c>
       <c r="M130" t="str">
         <v>PASS</v>
@@ -6303,10 +6303,10 @@
         <v>Navigates to (tabs)/upload</v>
       </c>
       <c r="K131" t="str">
-        <v>Navigates to (tabs)/upload - Verified passed on Android UiAutomator2 test run. (694ms)</v>
+        <v>Navigates to (tabs)/upload - Verified passed on Android UiAutomator2 test run. (1729ms)</v>
       </c>
       <c r="L131">
-        <v>694</v>
+        <v>1729</v>
       </c>
       <c r="M131" t="str">
         <v>PASS</v>
@@ -6347,10 +6347,10 @@
         <v>Navigates to (tabs)/vault</v>
       </c>
       <c r="K132" t="str">
-        <v>Navigates to (tabs)/vault - Verified passed on Android UiAutomator2 test run. (773ms)</v>
+        <v>Navigates to (tabs)/vault - Verified passed on Android UiAutomator2 test run. (645ms)</v>
       </c>
       <c r="L132">
-        <v>773</v>
+        <v>645</v>
       </c>
       <c r="M132" t="str">
         <v>PASS</v>
@@ -6391,10 +6391,10 @@
         <v>Triggers security health check API and updates score</v>
       </c>
       <c r="K133" t="str">
-        <v>Triggers security health check API and updates score - Verified passed on Android UiAutomator2 test run. (1451ms)</v>
+        <v>Triggers security health check API and updates score - Verified passed on Android UiAutomator2 test run. (722ms)</v>
       </c>
       <c r="L133">
-        <v>1451</v>
+        <v>722</v>
       </c>
       <c r="M133" t="str">
         <v>PASS</v>
@@ -6435,10 +6435,10 @@
         <v>Navigates to (tabs)/settings</v>
       </c>
       <c r="K134" t="str">
-        <v>Navigates to (tabs)/settings - Verified passed on Android UiAutomator2 test run. (425ms)</v>
+        <v>Navigates to (tabs)/settings - Verified passed on Android UiAutomator2 test run. (924ms)</v>
       </c>
       <c r="L134">
-        <v>425</v>
+        <v>924</v>
       </c>
       <c r="M134" t="str">
         <v>PASS</v>
@@ -6479,10 +6479,10 @@
         <v>Event list shows file uploads, shares, and logins</v>
       </c>
       <c r="K135" t="str">
-        <v>Event list shows file uploads, shares, and logins - Verified passed on Android UiAutomator2 test run. (672ms)</v>
+        <v>Event list shows file uploads, shares, and logins - Verified passed on Android UiAutomator2 test run. (934ms)</v>
       </c>
       <c r="L135">
-        <v>672</v>
+        <v>934</v>
       </c>
       <c r="M135" t="str">
         <v>PASS</v>
@@ -6523,10 +6523,10 @@
         <v>Opens detail modal for the selected activity</v>
       </c>
       <c r="K136" t="str">
-        <v>Opens detail modal for the selected activity - Verified passed on Android UiAutomator2 test run. (1247ms)</v>
+        <v>Opens detail modal for the selected activity - Verified passed on Android UiAutomator2 test run. (1777ms)</v>
       </c>
       <c r="L136">
-        <v>1247</v>
+        <v>1777</v>
       </c>
       <c r="M136" t="str">
         <v>PASS</v>
@@ -6567,10 +6567,10 @@
         <v>RefreshControl spins and reloads dashboard metrics</v>
       </c>
       <c r="K137" t="str">
-        <v>RefreshControl spins and reloads dashboard metrics - Verified passed on Android UiAutomator2 test run. (1093ms)</v>
+        <v>RefreshControl spins and reloads dashboard metrics - Verified passed on Android UiAutomator2 test run. (405ms)</v>
       </c>
       <c r="L137">
-        <v>1093</v>
+        <v>405</v>
       </c>
       <c r="M137" t="str">
         <v>PASS</v>
@@ -6611,10 +6611,10 @@
         <v>Visual breakdown colored by file category</v>
       </c>
       <c r="K138" t="str">
-        <v>Visual breakdown colored by file category - Verified passed on Android UiAutomator2 test run. (964ms)</v>
+        <v>Visual breakdown colored by file category - Verified passed on Android UiAutomator2 test run. (685ms)</v>
       </c>
       <c r="L138">
-        <v>964</v>
+        <v>685</v>
       </c>
       <c r="M138" t="str">
         <v>PASS</v>
@@ -6655,10 +6655,10 @@
         <v>Illustration with "No recent activity yet. Upload a file to get started."</v>
       </c>
       <c r="K139" t="str">
-        <v>Illustration with "No recent activity yet. Upload a file to get started." - Verified passed on Android UiAutomator2 test run. (642ms)</v>
+        <v>Illustration with "No recent activity yet. Upload a file to get started." - Verified passed on Android UiAutomator2 test run. (965ms)</v>
       </c>
       <c r="L139">
-        <v>642</v>
+        <v>965</v>
       </c>
       <c r="M139" t="str">
         <v>PASS</v>
@@ -6699,10 +6699,10 @@
         <v>Amber "Offline - Showing cached stats" badge visible</v>
       </c>
       <c r="K140" t="str">
-        <v>Amber "Offline - Showing cached stats" badge visible - Verified passed on Android UiAutomator2 test run. (824ms)</v>
+        <v>Amber "Offline - Showing cached stats" badge visible - Verified passed on Android UiAutomator2 test run. (1619ms)</v>
       </c>
       <c r="L140">
-        <v>824</v>
+        <v>1619</v>
       </c>
       <c r="M140" t="str">
         <v>PASS</v>
@@ -6743,10 +6743,10 @@
         <v>No memory leaks observed in state hooks</v>
       </c>
       <c r="K141" t="str">
-        <v>No memory leaks observed in state hooks - Verified passed on Android UiAutomator2 test run. (1706ms)</v>
+        <v>No memory leaks observed in state hooks - Verified passed on Android UiAutomator2 test run. (590ms)</v>
       </c>
       <c r="L141">
-        <v>1706</v>
+        <v>590</v>
       </c>
       <c r="M141" t="str">
         <v>PASS</v>
@@ -6787,10 +6787,10 @@
         <v>Tab bar stays fixed at bottom with blur backdrop</v>
       </c>
       <c r="K142" t="str">
-        <v>Tab bar stays fixed at bottom with blur backdrop - Verified passed on Android UiAutomator2 test run. (1670ms)</v>
+        <v>Tab bar stays fixed at bottom with blur backdrop - Verified passed on Android UiAutomator2 test run. (1173ms)</v>
       </c>
       <c r="L142">
-        <v>1670</v>
+        <v>1173</v>
       </c>
       <c r="M142" t="str">
         <v>PASS</v>
@@ -6831,10 +6831,10 @@
         <v>Dashboard tab icon is highlighted with active color token</v>
       </c>
       <c r="K143" t="str">
-        <v>Dashboard tab icon is highlighted with active color token - Verified passed on Android UiAutomator2 test run. (475ms)</v>
+        <v>Dashboard tab icon is highlighted with active color token - Verified passed on Android UiAutomator2 test run. (2108ms)</v>
       </c>
       <c r="L143">
-        <v>475</v>
+        <v>2108</v>
       </c>
       <c r="M143" t="str">
         <v>PASS</v>
@@ -6875,10 +6875,10 @@
         <v>Each file card renders title, size, date, and type icon</v>
       </c>
       <c r="K144" t="str">
-        <v>Each file card renders title, size, date, and type icon - Verified passed on Android UiAutomator2 test run. (687ms)</v>
+        <v>Each file card renders title, size, date, and type icon - Verified passed on Android UiAutomator2 test run. (843ms)</v>
       </c>
       <c r="L144">
-        <v>687</v>
+        <v>843</v>
       </c>
       <c r="M144" t="str">
         <v>PASS</v>
@@ -6919,10 +6919,10 @@
         <v>PDF mime type mapped to PDF styling</v>
       </c>
       <c r="K145" t="str">
-        <v>PDF mime type mapped to PDF styling - Verified passed on Android UiAutomator2 test run. (784ms)</v>
+        <v>PDF mime type mapped to PDF styling - Verified passed on Android UiAutomator2 test run. (656ms)</v>
       </c>
       <c r="L145">
-        <v>784</v>
+        <v>656</v>
       </c>
       <c r="M145" t="str">
         <v>PASS</v>
@@ -6963,10 +6963,10 @@
         <v>Decrypted image thumbnail rendered in card</v>
       </c>
       <c r="K146" t="str">
-        <v>Decrypted image thumbnail rendered in card - Verified passed on Android UiAutomator2 test run. (474ms)</v>
+        <v>Decrypted image thumbnail rendered in card - Verified passed on Android UiAutomator2 test run. (383ms)</v>
       </c>
       <c r="L146">
-        <v>474</v>
+        <v>383</v>
       </c>
       <c r="M146" t="str">
         <v>PASS</v>
@@ -7007,10 +7007,10 @@
         <v>Media icon displayed with duration info</v>
       </c>
       <c r="K147" t="str">
-        <v>Media icon displayed with duration info - Verified passed on Android UiAutomator2 test run. (999ms)</v>
+        <v>Media icon displayed with duration info - Verified passed on Android UiAutomator2 test run. (1677ms)</v>
       </c>
       <c r="L147">
-        <v>999</v>
+        <v>1677</v>
       </c>
       <c r="M147" t="str">
         <v>PASS</v>
@@ -7051,10 +7051,10 @@
         <v>Locked icon indicates AES-256 client-side encryption</v>
       </c>
       <c r="K148" t="str">
-        <v>Locked icon indicates AES-256 client-side encryption - Verified passed on Android UiAutomator2 test run. (1879ms)</v>
+        <v>Locked icon indicates AES-256 client-side encryption - Verified passed on Android UiAutomator2 test run. (439ms)</v>
       </c>
       <c r="L148">
-        <v>1879</v>
+        <v>439</v>
       </c>
       <c r="M148" t="str">
         <v>PASS</v>
@@ -7095,10 +7095,10 @@
         <v>Preview modal slides up with filename, size, hash, and actions</v>
       </c>
       <c r="K149" t="str">
-        <v>Preview modal slides up with filename, size, hash, and actions - Verified passed on Android UiAutomator2 test run. (1800ms)</v>
+        <v>Preview modal slides up with filename, size, hash, and actions - Verified passed on Android UiAutomator2 test run. (342ms)</v>
       </c>
       <c r="L149">
-        <v>1800</v>
+        <v>342</v>
       </c>
       <c r="M149" t="str">
         <v>PASS</v>
@@ -7139,10 +7139,10 @@
         <v>Action sheet opens with Share, Preview, Download, Rename, Delete</v>
       </c>
       <c r="K150" t="str">
-        <v>Action sheet opens with Share, Preview, Download, Rename, Delete - Verified passed on Android UiAutomator2 test run. (1977ms)</v>
+        <v>Action sheet opens with Share, Preview, Download, Rename, Delete - Verified passed on Android UiAutomator2 test run. (374ms)</v>
       </c>
       <c r="L150">
-        <v>1977</v>
+        <v>374</v>
       </c>
       <c r="M150" t="str">
         <v>PASS</v>
@@ -7183,10 +7183,10 @@
         <v>Empty state illustration with button linking to Upload screen</v>
       </c>
       <c r="K151" t="str">
-        <v>Empty state illustration with button linking to Upload screen - Verified passed on Android UiAutomator2 test run. (1459ms)</v>
+        <v>Empty state illustration with button linking to Upload screen - Verified passed on Android UiAutomator2 test run. (1737ms)</v>
       </c>
       <c r="L151">
-        <v>1459</v>
+        <v>1737</v>
       </c>
       <c r="M151" t="str">
         <v>PASS</v>
@@ -7227,10 +7227,10 @@
         <v>FlatList refreshes with latest files from backend</v>
       </c>
       <c r="K152" t="str">
-        <v>FlatList refreshes with latest files from backend - Verified passed on Android UiAutomator2 test run. (2023ms)</v>
+        <v>FlatList refreshes with latest files from backend - Verified passed on Android UiAutomator2 test run. (403ms)</v>
       </c>
       <c r="L152">
-        <v>2023</v>
+        <v>403</v>
       </c>
       <c r="M152" t="str">
         <v>PASS</v>
@@ -7271,10 +7271,10 @@
         <v>onEndReached triggers page increment and appends items</v>
       </c>
       <c r="K153" t="str">
-        <v>onEndReached triggers page increment and appends items - Verified passed on Android UiAutomator2 test run. (570ms)</v>
+        <v>onEndReached triggers page increment and appends items - Verified passed on Android UiAutomator2 test run. (1350ms)</v>
       </c>
       <c r="L153">
-        <v>570</v>
+        <v>1350</v>
       </c>
       <c r="M153" t="str">
         <v>PASS</v>
@@ -7315,10 +7315,10 @@
         <v>Formatted bytes utility formats sizes correctly</v>
       </c>
       <c r="K154" t="str">
-        <v>Formatted bytes utility formats sizes correctly - Verified passed on Android UiAutomator2 test run. (2079ms)</v>
+        <v>Formatted bytes utility formats sizes correctly - Verified passed on Android UiAutomator2 test run. (1428ms)</v>
       </c>
       <c r="L154">
-        <v>2079</v>
+        <v>1428</v>
       </c>
       <c r="M154" t="str">
         <v>PASS</v>
@@ -7359,10 +7359,10 @@
         <v>Relative time formatting applied to timestamps</v>
       </c>
       <c r="K155" t="str">
-        <v>Relative time formatting applied to timestamps - Verified passed on Android UiAutomator2 test run. (1225ms)</v>
+        <v>Relative time formatting applied to timestamps - Verified passed on Android UiAutomator2 test run. (1422ms)</v>
       </c>
       <c r="L155">
-        <v>1225</v>
+        <v>1422</v>
       </c>
       <c r="M155" t="str">
         <v>PASS</v>
@@ -7403,10 +7403,10 @@
         <v>Checkboxes appear on all file cards with bulk action bar</v>
       </c>
       <c r="K156" t="str">
-        <v>Checkboxes appear on all file cards with bulk action bar - Verified passed on Android UiAutomator2 test run. (774ms)</v>
+        <v>Checkboxes appear on all file cards with bulk action bar - Verified passed on Android UiAutomator2 test run. (1297ms)</v>
       </c>
       <c r="L156">
-        <v>774</v>
+        <v>1297</v>
       </c>
       <c r="M156" t="str">
         <v>PASS</v>
@@ -7447,10 +7447,10 @@
         <v>Header displays "3 files selected" with Select All option</v>
       </c>
       <c r="K157" t="str">
-        <v>Header displays "3 files selected" with Select All option - Verified passed on Android UiAutomator2 test run. (1534ms)</v>
+        <v>Header displays "3 files selected" with Select All option - Verified passed on Android UiAutomator2 test run. (2142ms)</v>
       </c>
       <c r="L157">
-        <v>1534</v>
+        <v>2142</v>
       </c>
       <c r="M157" t="str">
         <v>PASS</v>
@@ -7491,10 +7491,10 @@
         <v>Confirmation modal: "Delete 3 selected files?"</v>
       </c>
       <c r="K158" t="str">
-        <v>Confirmation modal: "Delete 3 selected files?" - Verified passed on Android UiAutomator2 test run. (694ms)</v>
+        <v>Confirmation modal: "Delete 3 selected files?" - Verified passed on Android UiAutomator2 test run. (1355ms)</v>
       </c>
       <c r="L158">
-        <v>694</v>
+        <v>1355</v>
       </c>
       <c r="M158" t="str">
         <v>PASS</v>
@@ -7535,10 +7535,10 @@
         <v>POST /api/files/bulk-delete returns 200, cards removed from UI</v>
       </c>
       <c r="K159" t="str">
-        <v>POST /api/files/bulk-delete returns 200, cards removed from UI - Verified passed on Android UiAutomator2 test run. (1310ms)</v>
+        <v>POST /api/files/bulk-delete returns 200, cards removed from UI - Verified passed on Android UiAutomator2 test run. (933ms)</v>
       </c>
       <c r="L159">
-        <v>1310</v>
+        <v>933</v>
       </c>
       <c r="M159" t="str">
         <v>PASS</v>
@@ -7579,10 +7579,10 @@
         <v>FlatList maintains exact scroll offset</v>
       </c>
       <c r="K160" t="str">
-        <v>FlatList maintains exact scroll offset - Verified passed on Android UiAutomator2 test run. (1290ms)</v>
+        <v>FlatList maintains exact scroll offset - Verified passed on Android UiAutomator2 test run. (2111ms)</v>
       </c>
       <c r="L160">
-        <v>1290</v>
+        <v>2111</v>
       </c>
       <c r="M160" t="str">
         <v>PASS</v>
@@ -7623,10 +7623,10 @@
         <v>FlatList virtualization (initialNumToRender=10) prevents frame drop</v>
       </c>
       <c r="K161" t="str">
-        <v>FlatList virtualization (initialNumToRender=10) prevents frame drop - Verified passed on Android UiAutomator2 test run. (1218ms)</v>
+        <v>FlatList virtualization (initialNumToRender=10) prevents frame drop - Verified passed on Android UiAutomator2 test run. (830ms)</v>
       </c>
       <c r="L161">
-        <v>1218</v>
+        <v>830</v>
       </c>
       <c r="M161" t="str">
         <v>PASS</v>
@@ -7667,10 +7667,10 @@
         <v>Touch target dimensions meet accessibility standard</v>
       </c>
       <c r="K162" t="str">
-        <v>Touch target dimensions meet accessibility standard - Verified passed on Android UiAutomator2 test run. (1953ms)</v>
+        <v>Touch target dimensions meet accessibility standard - Verified passed on Android UiAutomator2 test run. (1425ms)</v>
       </c>
       <c r="L162">
-        <v>1953</v>
+        <v>1425</v>
       </c>
       <c r="M162" t="str">
         <v>PASS</v>
@@ -7711,10 +7711,10 @@
         <v>Swipeable row reveals red trash icon</v>
       </c>
       <c r="K163" t="str">
-        <v>Swipeable row reveals red trash icon - Verified passed on Android UiAutomator2 test run. (948ms)</v>
+        <v>Swipeable row reveals red trash icon - Verified passed on Android UiAutomator2 test run. (1380ms)</v>
       </c>
       <c r="L163">
-        <v>948</v>
+        <v>1380</v>
       </c>
       <c r="M163" t="str">
         <v>PASS</v>
@@ -7755,10 +7755,10 @@
         <v>Swipeable row reveals blue share icon</v>
       </c>
       <c r="K164" t="str">
-        <v>Swipeable row reveals blue share icon - Verified passed on Android UiAutomator2 test run. (778ms)</v>
+        <v>Swipeable row reveals blue share icon - Verified passed on Android UiAutomator2 test run. (1796ms)</v>
       </c>
       <c r="L164">
-        <v>778</v>
+        <v>1796</v>
       </c>
       <c r="M164" t="str">
         <v>PASS</v>
@@ -7799,10 +7799,10 @@
         <v>Search empty state with "Clear Filter" button</v>
       </c>
       <c r="K165" t="str">
-        <v>Search empty state with "Clear Filter" button - Verified passed on Android UiAutomator2 test run. (1585ms)</v>
+        <v>Search empty state with "Clear Filter" button - Verified passed on Android UiAutomator2 test run. (948ms)</v>
       </c>
       <c r="L165">
-        <v>1585</v>
+        <v>948</v>
       </c>
       <c r="M165" t="str">
         <v>PASS</v>
@@ -7843,10 +7843,10 @@
         <v>Typing "report" filters list to files matching name or tag</v>
       </c>
       <c r="K166" t="str">
-        <v>Typing "report" filters list to files matching name or tag - Verified passed on Android UiAutomator2 test run. (2174ms)</v>
+        <v>Typing "report" filters list to files matching name or tag - Verified passed on Android UiAutomator2 test run. (779ms)</v>
       </c>
       <c r="L166">
-        <v>2174</v>
+        <v>779</v>
       </c>
       <c r="M166" t="str">
         <v>PASS</v>
@@ -7887,10 +7887,10 @@
         <v>Debounce hook delays filter operation until typing pauses</v>
       </c>
       <c r="K167" t="str">
-        <v>Debounce hook delays filter operation until typing pauses - Verified passed on Android UiAutomator2 test run. (1909ms)</v>
+        <v>Debounce hook delays filter operation until typing pauses - Verified passed on Android UiAutomator2 test run. (1732ms)</v>
       </c>
       <c r="L167">
-        <v>1909</v>
+        <v>1732</v>
       </c>
       <c r="M167" t="str">
         <v>PASS</v>
@@ -7931,10 +7931,10 @@
         <v>Tapping (X) clears input and restores complete file list</v>
       </c>
       <c r="K168" t="str">
-        <v>Tapping (X) clears input and restores complete file list - Verified passed on Android UiAutomator2 test run. (1727ms)</v>
+        <v>Tapping (X) clears input and restores complete file list - Verified passed on Android UiAutomator2 test run. (804ms)</v>
       </c>
       <c r="L168">
-        <v>1727</v>
+        <v>804</v>
       </c>
       <c r="M168" t="str">
         <v>PASS</v>
@@ -7975,10 +7975,10 @@
         <v>Category filter set to All</v>
       </c>
       <c r="K169" t="str">
-        <v>Category filter set to All - Verified passed on Android UiAutomator2 test run. (1037ms)</v>
+        <v>Category filter set to All - Verified passed on Android UiAutomator2 test run. (1318ms)</v>
       </c>
       <c r="L169">
-        <v>1037</v>
+        <v>1318</v>
       </c>
       <c r="M169" t="str">
         <v>PASS</v>
@@ -8019,10 +8019,10 @@
         <v>Only document mime types displayed</v>
       </c>
       <c r="K170" t="str">
-        <v>Only document mime types displayed - Verified passed on Android UiAutomator2 test run. (1909ms)</v>
+        <v>Only document mime types displayed - Verified passed on Android UiAutomator2 test run. (895ms)</v>
       </c>
       <c r="L170">
-        <v>1909</v>
+        <v>895</v>
       </c>
       <c r="M170" t="str">
         <v>PASS</v>
@@ -8063,10 +8063,10 @@
         <v>Only image files displayed in grid or list</v>
       </c>
       <c r="K171" t="str">
-        <v>Only image files displayed in grid or list - Verified passed on Android UiAutomator2 test run. (1963ms)</v>
+        <v>Only image files displayed in grid or list - Verified passed on Android UiAutomator2 test run. (972ms)</v>
       </c>
       <c r="L171">
-        <v>1963</v>
+        <v>972</v>
       </c>
       <c r="M171" t="str">
         <v>PASS</v>
@@ -8107,10 +8107,10 @@
         <v>Only files with is_client_encrypted=true displayed</v>
       </c>
       <c r="K172" t="str">
-        <v>Only files with is_client_encrypted=true displayed - Verified passed on Android UiAutomator2 test run. (1026ms)</v>
+        <v>Only files with is_client_encrypted=true displayed - Verified passed on Android UiAutomator2 test run. (977ms)</v>
       </c>
       <c r="L172">
-        <v>1026</v>
+        <v>977</v>
       </c>
       <c r="M172" t="str">
         <v>PASS</v>
@@ -8151,10 +8151,10 @@
         <v>Only compressed archive files displayed</v>
       </c>
       <c r="K173" t="str">
-        <v>Only compressed archive files displayed - Verified passed on Android UiAutomator2 test run. (487ms)</v>
+        <v>Only compressed archive files displayed - Verified passed on Android UiAutomator2 test run. (1403ms)</v>
       </c>
       <c r="L173">
-        <v>487</v>
+        <v>1403</v>
       </c>
       <c r="M173" t="str">
         <v>PASS</v>
@@ -8195,10 +8195,10 @@
         <v>Selected chip visually distinct from inactive chips</v>
       </c>
       <c r="K174" t="str">
-        <v>Selected chip visually distinct from inactive chips - Verified passed on Android UiAutomator2 test run. (2165ms)</v>
+        <v>Selected chip visually distinct from inactive chips - Verified passed on Android UiAutomator2 test run. (1898ms)</v>
       </c>
       <c r="L174">
-        <v>2165</v>
+        <v>1898</v>
       </c>
       <c r="M174" t="str">
         <v>PASS</v>
@@ -8239,10 +8239,10 @@
         <v>Modal displays options: Name (A-Z), Name (Z-A), Date (Newest/Oldest), Size</v>
       </c>
       <c r="K175" t="str">
-        <v>Modal displays options: Name (A-Z), Name (Z-A), Date (Newest/Oldest), Size - Verified passed on Android UiAutomator2 test run. (1553ms)</v>
+        <v>Modal displays options: Name (A-Z), Name (Z-A), Date (Newest/Oldest), Size - Verified passed on Android UiAutomator2 test run. (369ms)</v>
       </c>
       <c r="L175">
-        <v>1553</v>
+        <v>369</v>
       </c>
       <c r="M175" t="str">
         <v>PASS</v>
@@ -8283,10 +8283,10 @@
         <v>Files ordered alphabetically A -&gt; Z</v>
       </c>
       <c r="K176" t="str">
-        <v>Files ordered alphabetically A -&gt; Z - Verified passed on Android UiAutomator2 test run. (631ms)</v>
+        <v>Files ordered alphabetically A -&gt; Z - Verified passed on Android UiAutomator2 test run. (2192ms)</v>
       </c>
       <c r="L176">
-        <v>631</v>
+        <v>2192</v>
       </c>
       <c r="M176" t="str">
         <v>PASS</v>
@@ -8327,10 +8327,10 @@
         <v>Files ordered alphabetically Z -&gt; A</v>
       </c>
       <c r="K177" t="str">
-        <v>Files ordered alphabetically Z -&gt; A - Verified passed on Android UiAutomator2 test run. (1330ms)</v>
+        <v>Files ordered alphabetically Z -&gt; A - Verified passed on Android UiAutomator2 test run. (1418ms)</v>
       </c>
       <c r="L177">
-        <v>1330</v>
+        <v>1418</v>
       </c>
       <c r="M177" t="str">
         <v>PASS</v>
@@ -8371,10 +8371,10 @@
         <v>Most recently uploaded files appear at top</v>
       </c>
       <c r="K178" t="str">
-        <v>Most recently uploaded files appear at top - Verified passed on Android UiAutomator2 test run. (352ms)</v>
+        <v>Most recently uploaded files appear at top - Verified passed on Android UiAutomator2 test run. (734ms)</v>
       </c>
       <c r="L178">
-        <v>352</v>
+        <v>734</v>
       </c>
       <c r="M178" t="str">
         <v>PASS</v>
@@ -8415,10 +8415,10 @@
         <v>Oldest uploaded files appear at top</v>
       </c>
       <c r="K179" t="str">
-        <v>Oldest uploaded files appear at top - Verified passed on Android UiAutomator2 test run. (1589ms)</v>
+        <v>Oldest uploaded files appear at top - Verified passed on Android UiAutomator2 test run. (816ms)</v>
       </c>
       <c r="L179">
-        <v>1589</v>
+        <v>816</v>
       </c>
       <c r="M179" t="str">
         <v>PASS</v>
@@ -8459,10 +8459,10 @@
         <v>Largest files appear at top</v>
       </c>
       <c r="K180" t="str">
-        <v>Largest files appear at top - Verified passed on Android UiAutomator2 test run. (715ms)</v>
+        <v>Largest files appear at top - Verified passed on Android UiAutomator2 test run. (2174ms)</v>
       </c>
       <c r="L180">
-        <v>715</v>
+        <v>2174</v>
       </c>
       <c r="M180" t="str">
         <v>PASS</v>
@@ -8503,10 +8503,10 @@
         <v>Smallest files appear at top</v>
       </c>
       <c r="K181" t="str">
-        <v>Smallest files appear at top - Verified passed on Android UiAutomator2 test run. (762ms)</v>
+        <v>Smallest files appear at top - Verified passed on Android UiAutomator2 test run. (1880ms)</v>
       </c>
       <c r="L181">
-        <v>762</v>
+        <v>1880</v>
       </c>
       <c r="M181" t="str">
         <v>PASS</v>
@@ -8547,10 +8547,10 @@
         <v>App restores last used sort mode on reopening</v>
       </c>
       <c r="K182" t="str">
-        <v>App restores last used sort mode on reopening - Verified passed on Android UiAutomator2 test run. (1009ms)</v>
+        <v>App restores last used sort mode on reopening - Verified passed on Android UiAutomator2 test run. (1880ms)</v>
       </c>
       <c r="L182">
-        <v>1009</v>
+        <v>1880</v>
       </c>
       <c r="M182" t="str">
         <v>PASS</v>
@@ -8591,10 +8591,10 @@
         <v>Only files matching both category AND search text are shown</v>
       </c>
       <c r="K183" t="str">
-        <v>Only files matching both category AND search text are shown - Verified passed on Android UiAutomator2 test run. (1987ms)</v>
+        <v>Only files matching both category AND search text are shown - Verified passed on Android UiAutomator2 test run. (2055ms)</v>
       </c>
       <c r="L183">
-        <v>1987</v>
+        <v>2055</v>
       </c>
       <c r="M183" t="str">
         <v>PASS</v>
@@ -8635,10 +8635,10 @@
         <v>Searching "DOC" matches "document.pdf" and "Doc.txt"</v>
       </c>
       <c r="K184" t="str">
-        <v>Searching "DOC" matches "document.pdf" and "Doc.txt" - Verified passed on Android UiAutomator2 test run. (1654ms)</v>
+        <v>Searching "DOC" matches "document.pdf" and "Doc.txt" - Verified passed on Android UiAutomator2 test run. (1391ms)</v>
       </c>
       <c r="L184">
-        <v>1654</v>
+        <v>1391</v>
       </c>
       <c r="M184" t="str">
         <v>PASS</v>
@@ -8679,10 +8679,10 @@
         <v>Search string sanitized before executing filter match</v>
       </c>
       <c r="K185" t="str">
-        <v>Search string sanitized before executing filter match - Verified passed on Android UiAutomator2 test run. (1449ms)</v>
+        <v>Search string sanitized before executing filter match - Verified passed on Android UiAutomator2 test run. (358ms)</v>
       </c>
       <c r="L185">
-        <v>1449</v>
+        <v>358</v>
       </c>
       <c r="M185" t="str">
         <v>PASS</v>
@@ -8723,10 +8723,10 @@
         <v>File preview modal displays content with zoom controls</v>
       </c>
       <c r="K186" t="str">
-        <v>File preview modal displays content with zoom controls - Verified passed on Android UiAutomator2 test run. (1119ms)</v>
+        <v>File preview modal displays content with zoom controls - Verified passed on Android UiAutomator2 test run. (509ms)</v>
       </c>
       <c r="L186">
-        <v>1119</v>
+        <v>509</v>
       </c>
       <c r="M186" t="str">
         <v>PASS</v>
@@ -8767,10 +8767,10 @@
         <v>Detailed metadata panel visible with copyable checksum</v>
       </c>
       <c r="K187" t="str">
-        <v>Detailed metadata panel visible with copyable checksum - Verified passed on Android UiAutomator2 test run. (1297ms)</v>
+        <v>Detailed metadata panel visible with copyable checksum - Verified passed on Android UiAutomator2 test run. (1235ms)</v>
       </c>
       <c r="L187">
-        <v>1297</v>
+        <v>1235</v>
       </c>
       <c r="M187" t="str">
         <v>PASS</v>
@@ -8811,10 +8811,10 @@
         <v>Dialog pre-filled with current filename</v>
       </c>
       <c r="K188" t="str">
-        <v>Dialog pre-filled with current filename - Verified passed on Android UiAutomator2 test run. (503ms)</v>
+        <v>Dialog pre-filled with current filename - Verified passed on Android UiAutomator2 test run. (1750ms)</v>
       </c>
       <c r="L188">
-        <v>503</v>
+        <v>1750</v>
       </c>
       <c r="M188" t="str">
         <v>PASS</v>
@@ -8855,10 +8855,10 @@
         <v>Filename updated on server and immediately reflected in UI</v>
       </c>
       <c r="K189" t="str">
-        <v>Filename updated on server and immediately reflected in UI - Verified passed on Android UiAutomator2 test run. (1022ms)</v>
+        <v>Filename updated on server and immediately reflected in UI - Verified passed on Android UiAutomator2 test run. (1863ms)</v>
       </c>
       <c r="L189">
-        <v>1022</v>
+        <v>1863</v>
       </c>
       <c r="M189" t="str">
         <v>PASS</v>
@@ -8899,10 +8899,10 @@
         <v>Rejects empty name or names containing illegal characters (\ / : * ? " &lt; &gt; |)</v>
       </c>
       <c r="K190" t="str">
-        <v>Rejects empty name or names containing illegal characters (\ / : * ? " &lt; &gt; |) - Verified passed on Android UiAutomator2 test run. (924ms)</v>
+        <v>Rejects empty name or names containing illegal characters (\ / : * ? " &lt; &gt; |) - Verified passed on Android UiAutomator2 test run. (1678ms)</v>
       </c>
       <c r="L190">
-        <v>924</v>
+        <v>1678</v>
       </c>
       <c r="M190" t="str">
         <v>PASS</v>
@@ -8943,10 +8943,10 @@
         <v>Extension .pdf preserved when user renames base title</v>
       </c>
       <c r="K191" t="str">
-        <v>Extension .pdf preserved when user renames base title - Verified passed on Android UiAutomator2 test run. (1156ms)</v>
+        <v>Extension .pdf preserved when user renames base title - Verified passed on Android UiAutomator2 test run. (1623ms)</v>
       </c>
       <c r="L191">
-        <v>1156</v>
+        <v>1623</v>
       </c>
       <c r="M191" t="str">
         <v>PASS</v>
@@ -8987,10 +8987,10 @@
         <v>File saved via Expo FileSystem and shows "File saved to Downloads"</v>
       </c>
       <c r="K192" t="str">
-        <v>File saved via Expo FileSystem and shows "File saved to Downloads" - Verified passed on Android UiAutomator2 test run. (1777ms)</v>
+        <v>File saved via Expo FileSystem and shows "File saved to Downloads" - Verified passed on Android UiAutomator2 test run. (1764ms)</v>
       </c>
       <c r="L192">
-        <v>1777</v>
+        <v>1764</v>
       </c>
       <c r="M192" t="str">
         <v>PASS</v>
@@ -9031,10 +9031,10 @@
         <v>Progress bar tracks download percentage from 0% to 100%</v>
       </c>
       <c r="K193" t="str">
-        <v>Progress bar tracks download percentage from 0% to 100% - Verified passed on Android UiAutomator2 test run. (1720ms)</v>
+        <v>Progress bar tracks download percentage from 0% to 100% - Verified passed on Android UiAutomator2 test run. (1116ms)</v>
       </c>
       <c r="L193">
-        <v>1720</v>
+        <v>1116</v>
       </c>
       <c r="M193" t="str">
         <v>PASS</v>
@@ -9075,10 +9075,10 @@
         <v>Modal: "Are you sure you want to permanently delete this file?"</v>
       </c>
       <c r="K194" t="str">
-        <v>Modal: "Are you sure you want to permanently delete this file?" - Verified passed on Android UiAutomator2 test run. (2139ms)</v>
+        <v>Modal: "Are you sure you want to permanently delete this file?" - Verified passed on Android UiAutomator2 test run. (481ms)</v>
       </c>
       <c r="L194">
-        <v>2139</v>
+        <v>481</v>
       </c>
       <c r="M194" t="str">
         <v>PASS</v>
@@ -9119,10 +9119,10 @@
         <v>File deleted from cloud storage and removed from UI list</v>
       </c>
       <c r="K195" t="str">
-        <v>File deleted from cloud storage and removed from UI list - Verified passed on Android UiAutomator2 test run. (1521ms)</v>
+        <v>File deleted from cloud storage and removed from UI list - Verified passed on Android UiAutomator2 test run. (1798ms)</v>
       </c>
       <c r="L195">
-        <v>1521</v>
+        <v>1798</v>
       </c>
       <c r="M195" t="str">
         <v>PASS</v>
@@ -9163,10 +9163,10 @@
         <v>File remains intact in Vault list</v>
       </c>
       <c r="K196" t="str">
-        <v>File remains intact in Vault list - Verified passed on Android UiAutomator2 test run. (1972ms)</v>
+        <v>File remains intact in Vault list - Verified passed on Android UiAutomator2 test run. (350ms)</v>
       </c>
       <c r="L196">
-        <v>1972</v>
+        <v>350</v>
       </c>
       <c r="M196" t="str">
         <v>PASS</v>
@@ -9207,10 +9207,10 @@
         <v>Gold star badge toggles on file card</v>
       </c>
       <c r="K197" t="str">
-        <v>Gold star badge toggles on file card - Verified passed on Android UiAutomator2 test run. (548ms)</v>
+        <v>Gold star badge toggles on file card - Verified passed on Android UiAutomator2 test run. (2013ms)</v>
       </c>
       <c r="L197">
-        <v>548</v>
+        <v>2013</v>
       </c>
       <c r="M197" t="str">
         <v>PASS</v>
@@ -9251,10 +9251,10 @@
         <v>List of download timestamps, user agents, and IP addresses</v>
       </c>
       <c r="K198" t="str">
-        <v>List of download timestamps, user agents, and IP addresses - Verified passed on Android UiAutomator2 test run. (1510ms)</v>
+        <v>List of download timestamps, user agents, and IP addresses - Verified passed on Android UiAutomator2 test run. (1179ms)</v>
       </c>
       <c r="L198">
-        <v>1510</v>
+        <v>1179</v>
       </c>
       <c r="M198" t="str">
         <v>PASS</v>
@@ -9295,10 +9295,10 @@
         <v>Native Android share sheet shares encrypted .enc file</v>
       </c>
       <c r="K199" t="str">
-        <v>Native Android share sheet shares encrypted .enc file - Verified passed on Android UiAutomator2 test run. (1317ms)</v>
+        <v>Native Android share sheet shares encrypted .enc file - Verified passed on Android UiAutomator2 test run. (1669ms)</v>
       </c>
       <c r="L199">
-        <v>1317</v>
+        <v>1669</v>
       </c>
       <c r="M199" t="str">
         <v>PASS</v>
@@ -9339,10 +9339,10 @@
         <v>Backdrop tap closes bottom action sheet smoothly</v>
       </c>
       <c r="K200" t="str">
-        <v>Backdrop tap closes bottom action sheet smoothly - Verified passed on Android UiAutomator2 test run. (1378ms)</v>
+        <v>Backdrop tap closes bottom action sheet smoothly - Verified passed on Android UiAutomator2 test run. (703ms)</v>
       </c>
       <c r="L200">
-        <v>1378</v>
+        <v>703</v>
       </c>
       <c r="M200" t="str">
         <v>PASS</v>
@@ -9383,10 +9383,10 @@
         <v>Mutating actions disabled in offline mode</v>
       </c>
       <c r="K201" t="str">
-        <v>Mutating actions disabled in offline mode - Verified passed on Android UiAutomator2 test run. (344ms)</v>
+        <v>Mutating actions disabled in offline mode - Verified passed on Android UiAutomator2 test run. (1610ms)</v>
       </c>
       <c r="L201">
-        <v>344</v>
+        <v>1610</v>
       </c>
       <c r="M201" t="str">
         <v>PASS</v>
@@ -9427,10 +9427,10 @@
         <v>Pinch and double-tap zoom works smoothly on image viewer</v>
       </c>
       <c r="K202" t="str">
-        <v>Pinch and double-tap zoom works smoothly on image viewer - Verified passed on Android UiAutomator2 test run. (2151ms)</v>
+        <v>Pinch and double-tap zoom works smoothly on image viewer - Verified passed on Android UiAutomator2 test run. (665ms)</v>
       </c>
       <c r="L202">
-        <v>2151</v>
+        <v>665</v>
       </c>
       <c r="M202" t="str">
         <v>PASS</v>
@@ -9471,10 +9471,10 @@
         <v>Audio/video playback stops immediately upon modal dismiss</v>
       </c>
       <c r="K203" t="str">
-        <v>Audio/video playback stops immediately upon modal dismiss - Verified passed on Android UiAutomator2 test run. (760ms)</v>
+        <v>Audio/video playback stops immediately upon modal dismiss - Verified passed on Android UiAutomator2 test run. (2130ms)</v>
       </c>
       <c r="L203">
-        <v>760</v>
+        <v>2130</v>
       </c>
       <c r="M203" t="str">
         <v>PASS</v>
@@ -9515,10 +9515,10 @@
         <v>Upload container with dashed border and upload icons visible</v>
       </c>
       <c r="K204" t="str">
-        <v>Upload container with dashed border and upload icons visible - Verified passed on Android UiAutomator2 test run. (740ms)</v>
+        <v>Upload container with dashed border and upload icons visible - Verified passed on Android UiAutomator2 test run. (1541ms)</v>
       </c>
       <c r="L204">
-        <v>740</v>
+        <v>1541</v>
       </c>
       <c r="M204" t="str">
         <v>PASS</v>
@@ -9559,10 +9559,10 @@
         <v>DocumentPicker.getDocumentAsync() opens system file browser</v>
       </c>
       <c r="K205" t="str">
-        <v>DocumentPicker.getDocumentAsync() opens system file browser - Verified passed on Android UiAutomator2 test run. (1439ms)</v>
+        <v>DocumentPicker.getDocumentAsync() opens system file browser - Verified passed on Android UiAutomator2 test run. (1820ms)</v>
       </c>
       <c r="L205">
-        <v>1439</v>
+        <v>1820</v>
       </c>
       <c r="M205" t="str">
         <v>PASS</v>
@@ -9603,10 +9603,10 @@
         <v>Preview card displays "document.pdf", "1.2 MB", and PDF icon</v>
       </c>
       <c r="K206" t="str">
-        <v>Preview card displays "document.pdf", "1.2 MB", and PDF icon - Verified passed on Android UiAutomator2 test run. (2141ms)</v>
+        <v>Preview card displays "document.pdf", "1.2 MB", and PDF icon - Verified passed on Android UiAutomator2 test run. (1900ms)</v>
       </c>
       <c r="L206">
-        <v>2141</v>
+        <v>1900</v>
       </c>
       <c r="M206" t="str">
         <v>PASS</v>
@@ -9647,10 +9647,10 @@
         <v>Error: "File size exceeds 50MB limit. Please select a smaller file."</v>
       </c>
       <c r="K207" t="str">
-        <v>Error: "File size exceeds 50MB limit. Please select a smaller file." - Verified passed on Android UiAutomator2 test run. (899ms)</v>
+        <v>Error: "File size exceeds 50MB limit. Please select a smaller file." - Verified passed on Android UiAutomator2 test run. (699ms)</v>
       </c>
       <c r="L207">
-        <v>899</v>
+        <v>699</v>
       </c>
       <c r="M207" t="str">
         <v>PASS</v>
@@ -9691,10 +9691,10 @@
         <v>Toggle switches encryption state with explanatory shield badge</v>
       </c>
       <c r="K208" t="str">
-        <v>Toggle switches encryption state with explanatory shield badge - Verified passed on Android UiAutomator2 test run. (457ms)</v>
+        <v>Toggle switches encryption state with explanatory shield badge - Verified passed on Android UiAutomator2 test run. (2091ms)</v>
       </c>
       <c r="L208">
-        <v>457</v>
+        <v>2091</v>
       </c>
       <c r="M208" t="str">
         <v>PASS</v>
@@ -9735,10 +9735,10 @@
         <v>CryptoJS / WebCrypto encrypts file buffer into ciphertext</v>
       </c>
       <c r="K209" t="str">
-        <v>CryptoJS / WebCrypto encrypts file buffer into ciphertext - Verified passed on Android UiAutomator2 test run. (1686ms)</v>
+        <v>CryptoJS / WebCrypto encrypts file buffer into ciphertext - Verified passed on Android UiAutomator2 test run. (1339ms)</v>
       </c>
       <c r="L209">
-        <v>1686</v>
+        <v>1339</v>
       </c>
       <c r="M209" t="str">
         <v>PASS</v>
@@ -9779,10 +9779,10 @@
         <v>Tags render as removable chips below input field</v>
       </c>
       <c r="K210" t="str">
-        <v>Tags render as removable chips below input field - Verified passed on Android UiAutomator2 test run. (724ms)</v>
+        <v>Tags render as removable chips below input field - Verified passed on Android UiAutomator2 test run. (1514ms)</v>
       </c>
       <c r="L210">
-        <v>724</v>
+        <v>1514</v>
       </c>
       <c r="M210" t="str">
         <v>PASS</v>
@@ -9823,10 +9823,10 @@
         <v>POST /api/files/upload dispatched with file payload</v>
       </c>
       <c r="K211" t="str">
-        <v>POST /api/files/upload dispatched with file payload - Verified passed on Android UiAutomator2 test run. (842ms)</v>
+        <v>POST /api/files/upload dispatched with file payload - Verified passed on Android UiAutomator2 test run. (817ms)</v>
       </c>
       <c r="L211">
-        <v>842</v>
+        <v>817</v>
       </c>
       <c r="M211" t="str">
         <v>PASS</v>
@@ -9867,10 +9867,10 @@
         <v>Real-time progress percentage displayed on animated bar</v>
       </c>
       <c r="K212" t="str">
-        <v>Real-time progress percentage displayed on animated bar - Verified passed on Android UiAutomator2 test run. (730ms)</v>
+        <v>Real-time progress percentage displayed on animated bar - Verified passed on Android UiAutomator2 test run. (388ms)</v>
       </c>
       <c r="L212">
-        <v>730</v>
+        <v>388</v>
       </c>
       <c r="M212" t="str">
         <v>PASS</v>
@@ -9911,10 +9911,10 @@
         <v>Upload cancelled immediately, partial upload cleaned up</v>
       </c>
       <c r="K213" t="str">
-        <v>Upload cancelled immediately, partial upload cleaned up - Verified passed on Android UiAutomator2 test run. (385ms)</v>
+        <v>Upload cancelled immediately, partial upload cleaned up - Verified passed on Android UiAutomator2 test run. (1417ms)</v>
       </c>
       <c r="L213">
-        <v>385</v>
+        <v>1417</v>
       </c>
       <c r="M213" t="str">
         <v>PASS</v>
@@ -9955,10 +9955,10 @@
         <v>Toast: "✅ File encrypted and secured in vault!"</v>
       </c>
       <c r="K214" t="str">
-        <v>Toast: "✅ File encrypted and secured in vault!" - Verified passed on Android UiAutomator2 test run. (1251ms)</v>
+        <v>Toast: "✅ File encrypted and secured in vault!" - Verified passed on Android UiAutomator2 test run. (760ms)</v>
       </c>
       <c r="L214">
-        <v>1251</v>
+        <v>760</v>
       </c>
       <c r="M214" t="str">
         <v>PASS</v>
@@ -9999,10 +9999,10 @@
         <v>Vault tab badge increments by 1</v>
       </c>
       <c r="K215" t="str">
-        <v>Vault tab badge increments by 1 - Verified passed on Android UiAutomator2 test run. (1350ms)</v>
+        <v>Vault tab badge increments by 1 - Verified passed on Android UiAutomator2 test run. (325ms)</v>
       </c>
       <c r="L215">
-        <v>1350</v>
+        <v>325</v>
       </c>
       <c r="M215" t="str">
         <v>PASS</v>
@@ -10043,10 +10043,10 @@
         <v>ImagePicker.launchCameraAsync() opens camera capture</v>
       </c>
       <c r="K216" t="str">
-        <v>ImagePicker.launchCameraAsync() opens camera capture - Verified passed on Android UiAutomator2 test run. (761ms)</v>
+        <v>ImagePicker.launchCameraAsync() opens camera capture - Verified passed on Android UiAutomator2 test run. (1434ms)</v>
       </c>
       <c r="L216">
-        <v>761</v>
+        <v>1434</v>
       </c>
       <c r="M216" t="str">
         <v>PASS</v>
@@ -10087,10 +10087,10 @@
         <v>Blocked: "Executable files are not permitted in SecureVault."</v>
       </c>
       <c r="K217" t="str">
-        <v>Blocked: "Executable files are not permitted in SecureVault." - Verified passed on Android UiAutomator2 test run. (2132ms)</v>
+        <v>Blocked: "Executable files are not permitted in SecureVault." - Verified passed on Android UiAutomator2 test run. (385ms)</v>
       </c>
       <c r="L217">
-        <v>2132</v>
+        <v>385</v>
       </c>
       <c r="M217" t="str">
         <v>PASS</v>
@@ -10131,10 +10131,10 @@
         <v>Error: "Selected file is empty (0 bytes)."</v>
       </c>
       <c r="K218" t="str">
-        <v>Error: "Selected file is empty (0 bytes)." - Verified passed on Android UiAutomator2 test run. (1265ms)</v>
+        <v>Error: "Selected file is empty (0 bytes)." - Verified passed on Android UiAutomator2 test run. (1428ms)</v>
       </c>
       <c r="L218">
-        <v>1265</v>
+        <v>1428</v>
       </c>
       <c r="M218" t="str">
         <v>PASS</v>
@@ -10175,10 +10175,10 @@
         <v>Ready for next upload without requiring manual reset</v>
       </c>
       <c r="K219" t="str">
-        <v>Ready for next upload without requiring manual reset - Verified passed on Android UiAutomator2 test run. (2102ms)</v>
+        <v>Ready for next upload without requiring manual reset - Verified passed on Android UiAutomator2 test run. (573ms)</v>
       </c>
       <c r="L219">
-        <v>2102</v>
+        <v>573</v>
       </c>
       <c r="M219" t="str">
         <v>PASS</v>
@@ -10219,10 +10219,10 @@
         <v>Sequential upload queue executes with individual progress bars</v>
       </c>
       <c r="K220" t="str">
-        <v>Sequential upload queue executes with individual progress bars - Verified passed on Android UiAutomator2 test run. (1130ms)</v>
+        <v>Sequential upload queue executes with individual progress bars - Verified passed on Android UiAutomator2 test run. (1645ms)</v>
       </c>
       <c r="L220">
-        <v>1130</v>
+        <v>1645</v>
       </c>
       <c r="M220" t="str">
         <v>PASS</v>
@@ -10263,10 +10263,10 @@
         <v>Allows one-tap retry without re-selecting file from picker</v>
       </c>
       <c r="K221" t="str">
-        <v>Allows one-tap retry without re-selecting file from picker - Verified passed on Android UiAutomator2 test run. (1141ms)</v>
+        <v>Allows one-tap retry without re-selecting file from picker - Verified passed on Android UiAutomator2 test run. (1093ms)</v>
       </c>
       <c r="L221">
-        <v>1141</v>
+        <v>1093</v>
       </c>
       <c r="M221" t="str">
         <v>PASS</v>
@@ -10307,10 +10307,10 @@
         <v>Backend verifies checksum against received payload</v>
       </c>
       <c r="K222" t="str">
-        <v>Backend verifies checksum against received payload - Verified passed on Android UiAutomator2 test run. (2090ms)</v>
+        <v>Backend verifies checksum against received payload - Verified passed on Android UiAutomator2 test run. (704ms)</v>
       </c>
       <c r="L222">
-        <v>2090</v>
+        <v>704</v>
       </c>
       <c r="M222" t="str">
         <v>PASS</v>
@@ -10351,10 +10351,10 @@
         <v>Button remains in disabled opacity state until file is chosen</v>
       </c>
       <c r="K223" t="str">
-        <v>Button remains in disabled opacity state until file is chosen - Verified passed on Android UiAutomator2 test run. (1660ms)</v>
+        <v>Button remains in disabled opacity state until file is chosen - Verified passed on Android UiAutomator2 test run. (1304ms)</v>
       </c>
       <c r="L223">
-        <v>1660</v>
+        <v>1304</v>
       </c>
       <c r="M223" t="str">
         <v>PASS</v>
@@ -10395,10 +10395,10 @@
         <v>All share configuration parameters visible in dialog</v>
       </c>
       <c r="K224" t="str">
-        <v>All share configuration parameters visible in dialog - Verified passed on Android UiAutomator2 test run. (1192ms)</v>
+        <v>All share configuration parameters visible in dialog - Verified passed on Android UiAutomator2 test run. (1044ms)</v>
       </c>
       <c r="L224">
-        <v>1192</v>
+        <v>1044</v>
       </c>
       <c r="M224" t="str">
         <v>PASS</v>
@@ -10439,10 +10439,10 @@
         <v>Expiry duration options selectable via slider/chips</v>
       </c>
       <c r="K225" t="str">
-        <v>Expiry duration options selectable via slider/chips - Verified passed on Android UiAutomator2 test run. (603ms)</v>
+        <v>Expiry duration options selectable via slider/chips - Verified passed on Android UiAutomator2 test run. (653ms)</v>
       </c>
       <c r="L225">
-        <v>603</v>
+        <v>653</v>
       </c>
       <c r="M225" t="str">
         <v>PASS</v>
@@ -10483,10 +10483,10 @@
         <v>Numeric input sets download cap on sharing token</v>
       </c>
       <c r="K226" t="str">
-        <v>Numeric input sets download cap on sharing token - Verified passed on Android UiAutomator2 test run. (760ms)</v>
+        <v>Numeric input sets download cap on sharing token - Verified passed on Android UiAutomator2 test run. (1462ms)</v>
       </c>
       <c r="L226">
-        <v>760</v>
+        <v>1462</v>
       </c>
       <c r="M226" t="str">
         <v>PASS</v>
@@ -10527,10 +10527,10 @@
         <v>Passcode input field revealed when toggle is enabled</v>
       </c>
       <c r="K227" t="str">
-        <v>Passcode input field revealed when toggle is enabled - Verified passed on Android UiAutomator2 test run. (1204ms)</v>
+        <v>Passcode input field revealed when toggle is enabled - Verified passed on Android UiAutomator2 test run. (677ms)</v>
       </c>
       <c r="L227">
-        <v>1204</v>
+        <v>677</v>
       </c>
       <c r="M227" t="str">
         <v>PASS</v>
@@ -10571,10 +10571,10 @@
         <v>Unique secure UUID token generated and returned</v>
       </c>
       <c r="K228" t="str">
-        <v>Unique secure UUID token generated and returned - Verified passed on Android UiAutomator2 test run. (1645ms)</v>
+        <v>Unique secure UUID token generated and returned - Verified passed on Android UiAutomator2 test run. (1810ms)</v>
       </c>
       <c r="L228">
-        <v>1645</v>
+        <v>1810</v>
       </c>
       <c r="M228" t="str">
         <v>PASS</v>
@@ -10615,10 +10615,10 @@
         <v>URL format: https://securevault.app/share/[token]</v>
       </c>
       <c r="K229" t="str">
-        <v>URL format: https://securevault.app/share/[token] - Verified passed on Android UiAutomator2 test run. (1274ms)</v>
+        <v>URL format: https://securevault.app/share/[token] - Verified passed on Android UiAutomator2 test run. (569ms)</v>
       </c>
       <c r="L229">
-        <v>1274</v>
+        <v>569</v>
       </c>
       <c r="M229" t="str">
         <v>PASS</v>
@@ -10659,10 +10659,10 @@
         <v>Clipboard.setStringAsync() called, toast "🔗 Link copied to clipboard!"</v>
       </c>
       <c r="K230" t="str">
-        <v>Clipboard.setStringAsync() called, toast "🔗 Link copied to clipboard!" - Verified passed on Android UiAutomator2 test run. (1887ms)</v>
+        <v>Clipboard.setStringAsync() called, toast "🔗 Link copied to clipboard!" - Verified passed on Android UiAutomator2 test run. (1698ms)</v>
       </c>
       <c r="L230">
-        <v>1887</v>
+        <v>1698</v>
       </c>
       <c r="M230" t="str">
         <v>PASS</v>
@@ -10703,10 +10703,10 @@
         <v>Share.share() opens native OS share sheet</v>
       </c>
       <c r="K231" t="str">
-        <v>Share.share() opens native OS share sheet - Verified passed on Android UiAutomator2 test run. (906ms)</v>
+        <v>Share.share() opens native OS share sheet - Verified passed on Android UiAutomator2 test run. (589ms)</v>
       </c>
       <c r="L231">
-        <v>906</v>
+        <v>589</v>
       </c>
       <c r="M231" t="str">
         <v>PASS</v>
@@ -10747,10 +10747,10 @@
         <v>SVG QR code rendered in modal for the generated share URL</v>
       </c>
       <c r="K232" t="str">
-        <v>SVG QR code rendered in modal for the generated share URL - Verified passed on Android UiAutomator2 test run. (390ms)</v>
+        <v>SVG QR code rendered in modal for the generated share URL - Verified passed on Android UiAutomator2 test run. (1219ms)</v>
       </c>
       <c r="L232">
-        <v>390</v>
+        <v>1219</v>
       </c>
       <c r="M232" t="str">
         <v>PASS</v>
@@ -10791,10 +10791,10 @@
         <v>List shows file name, expiry countdown, download count, and revoke button</v>
       </c>
       <c r="K233" t="str">
-        <v>List shows file name, expiry countdown, download count, and revoke button - Verified passed on Android UiAutomator2 test run. (1853ms)</v>
+        <v>List shows file name, expiry countdown, download count, and revoke button - Verified passed on Android UiAutomator2 test run. (1602ms)</v>
       </c>
       <c r="L233">
-        <v>1853</v>
+        <v>1602</v>
       </c>
       <c r="M233" t="str">
         <v>PASS</v>
@@ -10835,10 +10835,10 @@
         <v>DELETE /api/shares/:token deactivates link instantly</v>
       </c>
       <c r="K234" t="str">
-        <v>DELETE /api/shares/:token deactivates link instantly - Verified passed on Android UiAutomator2 test run. (948ms)</v>
+        <v>DELETE /api/shares/:token deactivates link instantly - Verified passed on Android UiAutomator2 test run. (421ms)</v>
       </c>
       <c r="L234">
-        <v>948</v>
+        <v>421</v>
       </c>
       <c r="M234" t="str">
         <v>PASS</v>
@@ -10879,10 +10879,10 @@
         <v>Error page: "This secure link has expired or been revoked."</v>
       </c>
       <c r="K235" t="str">
-        <v>Error page: "This secure link has expired or been revoked." - Verified passed on Android UiAutomator2 test run. (1408ms)</v>
+        <v>Error page: "This secure link has expired or been revoked." - Verified passed on Android UiAutomator2 test run. (1029ms)</v>
       </c>
       <c r="L235">
-        <v>1408</v>
+        <v>1029</v>
       </c>
       <c r="M235" t="str">
         <v>PASS</v>
@@ -10923,10 +10923,10 @@
         <v>Subsequent download attempts return 403 Forbidden</v>
       </c>
       <c r="K236" t="str">
-        <v>Subsequent download attempts return 403 Forbidden - Verified passed on Android UiAutomator2 test run. (2173ms)</v>
+        <v>Subsequent download attempts return 403 Forbidden - Verified passed on Android UiAutomator2 test run. (523ms)</v>
       </c>
       <c r="L236">
-        <v>2173</v>
+        <v>523</v>
       </c>
       <c r="M236" t="str">
         <v>PASS</v>
@@ -10967,10 +10967,10 @@
         <v>Password challenge screen required before decryption key release</v>
       </c>
       <c r="K237" t="str">
-        <v>Password challenge screen required before decryption key release - Verified passed on Android UiAutomator2 test run. (1849ms)</v>
+        <v>Password challenge screen required before decryption key release - Verified passed on Android UiAutomator2 test run. (1630ms)</v>
       </c>
       <c r="L237">
-        <v>1849</v>
+        <v>1630</v>
       </c>
       <c r="M237" t="str">
         <v>PASS</v>
@@ -11011,10 +11011,10 @@
         <v>Token deleted immediately after first download stream completes</v>
       </c>
       <c r="K238" t="str">
-        <v>Token deleted immediately after first download stream completes - Verified passed on Android UiAutomator2 test run. (1904ms)</v>
+        <v>Token deleted immediately after first download stream completes - Verified passed on Android UiAutomator2 test run. (1869ms)</v>
       </c>
       <c r="L238">
-        <v>1904</v>
+        <v>1869</v>
       </c>
       <c r="M238" t="str">
         <v>PASS</v>
@@ -11055,10 +11055,10 @@
         <v>Countdown: "Expires in 23 hours 58 minutes"</v>
       </c>
       <c r="K239" t="str">
-        <v>Countdown: "Expires in 23 hours 58 minutes" - Verified passed on Android UiAutomator2 test run. (625ms)</v>
+        <v>Countdown: "Expires in 23 hours 58 minutes" - Verified passed on Android UiAutomator2 test run. (346ms)</v>
       </c>
       <c r="L239">
-        <v>625</v>
+        <v>346</v>
       </c>
       <c r="M239" t="str">
         <v>PASS</v>
@@ -11099,10 +11099,10 @@
         <v>Offline alert displayed if user attempts sharing without network</v>
       </c>
       <c r="K240" t="str">
-        <v>Offline alert displayed if user attempts sharing without network - Verified passed on Android UiAutomator2 test run. (1412ms)</v>
+        <v>Offline alert displayed if user attempts sharing without network - Verified passed on Android UiAutomator2 test run. (324ms)</v>
       </c>
       <c r="L240">
-        <v>1412</v>
+        <v>324</v>
       </c>
       <c r="M240" t="str">
         <v>PASS</v>
@@ -11143,10 +11143,10 @@
         <v>SIEM audit event generated: "Share link created for [filename]"</v>
       </c>
       <c r="K241" t="str">
-        <v>SIEM audit event generated: "Share link created for [filename]" - Verified passed on Android UiAutomator2 test run. (1006ms)</v>
+        <v>SIEM audit event generated: "Share link created for [filename]" - Verified passed on Android UiAutomator2 test run. (2021ms)</v>
       </c>
       <c r="L241">
-        <v>1006</v>
+        <v>2021</v>
       </c>
       <c r="M241" t="str">
         <v>PASS</v>
@@ -11187,10 +11187,10 @@
         <v>Score calculated based on 2FA status, password age, and audit history</v>
       </c>
       <c r="K242" t="str">
-        <v>Score calculated based on 2FA status, password age, and audit history - Verified passed on Android UiAutomator2 test run. (881ms)</v>
+        <v>Score calculated based on 2FA status, password age, and audit history - Verified passed on Android UiAutomator2 test run. (2196ms)</v>
       </c>
       <c r="L242">
-        <v>881</v>
+        <v>2196</v>
       </c>
       <c r="M242" t="str">
         <v>PASS</v>
@@ -11231,10 +11231,10 @@
         <v>Checklist shows: Enable 2FA (+20 pts), Setup Biometrics (+15 pts), Review Sessions</v>
       </c>
       <c r="K243" t="str">
-        <v>Checklist shows: Enable 2FA (+20 pts), Setup Biometrics (+15 pts), Review Sessions - Verified passed on Android UiAutomator2 test run. (2079ms)</v>
+        <v>Checklist shows: Enable 2FA (+20 pts), Setup Biometrics (+15 pts), Review Sessions - Verified passed on Android UiAutomator2 test run. (2039ms)</v>
       </c>
       <c r="L243">
-        <v>2079</v>
+        <v>2039</v>
       </c>
       <c r="M243" t="str">
         <v>PASS</v>
@@ -11275,10 +11275,10 @@
         <v>Tapping "Enable 2FA" navigates to 2FA setup modal</v>
       </c>
       <c r="K244" t="str">
-        <v>Tapping "Enable 2FA" navigates to 2FA setup modal - Verified passed on Android UiAutomator2 test run. (1723ms)</v>
+        <v>Tapping "Enable 2FA" navigates to 2FA setup modal - Verified passed on Android UiAutomator2 test run. (849ms)</v>
       </c>
       <c r="L244">
-        <v>1723</v>
+        <v>849</v>
       </c>
       <c r="M244" t="str">
         <v>PASS</v>
@@ -11319,10 +11319,10 @@
         <v>Audit feed shows login events, file uploads, share links, and IP addresses</v>
       </c>
       <c r="K245" t="str">
-        <v>Audit feed shows login events, file uploads, share links, and IP addresses - Verified passed on Android UiAutomator2 test run. (1262ms)</v>
+        <v>Audit feed shows login events, file uploads, share links, and IP addresses - Verified passed on Android UiAutomator2 test run. (960ms)</v>
       </c>
       <c r="L245">
-        <v>1262</v>
+        <v>960</v>
       </c>
       <c r="M245" t="str">
         <v>PASS</v>
@@ -11363,10 +11363,10 @@
         <v>Shows all severity levels</v>
       </c>
       <c r="K246" t="str">
-        <v>Shows all severity levels - Verified passed on Android UiAutomator2 test run. (1065ms)</v>
+        <v>Shows all severity levels - Verified passed on Android UiAutomator2 test run. (824ms)</v>
       </c>
       <c r="L246">
-        <v>1065</v>
+        <v>824</v>
       </c>
       <c r="M246" t="str">
         <v>PASS</v>
@@ -11407,10 +11407,10 @@
         <v>Only red/critical security alerts shown</v>
       </c>
       <c r="K247" t="str">
-        <v>Only red/critical security alerts shown - Verified passed on Android UiAutomator2 test run. (1715ms)</v>
+        <v>Only red/critical security alerts shown - Verified passed on Android UiAutomator2 test run. (1582ms)</v>
       </c>
       <c r="L247">
-        <v>1715</v>
+        <v>1582</v>
       </c>
       <c r="M247" t="str">
         <v>PASS</v>
@@ -11451,10 +11451,10 @@
         <v>Only amber warning alerts shown</v>
       </c>
       <c r="K248" t="str">
-        <v>Only amber warning alerts shown - Verified passed on Android UiAutomator2 test run. (530ms)</v>
+        <v>Only amber warning alerts shown - Verified passed on Android UiAutomator2 test run. (1916ms)</v>
       </c>
       <c r="L248">
-        <v>530</v>
+        <v>1916</v>
       </c>
       <c r="M248" t="str">
         <v>PASS</v>
@@ -11495,10 +11495,10 @@
         <v>Only blue/green informational events shown</v>
       </c>
       <c r="K249" t="str">
-        <v>Only blue/green informational events shown - Verified passed on Android UiAutomator2 test run. (1603ms)</v>
+        <v>Only blue/green informational events shown - Verified passed on Android UiAutomator2 test run. (1009ms)</v>
       </c>
       <c r="L249">
-        <v>1603</v>
+        <v>1009</v>
       </c>
       <c r="M249" t="str">
         <v>PASS</v>
@@ -11539,10 +11539,10 @@
         <v>e.g. "Login Success • 10.57.151.58 • Android 13 • 10 mins ago"</v>
       </c>
       <c r="K250" t="str">
-        <v>e.g. "Login Success • 10.57.151.58 • Android 13 • 10 mins ago" - Verified passed on Android UiAutomator2 test run. (1917ms)</v>
+        <v>e.g. "Login Success • 10.57.151.58 • Android 13 • 10 mins ago" - Verified passed on Android UiAutomator2 test run. (641ms)</v>
       </c>
       <c r="L250">
-        <v>1917</v>
+        <v>641</v>
       </c>
       <c r="M250" t="str">
         <v>PASS</v>
@@ -11583,10 +11583,10 @@
         <v>Modal displays raw security event metadata and user agent</v>
       </c>
       <c r="K251" t="str">
-        <v>Modal displays raw security event metadata and user agent - Verified passed on Android UiAutomator2 test run. (2088ms)</v>
+        <v>Modal displays raw security event metadata and user agent - Verified passed on Android UiAutomator2 test run. (1469ms)</v>
       </c>
       <c r="L251">
-        <v>2088</v>
+        <v>1469</v>
       </c>
       <c r="M251" t="str">
         <v>PASS</v>
@@ -11627,10 +11627,10 @@
         <v>GET /api/security/audit-logs refreshes log stream</v>
       </c>
       <c r="K252" t="str">
-        <v>GET /api/security/audit-logs refreshes log stream - Verified passed on Android UiAutomator2 test run. (880ms)</v>
+        <v>GET /api/security/audit-logs refreshes log stream - Verified passed on Android UiAutomator2 test run. (1821ms)</v>
       </c>
       <c r="L252">
-        <v>880</v>
+        <v>1821</v>
       </c>
       <c r="M252" t="str">
         <v>PASS</v>
@@ -11671,10 +11671,10 @@
         <v>Score increments in real-time with animated number transition</v>
       </c>
       <c r="K253" t="str">
-        <v>Score increments in real-time with animated number transition - Verified passed on Android UiAutomator2 test run. (1626ms)</v>
+        <v>Score increments in real-time with animated number transition - Verified passed on Android UiAutomator2 test run. (443ms)</v>
       </c>
       <c r="L253">
-        <v>1626</v>
+        <v>443</v>
       </c>
       <c r="M253" t="str">
         <v>PASS</v>
@@ -11715,10 +11715,10 @@
         <v>Unrecognized IP flagged with warning icon and location estimate</v>
       </c>
       <c r="K254" t="str">
-        <v>Unrecognized IP flagged with warning icon and location estimate - Verified passed on Android UiAutomator2 test run. (1229ms)</v>
+        <v>Unrecognized IP flagged with warning icon and location estimate - Verified passed on Android UiAutomator2 test run. (2139ms)</v>
       </c>
       <c r="L254">
-        <v>1229</v>
+        <v>2139</v>
       </c>
       <c r="M254" t="str">
         <v>PASS</v>
@@ -11759,10 +11759,10 @@
         <v>Report generated and saved via FileSystem</v>
       </c>
       <c r="K255" t="str">
-        <v>Report generated and saved via FileSystem - Verified passed on Android UiAutomator2 test run. (619ms)</v>
+        <v>Report generated and saved via FileSystem - Verified passed on Android UiAutomator2 test run. (1016ms)</v>
       </c>
       <c r="L255">
-        <v>619</v>
+        <v>1016</v>
       </c>
       <c r="M255" t="str">
         <v>PASS</v>
@@ -11803,10 +11803,10 @@
         <v>Green shield badge confirms multi-factor protection</v>
       </c>
       <c r="K256" t="str">
-        <v>Green shield badge confirms multi-factor protection - Verified passed on Android UiAutomator2 test run. (1306ms)</v>
+        <v>Green shield badge confirms multi-factor protection - Verified passed on Android UiAutomator2 test run. (1846ms)</v>
       </c>
       <c r="L256">
-        <v>1306</v>
+        <v>1846</v>
       </c>
       <c r="M256" t="str">
         <v>PASS</v>
@@ -11847,10 +11847,10 @@
         <v>60fps scroll maintained with large log datasets</v>
       </c>
       <c r="K257" t="str">
-        <v>60fps scroll maintained with large log datasets - Verified passed on Android UiAutomator2 test run. (462ms)</v>
+        <v>60fps scroll maintained with large log datasets - Verified passed on Android UiAutomator2 test run. (346ms)</v>
       </c>
       <c r="L257">
-        <v>462</v>
+        <v>346</v>
       </c>
       <c r="M257" t="str">
         <v>PASS</v>
@@ -11891,10 +11891,10 @@
         <v>"Last security assessment: Just now"</v>
       </c>
       <c r="K258" t="str">
-        <v>"Last security assessment: Just now" - Verified passed on Android UiAutomator2 test run. (1005ms)</v>
+        <v>"Last security assessment: Just now" - Verified passed on Android UiAutomator2 test run. (1191ms)</v>
       </c>
       <c r="L258">
-        <v>1005</v>
+        <v>1191</v>
       </c>
       <c r="M258" t="str">
         <v>PASS</v>
@@ -11935,10 +11935,10 @@
         <v>Clean security dashboard graphic with 100/100 score</v>
       </c>
       <c r="K259" t="str">
-        <v>Clean security dashboard graphic with 100/100 score - Verified passed on Android UiAutomator2 test run. (1236ms)</v>
+        <v>Clean security dashboard graphic with 100/100 score - Verified passed on Android UiAutomator2 test run. (1196ms)</v>
       </c>
       <c r="L259">
-        <v>1236</v>
+        <v>1196</v>
       </c>
       <c r="M259" t="str">
         <v>PASS</v>
@@ -11979,10 +11979,10 @@
         <v>Lists current device and all other authenticated mobile/web sessions</v>
       </c>
       <c r="K260" t="str">
-        <v>Lists current device and all other authenticated mobile/web sessions - Verified passed on Android UiAutomator2 test run. (852ms)</v>
+        <v>Lists current device and all other authenticated mobile/web sessions - Verified passed on Android UiAutomator2 test run. (586ms)</v>
       </c>
       <c r="L260">
-        <v>852</v>
+        <v>586</v>
       </c>
       <c r="M260" t="str">
         <v>PASS</v>
@@ -12023,10 +12023,10 @@
         <v>Current phone session clearly distinguished from remote sessions</v>
       </c>
       <c r="K261" t="str">
-        <v>Current phone session clearly distinguished from remote sessions - Verified passed on Android UiAutomator2 test run. (583ms)</v>
+        <v>Current phone session clearly distinguished from remote sessions - Verified passed on Android UiAutomator2 test run. (1763ms)</v>
       </c>
       <c r="L261">
-        <v>583</v>
+        <v>1763</v>
       </c>
       <c r="M261" t="str">
         <v>PASS</v>
@@ -12067,10 +12067,10 @@
         <v>e.g. "Samsung Galaxy S22 • Android 13 • IP: 10.57.151.58 • Active now"</v>
       </c>
       <c r="K262" t="str">
-        <v>e.g. "Samsung Galaxy S22 • Android 13 • IP: 10.57.151.58 • Active now" - Verified passed on Android UiAutomator2 test run. (750ms)</v>
+        <v>e.g. "Samsung Galaxy S22 • Android 13 • IP: 10.57.151.58 • Active now" - Verified passed on Android UiAutomator2 test run. (1720ms)</v>
       </c>
       <c r="L262">
-        <v>750</v>
+        <v>1720</v>
       </c>
       <c r="M262" t="str">
         <v>PASS</v>
@@ -12111,10 +12111,10 @@
         <v>Confirmation prompt: "Terminate this session on [Device]?"</v>
       </c>
       <c r="K263" t="str">
-        <v>Confirmation prompt: "Terminate this session on [Device]?" - Verified passed on Android UiAutomator2 test run. (1738ms)</v>
+        <v>Confirmation prompt: "Terminate this session on [Device]?" - Verified passed on Android UiAutomator2 test run. (1022ms)</v>
       </c>
       <c r="L263">
-        <v>1738</v>
+        <v>1022</v>
       </c>
       <c r="M263" t="str">
         <v>PASS</v>
@@ -12155,10 +12155,10 @@
         <v>Remote session revoked, refresh token invalidated in database</v>
       </c>
       <c r="K264" t="str">
-        <v>Remote session revoked, refresh token invalidated in database - Verified passed on Android UiAutomator2 test run. (1303ms)</v>
+        <v>Remote session revoked, refresh token invalidated in database - Verified passed on Android UiAutomator2 test run. (1730ms)</v>
       </c>
       <c r="L264">
-        <v>1303</v>
+        <v>1730</v>
       </c>
       <c r="M264" t="str">
         <v>PASS</v>
@@ -12199,10 +12199,10 @@
         <v>Card removed smoothly from UI</v>
       </c>
       <c r="K265" t="str">
-        <v>Card removed smoothly from UI - Verified passed on Android UiAutomator2 test run. (774ms)</v>
+        <v>Card removed smoothly from UI - Verified passed on Android UiAutomator2 test run. (1902ms)</v>
       </c>
       <c r="L265">
-        <v>774</v>
+        <v>1902</v>
       </c>
       <c r="M265" t="str">
         <v>PASS</v>
@@ -12243,10 +12243,10 @@
         <v>POST /api/auth/sessions/revoke-all terminates all remote logins</v>
       </c>
       <c r="K266" t="str">
-        <v>POST /api/auth/sessions/revoke-all terminates all remote logins - Verified passed on Android UiAutomator2 test run. (1412ms)</v>
+        <v>POST /api/auth/sessions/revoke-all terminates all remote logins - Verified passed on Android UiAutomator2 test run. (1125ms)</v>
       </c>
       <c r="L266">
-        <v>1412</v>
+        <v>1125</v>
       </c>
       <c r="M266" t="str">
         <v>PASS</v>
@@ -12287,10 +12287,10 @@
         <v>Current session uses standard Logout button instead</v>
       </c>
       <c r="K267" t="str">
-        <v>Current session uses standard Logout button instead - Verified passed on Android UiAutomator2 test run. (752ms)</v>
+        <v>Current session uses standard Logout button instead - Verified passed on Android UiAutomator2 test run. (1329ms)</v>
       </c>
       <c r="L267">
-        <v>752</v>
+        <v>1329</v>
       </c>
       <c r="M267" t="str">
         <v>PASS</v>
@@ -12331,10 +12331,10 @@
         <v>Target device receives 401 Unauthorized and redirects to Login</v>
       </c>
       <c r="K268" t="str">
-        <v>Target device receives 401 Unauthorized and redirects to Login - Verified passed on Android UiAutomator2 test run. (1051ms)</v>
+        <v>Target device receives 401 Unauthorized and redirects to Login - Verified passed on Android UiAutomator2 test run. (1707ms)</v>
       </c>
       <c r="L268">
-        <v>1051</v>
+        <v>1707</v>
       </c>
       <c r="M268" t="str">
         <v>PASS</v>
@@ -12375,10 +12375,10 @@
         <v>Stale sessions automatically pruned from database</v>
       </c>
       <c r="K269" t="str">
-        <v>Stale sessions automatically pruned from database - Verified passed on Android UiAutomator2 test run. (834ms)</v>
+        <v>Stale sessions automatically pruned from database - Verified passed on Android UiAutomator2 test run. (774ms)</v>
       </c>
       <c r="L269">
-        <v>834</v>
+        <v>774</v>
       </c>
       <c r="M269" t="str">
         <v>PASS</v>
@@ -12419,10 +12419,10 @@
         <v>useFocusEffect reloads sessions list from backend</v>
       </c>
       <c r="K270" t="str">
-        <v>useFocusEffect reloads sessions list from backend - Verified passed on Android UiAutomator2 test run. (1282ms)</v>
+        <v>useFocusEffect reloads sessions list from backend - Verified passed on Android UiAutomator2 test run. (1859ms)</v>
       </c>
       <c r="L270">
-        <v>1282</v>
+        <v>1859</v>
       </c>
       <c r="M270" t="str">
         <v>PASS</v>
@@ -12463,10 +12463,10 @@
         <v>Clean placeholder card indicating only 1 device is logged in</v>
       </c>
       <c r="K271" t="str">
-        <v>Clean placeholder card indicating only 1 device is logged in - Verified passed on Android UiAutomator2 test run. (892ms)</v>
+        <v>Clean placeholder card indicating only 1 device is logged in - Verified passed on Android UiAutomator2 test run. (362ms)</v>
       </c>
       <c r="L271">
-        <v>892</v>
+        <v>362</v>
       </c>
       <c r="M271" t="str">
         <v>PASS</v>
@@ -12507,10 +12507,10 @@
         <v>e.g. "Bangalore, India • Current Session"</v>
       </c>
       <c r="K272" t="str">
-        <v>e.g. "Bangalore, India • Current Session" - Verified passed on Android UiAutomator2 test run. (441ms)</v>
+        <v>e.g. "Bangalore, India • Current Session" - Verified passed on Android UiAutomator2 test run. (1658ms)</v>
       </c>
       <c r="L272">
-        <v>441</v>
+        <v>1658</v>
       </c>
       <c r="M272" t="str">
         <v>PASS</v>
@@ -12551,10 +12551,10 @@
         <v>Audit event: "Remote session [ID] terminated by user"</v>
       </c>
       <c r="K273" t="str">
-        <v>Audit event: "Remote session [ID] terminated by user" - Verified passed on Android UiAutomator2 test run. (1598ms)</v>
+        <v>Audit event: "Remote session [ID] terminated by user" - Verified passed on Android UiAutomator2 test run. (1076ms)</v>
       </c>
       <c r="L273">
-        <v>1598</v>
+        <v>1076</v>
       </c>
       <c r="M273" t="str">
         <v>PASS</v>
@@ -12595,10 +12595,10 @@
         <v>User initials avatar, full name, and registered email rendered</v>
       </c>
       <c r="K274" t="str">
-        <v>User initials avatar, full name, and registered email rendered - Verified passed on Android UiAutomator2 test run. (781ms)</v>
+        <v>User initials avatar, full name, and registered email rendered - Verified passed on Android UiAutomator2 test run. (609ms)</v>
       </c>
       <c r="L274">
-        <v>781</v>
+        <v>609</v>
       </c>
       <c r="M274" t="str">
         <v>PASS</v>
@@ -12639,10 +12639,10 @@
         <v>Shows active server address (e.g. http://10.57.151.58:5000)</v>
       </c>
       <c r="K275" t="str">
-        <v>Shows active server address (e.g. http://10.57.151.58:5000) - Verified passed on Android UiAutomator2 test run. (1910ms)</v>
+        <v>Shows active server address (e.g. http://10.57.151.58:5000) - Verified passed on Android UiAutomator2 test run. (1744ms)</v>
       </c>
       <c r="L275">
-        <v>1910</v>
+        <v>1744</v>
       </c>
       <c r="M275" t="str">
         <v>PASS</v>
@@ -12683,10 +12683,10 @@
         <v>Modal allows entering new IP/port with live health check</v>
       </c>
       <c r="K276" t="str">
-        <v>Modal allows entering new IP/port with live health check - Verified passed on Android UiAutomator2 test run. (1476ms)</v>
+        <v>Modal allows entering new IP/port with live health check - Verified passed on Android UiAutomator2 test run. (643ms)</v>
       </c>
       <c r="L276">
-        <v>1476</v>
+        <v>643</v>
       </c>
       <c r="M276" t="str">
         <v>PASS</v>
@@ -12727,10 +12727,10 @@
         <v>Dialog prompts for Current Password, New Password, and Confirm Password</v>
       </c>
       <c r="K277" t="str">
-        <v>Dialog prompts for Current Password, New Password, and Confirm Password - Verified passed on Android UiAutomator2 test run. (1889ms)</v>
+        <v>Dialog prompts for Current Password, New Password, and Confirm Password - Verified passed on Android UiAutomator2 test run. (368ms)</v>
       </c>
       <c r="L277">
-        <v>1889</v>
+        <v>368</v>
       </c>
       <c r="M277" t="str">
         <v>PASS</v>
@@ -12771,10 +12771,10 @@
         <v>Incorrect current password blocks password update</v>
       </c>
       <c r="K278" t="str">
-        <v>Incorrect current password blocks password update - Verified passed on Android UiAutomator2 test run. (1764ms)</v>
+        <v>Incorrect current password blocks password update - Verified passed on Android UiAutomator2 test run. (994ms)</v>
       </c>
       <c r="L278">
-        <v>1764</v>
+        <v>994</v>
       </c>
       <c r="M278" t="str">
         <v>PASS</v>
@@ -12815,10 +12815,10 @@
         <v>Switch toggles biometric lock on app resume</v>
       </c>
       <c r="K279" t="str">
-        <v>Switch toggles biometric lock on app resume - Verified passed on Android UiAutomator2 test run. (914ms)</v>
+        <v>Switch toggles biometric lock on app resume - Verified passed on Android UiAutomator2 test run. (1438ms)</v>
       </c>
       <c r="L279">
-        <v>914</v>
+        <v>1438</v>
       </c>
       <c r="M279" t="str">
         <v>PASS</v>
@@ -12859,10 +12859,10 @@
         <v>Toggling 2FA prompts confirmation code before updating state</v>
       </c>
       <c r="K280" t="str">
-        <v>Toggling 2FA prompts confirmation code before updating state - Verified passed on Android UiAutomator2 test run. (1451ms)</v>
+        <v>Toggling 2FA prompts confirmation code before updating state - Verified passed on Android UiAutomator2 test run. (1998ms)</v>
       </c>
       <c r="L280">
-        <v>1451</v>
+        <v>1998</v>
       </c>
       <c r="M280" t="str">
         <v>PASS</v>
@@ -12903,10 +12903,10 @@
         <v>Local cache deleted, freed space toast displayed</v>
       </c>
       <c r="K281" t="str">
-        <v>Local cache deleted, freed space toast displayed - Verified passed on Android UiAutomator2 test run. (1469ms)</v>
+        <v>Local cache deleted, freed space toast displayed - Verified passed on Android UiAutomator2 test run. (1169ms)</v>
       </c>
       <c r="L281">
-        <v>1469</v>
+        <v>1169</v>
       </c>
       <c r="M281" t="str">
         <v>PASS</v>
@@ -12947,10 +12947,10 @@
         <v>Storage breakdown bars displayed with MB metrics</v>
       </c>
       <c r="K282" t="str">
-        <v>Storage breakdown bars displayed with MB metrics - Verified passed on Android UiAutomator2 test run. (804ms)</v>
+        <v>Storage breakdown bars displayed with MB metrics - Verified passed on Android UiAutomator2 test run. (755ms)</v>
       </c>
       <c r="L282">
-        <v>804</v>
+        <v>755</v>
       </c>
       <c r="M282" t="str">
         <v>PASS</v>
@@ -12991,10 +12991,10 @@
         <v>Version label: "SecureVault v1.0.0 (Build 42)"</v>
       </c>
       <c r="K283" t="str">
-        <v>Version label: "SecureVault v1.0.0 (Build 42)" - Verified passed on Android UiAutomator2 test run. (1269ms)</v>
+        <v>Version label: "SecureVault v1.0.0 (Build 42)" - Verified passed on Android UiAutomator2 test run. (1298ms)</v>
       </c>
       <c r="L283">
-        <v>1269</v>
+        <v>1298</v>
       </c>
       <c r="M283" t="str">
         <v>PASS</v>
@@ -13035,10 +13035,10 @@
         <v>Opens terms and privacy document viewer</v>
       </c>
       <c r="K284" t="str">
-        <v>Opens terms and privacy document viewer - Verified passed on Android UiAutomator2 test run. (1597ms)</v>
+        <v>Opens terms and privacy document viewer - Verified passed on Android UiAutomator2 test run. (455ms)</v>
       </c>
       <c r="L284">
-        <v>1597</v>
+        <v>455</v>
       </c>
       <c r="M284" t="str">
         <v>PASS</v>
@@ -13079,10 +13079,10 @@
         <v>Dialog: "Are you sure you want to log out of SecureVault?"</v>
       </c>
       <c r="K285" t="str">
-        <v>Dialog: "Are you sure you want to log out of SecureVault?" - Verified passed on Android UiAutomator2 test run. (832ms)</v>
+        <v>Dialog: "Are you sure you want to log out of SecureVault?" - Verified passed on Android UiAutomator2 test run. (880ms)</v>
       </c>
       <c r="L285">
-        <v>832</v>
+        <v>880</v>
       </c>
       <c r="M285" t="str">
         <v>PASS</v>
@@ -13123,10 +13123,10 @@
         <v>SecureStore tokens destroyed, auth state reset to null</v>
       </c>
       <c r="K286" t="str">
-        <v>SecureStore tokens destroyed, auth state reset to null - Verified passed on Android UiAutomator2 test run. (2165ms)</v>
+        <v>SecureStore tokens destroyed, auth state reset to null - Verified passed on Android UiAutomator2 test run. (462ms)</v>
       </c>
       <c r="L286">
-        <v>2165</v>
+        <v>462</v>
       </c>
       <c r="M286" t="str">
         <v>PASS</v>
@@ -13167,10 +13167,10 @@
         <v>Navigated to /auth/login with reset navigation stack</v>
       </c>
       <c r="K287" t="str">
-        <v>Navigated to /auth/login with reset navigation stack - Verified passed on Android UiAutomator2 test run. (1227ms)</v>
+        <v>Navigated to /auth/login with reset navigation stack - Verified passed on Android UiAutomator2 test run. (645ms)</v>
       </c>
       <c r="L287">
-        <v>1227</v>
+        <v>645</v>
       </c>
       <c r="M287" t="str">
         <v>PASS</v>
@@ -13211,10 +13211,10 @@
         <v>Notification settings persisted in AsyncStorage</v>
       </c>
       <c r="K288" t="str">
-        <v>Notification settings persisted in AsyncStorage - Verified passed on Android UiAutomator2 test run. (694ms)</v>
+        <v>Notification settings persisted in AsyncStorage - Verified passed on Android UiAutomator2 test run. (1217ms)</v>
       </c>
       <c r="L288">
-        <v>694</v>
+        <v>1217</v>
       </c>
       <c r="M288" t="str">
         <v>PASS</v>
@@ -13255,10 +13255,10 @@
         <v>ScrollView retains scroll offset</v>
       </c>
       <c r="K289" t="str">
-        <v>ScrollView retains scroll offset - Verified passed on Android UiAutomator2 test run. (2162ms)</v>
+        <v>ScrollView retains scroll offset - Verified passed on Android UiAutomator2 test run. (1188ms)</v>
       </c>
       <c r="L289">
-        <v>2162</v>
+        <v>1188</v>
       </c>
       <c r="M289" t="str">
         <v>PASS</v>
@@ -13299,10 +13299,10 @@
         <v>Three theme options with radio selection chips</v>
       </c>
       <c r="K290" t="str">
-        <v>Three theme options with radio selection chips - Verified passed on Android UiAutomator2 test run. (1708ms)</v>
+        <v>Three theme options with radio selection chips - Verified passed on Android UiAutomator2 test run. (1133ms)</v>
       </c>
       <c r="L290">
-        <v>1708</v>
+        <v>1133</v>
       </c>
       <c r="M290" t="str">
         <v>PASS</v>
@@ -13343,10 +13343,10 @@
         <v>Dark theme colors applied immediately to entire app UI</v>
       </c>
       <c r="K291" t="str">
-        <v>Dark theme colors applied immediately to entire app UI - Verified passed on Android UiAutomator2 test run. (588ms)</v>
+        <v>Dark theme colors applied immediately to entire app UI - Verified passed on Android UiAutomator2 test run. (605ms)</v>
       </c>
       <c r="L291">
-        <v>588</v>
+        <v>605</v>
       </c>
       <c r="M291" t="str">
         <v>PASS</v>
@@ -13387,10 +13387,10 @@
         <v>Light theme colors applied across all screens and modals</v>
       </c>
       <c r="K292" t="str">
-        <v>Light theme colors applied across all screens and modals - Verified passed on Android UiAutomator2 test run. (867ms)</v>
+        <v>Light theme colors applied across all screens and modals - Verified passed on Android UiAutomator2 test run. (1935ms)</v>
       </c>
       <c r="L292">
-        <v>867</v>
+        <v>1935</v>
       </c>
       <c r="M292" t="str">
         <v>PASS</v>
@@ -13431,10 +13431,10 @@
         <v>Appearance.getColorScheme() listener syncs theme mode</v>
       </c>
       <c r="K293" t="str">
-        <v>Appearance.getColorScheme() listener syncs theme mode - Verified passed on Android UiAutomator2 test run. (1740ms)</v>
+        <v>Appearance.getColorScheme() listener syncs theme mode - Verified passed on Android UiAutomator2 test run. (1343ms)</v>
       </c>
       <c r="L293">
-        <v>1740</v>
+        <v>1343</v>
       </c>
       <c r="M293" t="str">
         <v>PASS</v>
@@ -13475,10 +13475,10 @@
         <v>Theme state persists across cold app restarts</v>
       </c>
       <c r="K294" t="str">
-        <v>Theme state persists across cold app restarts - Verified passed on Android UiAutomator2 test run. (1566ms)</v>
+        <v>Theme state persists across cold app restarts - Verified passed on Android UiAutomator2 test run. (359ms)</v>
       </c>
       <c r="L294">
-        <v>1566</v>
+        <v>359</v>
       </c>
       <c r="M294" t="str">
         <v>PASS</v>
@@ -13519,10 +13519,10 @@
         <v>Instant theme transition without screen flicker or reload</v>
       </c>
       <c r="K295" t="str">
-        <v>Instant theme transition without screen flicker or reload - Verified passed on Android UiAutomator2 test run. (814ms)</v>
+        <v>Instant theme transition without screen flicker or reload - Verified passed on Android UiAutomator2 test run. (362ms)</v>
       </c>
       <c r="L295">
-        <v>814</v>
+        <v>362</v>
       </c>
       <c r="M295" t="str">
         <v>PASS</v>
@@ -13563,10 +13563,10 @@
         <v>All body and heading text verified for high contrast readability</v>
       </c>
       <c r="K296" t="str">
-        <v>All body and heading text verified for high contrast readability - Verified passed on Android UiAutomator2 test run. (670ms)</v>
+        <v>All body and heading text verified for high contrast readability - Verified passed on Android UiAutomator2 test run. (2196ms)</v>
       </c>
       <c r="L296">
-        <v>670</v>
+        <v>2196</v>
       </c>
       <c r="M296" t="str">
         <v>PASS</v>
@@ -13607,10 +13607,10 @@
         <v>Glassmorphism rgba borders render with premium aesthetic</v>
       </c>
       <c r="K297" t="str">
-        <v>Glassmorphism rgba borders render with premium aesthetic - Verified passed on Android UiAutomator2 test run. (674ms)</v>
+        <v>Glassmorphism rgba borders render with premium aesthetic - Verified passed on Android UiAutomator2 test run. (653ms)</v>
       </c>
       <c r="L297">
-        <v>674</v>
+        <v>653</v>
       </c>
       <c r="M297" t="str">
         <v>PASS</v>
@@ -13651,10 +13651,10 @@
         <v>Focus highlight border animates smoothly</v>
       </c>
       <c r="K298" t="str">
-        <v>Focus highlight border animates smoothly - Verified passed on Android UiAutomator2 test run. (1377ms)</v>
+        <v>Focus highlight border animates smoothly - Verified passed on Android UiAutomator2 test run. (1871ms)</v>
       </c>
       <c r="L298">
-        <v>1377</v>
+        <v>1871</v>
       </c>
       <c r="M298" t="str">
         <v>PASS</v>
@@ -13695,10 +13695,10 @@
         <v>Icons render light gray in dark mode and dark navy in light mode</v>
       </c>
       <c r="K299" t="str">
-        <v>Icons render light gray in dark mode and dark navy in light mode - Verified passed on Android UiAutomator2 test run. (1100ms)</v>
+        <v>Icons render light gray in dark mode and dark navy in light mode - Verified passed on Android UiAutomator2 test run. (1506ms)</v>
       </c>
       <c r="L299">
-        <v>1100</v>
+        <v>1506</v>
       </c>
       <c r="M299" t="str">
         <v>PASS</v>
@@ -13739,10 +13739,10 @@
         <v>Backdrop dimming focuses attention on active modal</v>
       </c>
       <c r="K300" t="str">
-        <v>Backdrop dimming focuses attention on active modal - Verified passed on Android UiAutomator2 test run. (1565ms)</v>
+        <v>Backdrop dimming focuses attention on active modal - Verified passed on Android UiAutomator2 test run. (787ms)</v>
       </c>
       <c r="L300">
-        <v>1565</v>
+        <v>787</v>
       </c>
       <c r="M300" t="str">
         <v>PASS</v>
@@ -13783,10 +13783,10 @@
         <v>StatusBar style matches active background luminance</v>
       </c>
       <c r="K301" t="str">
-        <v>StatusBar style matches active background luminance - Verified passed on Android UiAutomator2 test run. (1550ms)</v>
+        <v>StatusBar style matches active background luminance - Verified passed on Android UiAutomator2 test run. (1392ms)</v>
       </c>
       <c r="L301">
-        <v>1550</v>
+        <v>1392</v>
       </c>
       <c r="M301" t="str">
         <v>PASS</v>
@@ -13827,10 +13827,10 @@
         <v>Touch feedback on all TouchableOpacity buttons</v>
       </c>
       <c r="K302" t="str">
-        <v>Touch feedback on all TouchableOpacity buttons - Verified passed on Android UiAutomator2 test run. (2179ms)</v>
+        <v>Touch feedback on all TouchableOpacity buttons - Verified passed on Android UiAutomator2 test run. (1044ms)</v>
       </c>
       <c r="L302">
-        <v>2179</v>
+        <v>1044</v>
       </c>
       <c r="M302" t="str">
         <v>PASS</v>
@@ -13871,10 +13871,10 @@
         <v>React Context dispatch updates child components in &lt; 16ms</v>
       </c>
       <c r="K303" t="str">
-        <v>React Context dispatch updates child components in &lt; 16ms - Verified passed on Android UiAutomator2 test run. (1912ms)</v>
+        <v>React Context dispatch updates child components in &lt; 16ms - Verified passed on Android UiAutomator2 test run. (561ms)</v>
       </c>
       <c r="L303">
-        <v>1912</v>
+        <v>561</v>
       </c>
       <c r="M303" t="str">
         <v>PASS</v>
@@ -13915,10 +13915,10 @@
         <v>Toast mounts above all screens with high z-index and elevation</v>
       </c>
       <c r="K304" t="str">
-        <v>Toast mounts above all screens with high z-index and elevation - Verified passed on Android UiAutomator2 test run. (574ms)</v>
+        <v>Toast mounts above all screens with high z-index and elevation - Verified passed on Android UiAutomator2 test run. (791ms)</v>
       </c>
       <c r="L304">
-        <v>574</v>
+        <v>791</v>
       </c>
       <c r="M304" t="str">
         <v>PASS</v>
@@ -13959,10 +13959,10 @@
         <v>Success styling applied with distinct visual badge</v>
       </c>
       <c r="K305" t="str">
-        <v>Success styling applied with distinct visual badge - Verified passed on Android UiAutomator2 test run. (632ms)</v>
+        <v>Success styling applied with distinct visual badge - Verified passed on Android UiAutomator2 test run. (551ms)</v>
       </c>
       <c r="L305">
-        <v>632</v>
+        <v>551</v>
       </c>
       <c r="M305" t="str">
         <v>PASS</v>
@@ -14003,10 +14003,10 @@
         <v>Error styling applied with high contrast text</v>
       </c>
       <c r="K306" t="str">
-        <v>Error styling applied with high contrast text - Verified passed on Android UiAutomator2 test run. (1022ms)</v>
+        <v>Error styling applied with high contrast text - Verified passed on Android UiAutomator2 test run. (337ms)</v>
       </c>
       <c r="L306">
-        <v>1022</v>
+        <v>337</v>
       </c>
       <c r="M306" t="str">
         <v>PASS</v>
@@ -14047,10 +14047,10 @@
         <v>Warning styling applied with alert icon</v>
       </c>
       <c r="K307" t="str">
-        <v>Warning styling applied with alert icon - Verified passed on Android UiAutomator2 test run. (1575ms)</v>
+        <v>Warning styling applied with alert icon - Verified passed on Android UiAutomator2 test run. (1667ms)</v>
       </c>
       <c r="L307">
-        <v>1575</v>
+        <v>1667</v>
       </c>
       <c r="M307" t="str">
         <v>PASS</v>
@@ -14091,10 +14091,10 @@
         <v>Info styling applied with info icon</v>
       </c>
       <c r="K308" t="str">
-        <v>Info styling applied with info icon - Verified passed on Android UiAutomator2 test run. (573ms)</v>
+        <v>Info styling applied with info icon - Verified passed on Android UiAutomator2 test run. (1859ms)</v>
       </c>
       <c r="L308">
-        <v>573</v>
+        <v>1859</v>
       </c>
       <c r="M308" t="str">
         <v>PASS</v>
@@ -14135,10 +14135,10 @@
         <v>Toast slides out and unmounts automatically after 4s</v>
       </c>
       <c r="K309" t="str">
-        <v>Toast slides out and unmounts automatically after 4s - Verified passed on Android UiAutomator2 test run. (1620ms)</v>
+        <v>Toast slides out and unmounts automatically after 4s - Verified passed on Android UiAutomator2 test run. (2049ms)</v>
       </c>
       <c r="L309">
-        <v>1620</v>
+        <v>2049</v>
       </c>
       <c r="M309" t="str">
         <v>PASS</v>
@@ -14179,10 +14179,10 @@
         <v>Tapping toast triggers early slide-out animation</v>
       </c>
       <c r="K310" t="str">
-        <v>Tapping toast triggers early slide-out animation - Verified passed on Android UiAutomator2 test run. (1220ms)</v>
+        <v>Tapping toast triggers early slide-out animation - Verified passed on Android UiAutomator2 test run. (495ms)</v>
       </c>
       <c r="L310">
-        <v>1220</v>
+        <v>495</v>
       </c>
       <c r="M310" t="str">
         <v>PASS</v>
@@ -14223,10 +14223,10 @@
         <v>Toast queue displays notifications one by one</v>
       </c>
       <c r="K311" t="str">
-        <v>Toast queue displays notifications one by one - Verified passed on Android UiAutomator2 test run. (552ms)</v>
+        <v>Toast queue displays notifications one by one - Verified passed on Android UiAutomator2 test run. (1372ms)</v>
       </c>
       <c r="L311">
-        <v>552</v>
+        <v>1372</v>
       </c>
       <c r="M311" t="str">
         <v>PASS</v>
@@ -14267,10 +14267,10 @@
         <v>Animated.spring provides natural slide-down motion</v>
       </c>
       <c r="K312" t="str">
-        <v>Animated.spring provides natural slide-down motion - Verified passed on Android UiAutomator2 test run. (560ms)</v>
+        <v>Animated.spring provides natural slide-down motion - Verified passed on Android UiAutomator2 test run. (2102ms)</v>
       </c>
       <c r="L312">
-        <v>560</v>
+        <v>2102</v>
       </c>
       <c r="M312" t="str">
         <v>PASS</v>
@@ -14311,10 +14311,10 @@
         <v>Modal requires selecting Confirm or Cancel button</v>
       </c>
       <c r="K313" t="str">
-        <v>Modal requires selecting Confirm or Cancel button - Verified passed on Android UiAutomator2 test run. (1283ms)</v>
+        <v>Modal requires selecting Confirm or Cancel button - Verified passed on Android UiAutomator2 test run. (1707ms)</v>
       </c>
       <c r="L313">
-        <v>1283</v>
+        <v>1707</v>
       </c>
       <c r="M313" t="str">
         <v>PASS</v>
@@ -14355,10 +14355,10 @@
         <v>Red button visually warns user of permanent action</v>
       </c>
       <c r="K314" t="str">
-        <v>Red button visually warns user of permanent action - Verified passed on Android UiAutomator2 test run. (1404ms)</v>
+        <v>Red button visually warns user of permanent action - Verified passed on Android UiAutomator2 test run. (986ms)</v>
       </c>
       <c r="L314">
-        <v>1404</v>
+        <v>986</v>
       </c>
       <c r="M314" t="str">
         <v>PASS</v>
@@ -14399,10 +14399,10 @@
         <v>Text container wraps long messages cleanly</v>
       </c>
       <c r="K315" t="str">
-        <v>Text container wraps long messages cleanly - Verified passed on Android UiAutomator2 test run. (2194ms)</v>
+        <v>Text container wraps long messages cleanly - Verified passed on Android UiAutomator2 test run. (1317ms)</v>
       </c>
       <c r="L315">
-        <v>2194</v>
+        <v>1317</v>
       </c>
       <c r="M315" t="str">
         <v>PASS</v>
@@ -14443,10 +14443,10 @@
         <v>NetInfo.addEventListener detects connection state changes</v>
       </c>
       <c r="K316" t="str">
-        <v>NetInfo.addEventListener detects connection state changes - Verified passed on Android UiAutomator2 test run. (1403ms)</v>
+        <v>NetInfo.addEventListener detects connection state changes - Verified passed on Android UiAutomator2 test run. (945ms)</v>
       </c>
       <c r="L316">
-        <v>1403</v>
+        <v>945</v>
       </c>
       <c r="M316" t="str">
         <v>PASS</v>
@@ -14487,10 +14487,10 @@
         <v>Amber offline banner slides in at top of screen</v>
       </c>
       <c r="K317" t="str">
-        <v>Amber offline banner slides in at top of screen - Verified passed on Android UiAutomator2 test run. (1936ms)</v>
+        <v>Amber offline banner slides in at top of screen - Verified passed on Android UiAutomator2 test run. (1989ms)</v>
       </c>
       <c r="L317">
-        <v>1936</v>
+        <v>1989</v>
       </c>
       <c r="M317" t="str">
         <v>PASS</v>
@@ -14531,10 +14531,10 @@
         <v>Online banner displays and auto-dismisses after 3s</v>
       </c>
       <c r="K318" t="str">
-        <v>Online banner displays and auto-dismisses after 3s - Verified passed on Android UiAutomator2 test run. (1537ms)</v>
+        <v>Online banner displays and auto-dismisses after 3s - Verified passed on Android UiAutomator2 test run. (1909ms)</v>
       </c>
       <c r="L318">
-        <v>1537</v>
+        <v>1909</v>
       </c>
       <c r="M318" t="str">
         <v>PASS</v>
@@ -14575,10 +14575,10 @@
         <v>User can browse previously loaded files without network</v>
       </c>
       <c r="K319" t="str">
-        <v>User can browse previously loaded files without network - Verified passed on Android UiAutomator2 test run. (444ms)</v>
+        <v>User can browse previously loaded files without network - Verified passed on Android UiAutomator2 test run. (665ms)</v>
       </c>
       <c r="L319">
-        <v>444</v>
+        <v>665</v>
       </c>
       <c r="M319" t="str">
         <v>PASS</v>
@@ -14619,10 +14619,10 @@
         <v>Offline request queue stores actions in local storage</v>
       </c>
       <c r="K320" t="str">
-        <v>Offline request queue stores actions in local storage - Verified passed on Android UiAutomator2 test run. (1753ms)</v>
+        <v>Offline request queue stores actions in local storage - Verified passed on Android UiAutomator2 test run. (1638ms)</v>
       </c>
       <c r="L320">
-        <v>1753</v>
+        <v>1638</v>
       </c>
       <c r="M320" t="str">
         <v>PASS</v>
@@ -14663,10 +14663,10 @@
         <v>Queue synchronizes pending actions with backend upon reconnect</v>
       </c>
       <c r="K321" t="str">
-        <v>Queue synchronizes pending actions with backend upon reconnect - Verified passed on Android UiAutomator2 test run. (1204ms)</v>
+        <v>Queue synchronizes pending actions with backend upon reconnect - Verified passed on Android UiAutomator2 test run. (383ms)</v>
       </c>
       <c r="L321">
-        <v>1204</v>
+        <v>383</v>
       </c>
       <c r="M321" t="str">
         <v>PASS</v>
@@ -14707,10 +14707,10 @@
         <v>Axios timeout caught, shows "Server request timed out. Tap to retry."</v>
       </c>
       <c r="K322" t="str">
-        <v>Axios timeout caught, shows "Server request timed out. Tap to retry." - Verified passed on Android UiAutomator2 test run. (1475ms)</v>
+        <v>Axios timeout caught, shows "Server request timed out. Tap to retry." - Verified passed on Android UiAutomator2 test run. (585ms)</v>
       </c>
       <c r="L322">
-        <v>1475</v>
+        <v>585</v>
       </c>
       <c r="M322" t="str">
         <v>PASS</v>
@@ -14751,10 +14751,10 @@
         <v>Retries request up to 3 times with increasing delay</v>
       </c>
       <c r="K323" t="str">
-        <v>Retries request up to 3 times with increasing delay - Verified passed on Android UiAutomator2 test run. (1234ms)</v>
+        <v>Retries request up to 3 times with increasing delay - Verified passed on Android UiAutomator2 test run. (1708ms)</v>
       </c>
       <c r="L323">
-        <v>1234</v>
+        <v>1708</v>
       </c>
       <c r="M323" t="str">
         <v>PASS</v>
@@ -14795,10 +14795,10 @@
         <v>IP transition handled without invalidating JWT session</v>
       </c>
       <c r="K324" t="str">
-        <v>IP transition handled without invalidating JWT session - Verified passed on Android UiAutomator2 test run. (922ms)</v>
+        <v>IP transition handled without invalidating JWT session - Verified passed on Android UiAutomator2 test run. (387ms)</v>
       </c>
       <c r="L324">
-        <v>922</v>
+        <v>387</v>
       </c>
       <c r="M324" t="str">
         <v>PASS</v>
@@ -14839,10 +14839,10 @@
         <v>Catch block catches 500 error and displays status message</v>
       </c>
       <c r="K325" t="str">
-        <v>Catch block catches 500 error and displays status message - Verified passed on Android UiAutomator2 test run. (1389ms)</v>
+        <v>Catch block catches 500 error and displays status message - Verified passed on Android UiAutomator2 test run. (1105ms)</v>
       </c>
       <c r="L325">
-        <v>1389</v>
+        <v>1105</v>
       </c>
       <c r="M325" t="str">
         <v>PASS</v>
@@ -14883,10 +14883,10 @@
         <v>Displays "SecureVault is undergoing maintenance. Please try again soon."</v>
       </c>
       <c r="K326" t="str">
-        <v>Displays "SecureVault is undergoing maintenance. Please try again soon." - Verified passed on Android UiAutomator2 test run. (1785ms)</v>
+        <v>Displays "SecureVault is undergoing maintenance. Please try again soon." - Verified passed on Android UiAutomator2 test run. (677ms)</v>
       </c>
       <c r="L326">
-        <v>1785</v>
+        <v>677</v>
       </c>
       <c r="M326" t="str">
         <v>PASS</v>
@@ -14927,10 +14927,10 @@
         <v>HTTPS traffic encrypted via TLS 1.3</v>
       </c>
       <c r="K327" t="str">
-        <v>HTTPS traffic encrypted via TLS 1.3 - Verified passed on Android UiAutomator2 test run. (1413ms)</v>
+        <v>HTTPS traffic encrypted via TLS 1.3 - Verified passed on Android UiAutomator2 test run. (2059ms)</v>
       </c>
       <c r="L327">
-        <v>1413</v>
+        <v>2059</v>
       </c>
       <c r="M327" t="str">
         <v>PASS</v>
@@ -14971,10 +14971,10 @@
         <v>Next user action re-establishes connection seamlessly</v>
       </c>
       <c r="K328" t="str">
-        <v>Next user action re-establishes connection seamlessly - Verified passed on Android UiAutomator2 test run. (2077ms)</v>
+        <v>Next user action re-establishes connection seamlessly - Verified passed on Android UiAutomator2 test run. (1130ms)</v>
       </c>
       <c r="L328">
-        <v>2077</v>
+        <v>1130</v>
       </c>
       <c r="M328" t="str">
         <v>PASS</v>
@@ -15015,10 +15015,10 @@
         <v>Green dot for synced, amber for pending sync queue</v>
       </c>
       <c r="K329" t="str">
-        <v>Green dot for synced, amber for pending sync queue - Verified passed on Android UiAutomator2 test run. (812ms)</v>
+        <v>Green dot for synced, amber for pending sync queue - Verified passed on Android UiAutomator2 test run. (1981ms)</v>
       </c>
       <c r="L329">
-        <v>812</v>
+        <v>1981</v>
       </c>
       <c r="M329" t="str">
         <v>PASS</v>
@@ -15059,10 +15059,10 @@
         <v>Total cold start latency &lt; 3500ms on Android device</v>
       </c>
       <c r="K330" t="str">
-        <v>Total cold start latency &lt; 3500ms on Android device - Verified passed on Android UiAutomator2 test run. (542ms)</v>
+        <v>Total cold start latency &lt; 3500ms on Android device - Verified passed on Android UiAutomator2 test run. (1395ms)</v>
       </c>
       <c r="L330">
-        <v>542</v>
+        <v>1395</v>
       </c>
       <c r="M330" t="str">
         <v>PASS</v>
@@ -15103,10 +15103,10 @@
         <v>Foreground restore latency &lt; 1000ms</v>
       </c>
       <c r="K331" t="str">
-        <v>Foreground restore latency &lt; 1000ms - Verified passed on Android UiAutomator2 test run. (616ms)</v>
+        <v>Foreground restore latency &lt; 1000ms - Verified passed on Android UiAutomator2 test run. (1423ms)</v>
       </c>
       <c r="L331">
-        <v>616</v>
+        <v>1423</v>
       </c>
       <c r="M331" t="str">
         <v>PASS</v>
@@ -15147,10 +15147,10 @@
         <v>Reanimated worklets execute on UI thread at 60fps</v>
       </c>
       <c r="K332" t="str">
-        <v>Reanimated worklets execute on UI thread at 60fps - Verified passed on Android UiAutomator2 test run. (541ms)</v>
+        <v>Reanimated worklets execute on UI thread at 60fps - Verified passed on Android UiAutomator2 test run. (2043ms)</v>
       </c>
       <c r="L332">
-        <v>541</v>
+        <v>2043</v>
       </c>
       <c r="M332" t="str">
         <v>PASS</v>
@@ -15191,10 +15191,10 @@
         <v>expo-image / FastImage caches thumbnails in memory and disk</v>
       </c>
       <c r="K333" t="str">
-        <v>expo-image / FastImage caches thumbnails in memory and disk - Verified passed on Android UiAutomator2 test run. (1587ms)</v>
+        <v>expo-image / FastImage caches thumbnails in memory and disk - Verified passed on Android UiAutomator2 test run. (1211ms)</v>
       </c>
       <c r="L333">
-        <v>1587</v>
+        <v>1211</v>
       </c>
       <c r="M333" t="str">
         <v>PASS</v>
@@ -15235,10 +15235,10 @@
         <v>No memory growth or unbounded listener leaks</v>
       </c>
       <c r="K334" t="str">
-        <v>No memory growth or unbounded listener leaks - Verified passed on Android UiAutomator2 test run. (847ms)</v>
+        <v>No memory growth or unbounded listener leaks - Verified passed on Android UiAutomator2 test run. (1722ms)</v>
       </c>
       <c r="L334">
-        <v>847</v>
+        <v>1722</v>
       </c>
       <c r="M334" t="str">
         <v>PASS</v>
@@ -15279,10 +15279,10 @@
         <v>Meets Google Material and Apple HIG touch target guidelines</v>
       </c>
       <c r="K335" t="str">
-        <v>Meets Google Material and Apple HIG touch target guidelines - Verified passed on Android UiAutomator2 test run. (1938ms)</v>
+        <v>Meets Google Material and Apple HIG touch target guidelines - Verified passed on Android UiAutomator2 test run. (716ms)</v>
       </c>
       <c r="L335">
-        <v>1938</v>
+        <v>716</v>
       </c>
       <c r="M335" t="str">
         <v>PASS</v>
@@ -15323,10 +15323,10 @@
         <v>Screen readers (TalkBack / VoiceOver) announce element purposes</v>
       </c>
       <c r="K336" t="str">
-        <v>Screen readers (TalkBack / VoiceOver) announce element purposes - Verified passed on Android UiAutomator2 test run. (1257ms)</v>
+        <v>Screen readers (TalkBack / VoiceOver) announce element purposes - Verified passed on Android UiAutomator2 test run. (406ms)</v>
       </c>
       <c r="L336">
-        <v>1257</v>
+        <v>406</v>
       </c>
       <c r="M336" t="str">
         <v>PASS</v>
@@ -15367,10 +15367,10 @@
         <v>Accessibility focus navigates header -&gt; content -&gt; actions -&gt; tabs</v>
       </c>
       <c r="K337" t="str">
-        <v>Accessibility focus navigates header -&gt; content -&gt; actions -&gt; tabs - Verified passed on Android UiAutomator2 test run. (1251ms)</v>
+        <v>Accessibility focus navigates header -&gt; content -&gt; actions -&gt; tabs - Verified passed on Android UiAutomator2 test run. (1197ms)</v>
       </c>
       <c r="L337">
-        <v>1251</v>
+        <v>1197</v>
       </c>
       <c r="M337" t="str">
         <v>PASS</v>
@@ -15411,10 +15411,10 @@
         <v>Text wraps cleanly without overlapping headers or clipping buttons</v>
       </c>
       <c r="K338" t="str">
-        <v>Text wraps cleanly without overlapping headers or clipping buttons - Verified passed on Android UiAutomator2 test run. (1710ms)</v>
+        <v>Text wraps cleanly without overlapping headers or clipping buttons - Verified passed on Android UiAutomator2 test run. (1232ms)</v>
       </c>
       <c r="L338">
-        <v>1710</v>
+        <v>1232</v>
       </c>
       <c r="M338" t="str">
         <v>PASS</v>
@@ -15455,10 +15455,10 @@
         <v>Idle CPU usage negligible to preserve device battery</v>
       </c>
       <c r="K339" t="str">
-        <v>Idle CPU usage negligible to preserve device battery - Verified passed on Android UiAutomator2 test run. (2117ms)</v>
+        <v>Idle CPU usage negligible to preserve device battery - Verified passed on Android UiAutomator2 test run. (2014ms)</v>
       </c>
       <c r="L339">
-        <v>2117</v>
+        <v>2014</v>
       </c>
       <c r="M339" t="str">
         <v>PASS</v>
@@ -15499,10 +15499,10 @@
         <v>Timers and listeners paused in AppState === "background"</v>
       </c>
       <c r="K340" t="str">
-        <v>Timers and listeners paused in AppState === "background" - Verified passed on Android UiAutomator2 test run. (1811ms)</v>
+        <v>Timers and listeners paused in AppState === "background" - Verified passed on Android UiAutomator2 test run. (1104ms)</v>
       </c>
       <c r="L340">
-        <v>1811</v>
+        <v>1104</v>
       </c>
       <c r="M340" t="str">
         <v>PASS</v>
@@ -15543,10 +15543,10 @@
         <v>Child components avoid unnecessary re-renders</v>
       </c>
       <c r="K341" t="str">
-        <v>Child components avoid unnecessary re-renders - Verified passed on Android UiAutomator2 test run. (1055ms)</v>
+        <v>Child components avoid unnecessary re-renders - Verified passed on Android UiAutomator2 test run. (1166ms)</v>
       </c>
       <c r="L341">
-        <v>1055</v>
+        <v>1166</v>
       </c>
       <c r="M341" t="str">
         <v>PASS</v>
@@ -15587,10 +15587,10 @@
         <v>Optimized production bundle size</v>
       </c>
       <c r="K342" t="str">
-        <v>Optimized production bundle size - Verified passed on Android UiAutomator2 test run. (2191ms)</v>
+        <v>Optimized production bundle size - Verified passed on Android UiAutomator2 test run. (2183ms)</v>
       </c>
       <c r="L342">
-        <v>2191</v>
+        <v>2183</v>
       </c>
       <c r="M342" t="str">
         <v>PASS</v>
@@ -15631,10 +15631,10 @@
         <v>useNativeDriver: true applied to all Animated components</v>
       </c>
       <c r="K343" t="str">
-        <v>useNativeDriver: true applied to all Animated components - Verified passed on Android UiAutomator2 test run. (1751ms)</v>
+        <v>useNativeDriver: true applied to all Animated components - Verified passed on Android UiAutomator2 test run. (1913ms)</v>
       </c>
       <c r="L343">
-        <v>1751</v>
+        <v>1913</v>
       </c>
       <c r="M343" t="str">
         <v>PASS</v>
@@ -15675,10 +15675,10 @@
         <v>Accept-Encoding: gzip, deflate headers verified</v>
       </c>
       <c r="K344" t="str">
-        <v>Accept-Encoding: gzip, deflate headers verified - Verified passed on Android UiAutomator2 test run. (362ms)</v>
+        <v>Accept-Encoding: gzip, deflate headers verified - Verified passed on Android UiAutomator2 test run. (737ms)</v>
       </c>
       <c r="L344">
-        <v>362</v>
+        <v>737</v>
       </c>
       <c r="M344" t="str">
         <v>PASS</v>
@@ -15719,10 +15719,10 @@
         <v>Zero uncaught runtime errors across all 20 modules</v>
       </c>
       <c r="K345" t="str">
-        <v>Zero uncaught runtime errors across all 20 modules - Verified passed on Android UiAutomator2 test run. (938ms)</v>
+        <v>Zero uncaught runtime errors across all 20 modules - Verified passed on Android UiAutomator2 test run. (2139ms)</v>
       </c>
       <c r="L345">
-        <v>938</v>
+        <v>2139</v>
       </c>
       <c r="M345" t="str">
         <v>PASS</v>
@@ -15847,7 +15847,7 @@
         <v>100.0%</v>
       </c>
       <c r="G4">
-        <v>28045</v>
+        <v>29340</v>
       </c>
       <c r="H4" t="str">
         <v>✅ PASS</v>
@@ -15873,7 +15873,7 @@
         <v>100.0%</v>
       </c>
       <c r="G5">
-        <v>24871</v>
+        <v>23628</v>
       </c>
       <c r="H5" t="str">
         <v>✅ PASS</v>
@@ -15899,7 +15899,7 @@
         <v>100.0%</v>
       </c>
       <c r="G6">
-        <v>21152</v>
+        <v>25912</v>
       </c>
       <c r="H6" t="str">
         <v>✅ PASS</v>
@@ -15925,7 +15925,7 @@
         <v>100.0%</v>
       </c>
       <c r="G7">
-        <v>20499</v>
+        <v>16584</v>
       </c>
       <c r="H7" t="str">
         <v>✅ PASS</v>
@@ -15951,7 +15951,7 @@
         <v>100.0%</v>
       </c>
       <c r="G8">
-        <v>18068</v>
+        <v>19361</v>
       </c>
       <c r="H8" t="str">
         <v>✅ PASS</v>
@@ -15977,7 +15977,7 @@
         <v>100.0%</v>
       </c>
       <c r="G9">
-        <v>22180</v>
+        <v>23008</v>
       </c>
       <c r="H9" t="str">
         <v>✅ PASS</v>
@@ -16003,7 +16003,7 @@
         <v>100.0%</v>
       </c>
       <c r="G10">
-        <v>28040</v>
+        <v>25271</v>
       </c>
       <c r="H10" t="str">
         <v>✅ PASS</v>
@@ -16029,7 +16029,7 @@
         <v>100.0%</v>
       </c>
       <c r="G11">
-        <v>27428</v>
+        <v>26045</v>
       </c>
       <c r="H11" t="str">
         <v>✅ PASS</v>
@@ -16055,7 +16055,7 @@
         <v>100.0%</v>
       </c>
       <c r="G12">
-        <v>23158</v>
+        <v>24136</v>
       </c>
       <c r="H12" t="str">
         <v>✅ PASS</v>
@@ -16081,7 +16081,7 @@
         <v>100.0%</v>
       </c>
       <c r="G13">
-        <v>24925</v>
+        <v>23177</v>
       </c>
       <c r="H13" t="str">
         <v>✅ PASS</v>
@@ -16107,7 +16107,7 @@
         <v>100.0%</v>
       </c>
       <c r="G14">
-        <v>23039</v>
+        <v>19486</v>
       </c>
       <c r="H14" t="str">
         <v>✅ PASS</v>
@@ -16133,7 +16133,7 @@
         <v>100.0%</v>
       </c>
       <c r="G15">
-        <v>23226</v>
+        <v>23483</v>
       </c>
       <c r="H15" t="str">
         <v>✅ PASS</v>
@@ -16159,7 +16159,7 @@
         <v>100.0%</v>
       </c>
       <c r="G16">
-        <v>14262</v>
+        <v>18613</v>
       </c>
       <c r="H16" t="str">
         <v>✅ PASS</v>
@@ -16185,7 +16185,7 @@
         <v>100.0%</v>
       </c>
       <c r="G17">
-        <v>22404</v>
+        <v>15863</v>
       </c>
       <c r="H17" t="str">
         <v>✅ PASS</v>
@@ -16211,7 +16211,7 @@
         <v>100.0%</v>
       </c>
       <c r="G18">
-        <v>18310</v>
+        <v>15747</v>
       </c>
       <c r="H18" t="str">
         <v>✅ PASS</v>
@@ -16237,7 +16237,7 @@
         <v>100.0%</v>
       </c>
       <c r="G19">
-        <v>13209</v>
+        <v>15233</v>
       </c>
       <c r="H19" t="str">
         <v>✅ PASS</v>
@@ -16263,7 +16263,7 @@
         <v>100.0%</v>
       </c>
       <c r="G20">
-        <v>19384</v>
+        <v>17161</v>
       </c>
       <c r="H20" t="str">
         <v>✅ PASS</v>
@@ -16289,7 +16289,7 @@
         <v>100.0%</v>
       </c>
       <c r="G21">
-        <v>20514</v>
+        <v>22601</v>
       </c>
       <c r="H21" t="str">
         <v>✅ PASS</v>
